--- a/research/traditional_assets/database/data/united_states/united_states_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_rubber_tires.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05019999999999999</v>
+        <v>0.02755</v>
       </c>
       <c r="F2">
         <v>1.244</v>
       </c>
       <c r="G2">
-        <v>0.1029033443586917</v>
+        <v>0.1022495646883588</v>
       </c>
       <c r="H2">
-        <v>0.07870005775187694</v>
+        <v>0.07807141208802736</v>
       </c>
       <c r="I2">
-        <v>0.04433309082272166</v>
+        <v>0.04340100162296367</v>
       </c>
       <c r="J2">
-        <v>0.04433309082272166</v>
+        <v>0.04340100162296367</v>
       </c>
       <c r="K2">
-        <v>-297</v>
+        <v>-323.5</v>
       </c>
       <c r="L2">
-        <v>-0.01559300677272011</v>
+        <v>-0.01696666456877924</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -635,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>905</v>
+        <v>905.275</v>
       </c>
       <c r="V2">
-        <v>0.3529228249424794</v>
+        <v>0.3487473948200741</v>
       </c>
       <c r="W2">
-        <v>-0.05948327658722211</v>
+        <v>-0.2900559801403694</v>
       </c>
       <c r="X2">
-        <v>0.1916530501994924</v>
+        <v>0.08568550319050666</v>
       </c>
       <c r="Y2">
-        <v>-0.2511363267867145</v>
+        <v>-0.375741483330876</v>
       </c>
       <c r="Z2">
-        <v>1.503915759901778</v>
+        <v>1.500325306002394</v>
       </c>
       <c r="AA2">
         <v>0.06667323397344797</v>
       </c>
       <c r="AB2">
-        <v>0.081932087293034</v>
+        <v>0.08215688409514373</v>
       </c>
       <c r="AC2">
-        <v>-0.01525885331958603</v>
+        <v>-0.01523978501947661</v>
       </c>
       <c r="AD2">
-        <v>9028</v>
+        <v>9030.93</v>
       </c>
       <c r="AE2">
-        <v>1017.938095498102</v>
+        <v>1018.153911276381</v>
       </c>
       <c r="AF2">
-        <v>10045.9380954981</v>
+        <v>10049.08391127638</v>
       </c>
       <c r="AG2">
-        <v>9140.938095498102</v>
+        <v>9143.808911276383</v>
       </c>
       <c r="AH2">
-        <v>0.7966493589906551</v>
+        <v>0.7947160234088898</v>
       </c>
       <c r="AI2">
-        <v>0.6719718858583937</v>
+        <v>0.670717679325868</v>
       </c>
       <c r="AJ2">
-        <v>0.7809271388519433</v>
+        <v>0.7788859722024547</v>
       </c>
       <c r="AK2">
-        <v>0.6508350576801827</v>
+        <v>0.6495423925770283</v>
       </c>
       <c r="AL2">
-        <v>520</v>
+        <v>520.254</v>
       </c>
       <c r="AM2">
-        <v>450</v>
+        <v>450.254</v>
       </c>
       <c r="AN2">
-        <v>4.37827352085354</v>
+        <v>4.411466874174767</v>
       </c>
       <c r="AO2">
-        <v>1.515384615384615</v>
+        <v>1.481968423116401</v>
       </c>
       <c r="AP2">
-        <v>4.433044663190157</v>
+        <v>4.466606442069621</v>
       </c>
       <c r="AQ2">
-        <v>1.751111111111111</v>
+        <v>1.712366797407685</v>
       </c>
     </row>
     <row r="3">
@@ -712,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Goodyear Tire &amp; Rubber Company (NasdaqGS:GT)</t>
+          <t>Amerityre Corporation (OTCPK:AMTY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,29 +720,8 @@
           <t>Rubber&amp; Tires</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.05019999999999999</v>
-      </c>
-      <c r="F3">
-        <v>1.244</v>
-      </c>
-      <c r="G3">
-        <v>0.1029033443586917</v>
-      </c>
-      <c r="H3">
-        <v>0.07870005775187694</v>
-      </c>
-      <c r="I3">
-        <v>0.04433309082272166</v>
-      </c>
-      <c r="J3">
-        <v>0.04433309082272166</v>
-      </c>
       <c r="K3">
-        <v>-297</v>
-      </c>
-      <c r="L3">
-        <v>-0.01559300677272011</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -750,89 +729,330 @@
       <c r="N3">
         <v>-0</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>905</v>
+        <v>0</v>
       </c>
       <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0.08468953015995906</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0.4904036451278631</v>
+      </c>
+      <c r="AB3">
+        <v>0.08360028397894625</v>
+      </c>
+      <c r="AC3">
+        <v>0.4068033611489168</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0.2158157782791039</v>
+      </c>
+      <c r="AF3">
+        <v>0.2158157782791039</v>
+      </c>
+      <c r="AG3">
+        <v>0.2158157782791039</v>
+      </c>
+      <c r="AH3">
+        <v>0.06336683846950512</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>0.06336683846950512</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1.448428042141637</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>The Goodyear Tire &amp; Rubber Company (NasdaqGS:GT)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Rubber&amp; Tires</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.05019999999999999</v>
+      </c>
+      <c r="F4">
+        <v>1.244</v>
+      </c>
+      <c r="G4">
+        <v>0.1029033443586917</v>
+      </c>
+      <c r="H4">
+        <v>0.07870005775187694</v>
+      </c>
+      <c r="I4">
+        <v>0.04433309082272166</v>
+      </c>
+      <c r="J4">
+        <v>0.04433309082272166</v>
+      </c>
+      <c r="K4">
+        <v>-297</v>
+      </c>
+      <c r="L4">
+        <v>-0.01559300677272011</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>905</v>
+      </c>
+      <c r="V4">
         <v>0.3529228249424794</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>-0.05948327658722211</v>
       </c>
-      <c r="X3">
-        <v>0.1916530501994924</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2511363267867145</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.1915592796560863</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2510425562433084</v>
+      </c>
+      <c r="Z4">
         <v>1.503915759901778</v>
       </c>
-      <c r="AA3">
+      <c r="AA4">
         <v>0.06667323397344797</v>
       </c>
-      <c r="AB3">
-        <v>0.081932087293034</v>
-      </c>
-      <c r="AC3">
-        <v>-0.01525885331958603</v>
-      </c>
-      <c r="AD3">
+      <c r="AB4">
+        <v>0.08191301899292458</v>
+      </c>
+      <c r="AC4">
+        <v>-0.01523978501947661</v>
+      </c>
+      <c r="AD4">
         <v>9028</v>
       </c>
-      <c r="AE3">
+      <c r="AE4">
         <v>1017.938095498102</v>
       </c>
-      <c r="AF3">
+      <c r="AF4">
         <v>10045.9380954981</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>9140.938095498102</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.7966493589906551</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.6719718858583937</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>0.7809271388519433</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>0.6508350576801827</v>
       </c>
-      <c r="AL3">
+      <c r="AL4">
         <v>520</v>
       </c>
-      <c r="AM3">
+      <c r="AM4">
         <v>450</v>
       </c>
-      <c r="AN3">
+      <c r="AN4">
         <v>4.37827352085354</v>
       </c>
-      <c r="AO3">
+      <c r="AO4">
         <v>1.515384615384615</v>
       </c>
-      <c r="AP3">
+      <c r="AP4">
         <v>4.433044663190157</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ4">
         <v>1.751111111111111</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ameridge Corporation (KOSDAQ:A900100)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rubber&amp; Tires</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0049</v>
+      </c>
+      <c r="G5">
+        <v>-0.5505050505050505</v>
+      </c>
+      <c r="H5">
+        <v>-0.5505050505050505</v>
+      </c>
+      <c r="I5">
+        <v>-0.8585858585858586</v>
+      </c>
+      <c r="J5">
+        <v>-0.8585858585858586</v>
+      </c>
+      <c r="K5">
+        <v>-26.5</v>
+      </c>
+      <c r="L5">
+        <v>-1.338383838383838</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.275</v>
+      </c>
+      <c r="V5">
+        <v>0.00971731448763251</v>
+      </c>
+      <c r="W5">
+        <v>-0.5206286836935167</v>
+      </c>
+      <c r="X5">
+        <v>0.08568550319050666</v>
+      </c>
+      <c r="Y5">
+        <v>-0.6063141868840234</v>
+      </c>
+      <c r="Z5">
+        <v>0.4573804573804574</v>
+      </c>
+      <c r="AA5">
+        <v>-0.3927003927003927</v>
+      </c>
+      <c r="AB5">
+        <v>0.08215688409514373</v>
+      </c>
+      <c r="AC5">
+        <v>-0.4748572767955364</v>
+      </c>
+      <c r="AD5">
+        <v>2.93</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>2.93</v>
+      </c>
+      <c r="AG5">
+        <v>2.655</v>
+      </c>
+      <c r="AH5">
+        <v>0.09382004482869037</v>
+      </c>
+      <c r="AI5">
+        <v>0.09034844279987667</v>
+      </c>
+      <c r="AJ5">
+        <v>0.0857696656436763</v>
+      </c>
+      <c r="AK5">
+        <v>0.08256880733944955</v>
+      </c>
+      <c r="AL5">
+        <v>0.254</v>
+      </c>
+      <c r="AM5">
+        <v>0.254</v>
+      </c>
+      <c r="AN5">
+        <v>-0.1953333333333333</v>
+      </c>
+      <c r="AO5">
+        <v>-66.92913385826772</v>
+      </c>
+      <c r="AP5">
+        <v>-0.177</v>
+      </c>
+      <c r="AQ5">
+        <v>-66.92913385826772</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1347,49 @@
         <v>2.01538461538462</v>
       </c>
       <c r="F2">
-        <v>4.57064735676255</v>
+        <v>4.52451259633098</v>
       </c>
       <c r="G2">
         <v>4.87193894059074</v>
       </c>
       <c r="H2">
-        <v>3.18007944212367</v>
+        <v>3.36354556378465</v>
       </c>
       <c r="I2">
         <v>0.796649358990655</v>
       </c>
       <c r="J2">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="K2">
         <v>2564.3</v>
       </c>
       <c r="L2">
-        <v>7996.99891070457</v>
+        <v>8277.37102801551</v>
       </c>
       <c r="M2">
         <v>11705.2380954981</v>
       </c>
       <c r="N2">
-        <v>13649.3227203636</v>
+        <v>14308.0019805395</v>
       </c>
       <c r="O2">
         <v>10045.9380954981</v>
       </c>
       <c r="P2">
-        <v>6557.32380965901</v>
+        <v>6935.63095252396</v>
       </c>
       <c r="Q2">
-        <v>0.081932087293034</v>
+        <v>0.08191301899292459</v>
       </c>
       <c r="R2">
-        <v>0.0767857634196973</v>
+        <v>0.0753437117100182</v>
       </c>
       <c r="S2">
         <v>0.053925</v>
       </c>
       <c r="T2">
-        <v>0.043425</v>
+        <v>0.041475</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1402,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.191653050199492</v>
+        <v>0.191559279656086</v>
       </c>
       <c r="X2">
-        <v>0.112926590457703</v>
+        <v>0.11673880380004</v>
       </c>
       <c r="Y2">
         <v>3.3662651190782</v>
       </c>
       <c r="Z2">
-        <v>1.54927099372515</v>
+        <v>1.63830955658292</v>
       </c>
       <c r="AA2">
         <v>9028</v>
@@ -1224,7 +1444,7 @@
         <v>2564.3</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1632,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08283536025252555</v>
+        <v>0.08281154980871674</v>
       </c>
       <c r="C2">
-        <v>12324.75349418785</v>
+        <v>12326.06958082238</v>
       </c>
       <c r="D2">
-        <v>11419.75349418785</v>
+        <v>11421.06958082238</v>
       </c>
       <c r="E2">
         <v>-10045.9380954981</v>
@@ -1463,19 +1683,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08283536025252555</v>
+        <v>0.08281154980871674</v>
       </c>
       <c r="T2">
         <v>0.8547702034345667</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1714,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08267252185189425</v>
+        <v>0.08263827093419493</v>
       </c>
       <c r="C3">
-        <v>12249.08363862581</v>
+        <v>12253.68932179694</v>
       </c>
       <c r="D3">
-        <v>11470.18601958079</v>
+        <v>11474.79170275192</v>
       </c>
       <c r="E3">
         <v>-9919.835714543122</v>
@@ -1527,37 +1747,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M3">
-        <v>6.519493095372519</v>
+        <v>6.342949762035546</v>
       </c>
       <c r="N3">
-        <v>1728.813840237961</v>
+        <v>1728.990383571298</v>
       </c>
       <c r="O3">
-        <v>432.2034600594902</v>
+        <v>432.2475958928245</v>
       </c>
       <c r="P3">
-        <v>1296.610380178471</v>
+        <v>1296.742787678474</v>
       </c>
       <c r="Q3">
-        <v>2310.610380178471</v>
+        <v>2310.742787678474</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08311593116352954</v>
+        <v>0.08309194033757064</v>
       </c>
       <c r="T3">
         <v>0.8612457352787679</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1785,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>266.1761133798973</v>
+        <v>273.5845936727772</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1796,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08250968345126293</v>
+        <v>0.08246499205967316</v>
       </c>
       <c r="C4">
-        <v>12173.86120461594</v>
+        <v>12181.81684462562</v>
       </c>
       <c r="D4">
-        <v>11521.0659665259</v>
+        <v>11529.02160653558</v>
       </c>
       <c r="E4">
         <v>-9793.733333588141</v>
@@ -1609,37 +1829,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M4">
-        <v>13.03898619074504</v>
+        <v>12.68589952407109</v>
       </c>
       <c r="N4">
-        <v>1722.294347142589</v>
+        <v>1722.647433809262</v>
       </c>
       <c r="O4">
-        <v>430.5735867856471</v>
+        <v>430.6618584523156</v>
       </c>
       <c r="P4">
-        <v>1291.720760356941</v>
+        <v>1291.985575356947</v>
       </c>
       <c r="Q4">
-        <v>2305.720760356941</v>
+        <v>2305.985575356947</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08340222801149279</v>
+        <v>0.08337805312211546</v>
       </c>
       <c r="T4">
         <v>0.8678534208340754</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1867,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>133.0880566899487</v>
+        <v>136.7922968363886</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1878,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08234684505063163</v>
+        <v>0.08229171318515134</v>
       </c>
       <c r="C5">
-        <v>12099.09217276285</v>
+        <v>12110.45938283028</v>
       </c>
       <c r="D5">
-        <v>11572.39931562779</v>
+        <v>11583.76652569523</v>
       </c>
       <c r="E5">
         <v>-9667.630952633159</v>
@@ -1691,37 +1911,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M5">
-        <v>19.55847928611756</v>
+        <v>19.02884928610664</v>
       </c>
       <c r="N5">
-        <v>1715.774854047216</v>
+        <v>1716.304484047227</v>
       </c>
       <c r="O5">
-        <v>428.943713511804</v>
+        <v>429.0761210118067</v>
       </c>
       <c r="P5">
-        <v>1286.831140535412</v>
+        <v>1287.22836303542</v>
       </c>
       <c r="Q5">
-        <v>2300.831140535412</v>
+        <v>2301.22836303542</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.0836944278872491</v>
+        <v>0.08367006513933128</v>
       </c>
       <c r="T5">
         <v>0.8745973473286673</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1949,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.72537112663244</v>
+        <v>91.1948645575924</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1960,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08218400665000031</v>
+        <v>0.08211843431062957</v>
       </c>
       <c r="C6">
-        <v>12024.78263073711</v>
+        <v>12039.62430798018</v>
       </c>
       <c r="D6">
-        <v>11624.19215455703</v>
+        <v>11639.0338318001</v>
       </c>
       <c r="E6">
         <v>-9541.528571678178</v>
@@ -1773,37 +1993,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M6">
-        <v>26.07797238149008</v>
+        <v>25.37179904814218</v>
       </c>
       <c r="N6">
-        <v>1709.255360951843</v>
+        <v>1709.961534285191</v>
       </c>
       <c r="O6">
-        <v>427.3138402379608</v>
+        <v>427.4903835712978</v>
       </c>
       <c r="P6">
-        <v>1281.941520713882</v>
+        <v>1282.471150713893</v>
       </c>
       <c r="Q6">
-        <v>2295.941520713883</v>
+        <v>2296.471150713894</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08399271526041699</v>
+        <v>0.08396816074023913</v>
       </c>
       <c r="T6">
         <v>0.8814817722918968</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +2031,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.54402834497434</v>
+        <v>68.39614841819429</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +2042,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08202116824936899</v>
+        <v>0.08194515543610778</v>
       </c>
       <c r="C7">
-        <v>11950.93877568189</v>
+        <v>11969.31913300099</v>
       </c>
       <c r="D7">
-        <v>11676.45068045679</v>
+        <v>11694.83103777589</v>
       </c>
       <c r="E7">
         <v>-9415.426190723198</v>
@@ -1855,37 +2075,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M7">
-        <v>32.5974654768626</v>
+        <v>31.71474881017773</v>
       </c>
       <c r="N7">
-        <v>1702.735867856471</v>
+        <v>1703.618584523156</v>
       </c>
       <c r="O7">
-        <v>425.6839669641177</v>
+        <v>425.9046461307889</v>
       </c>
       <c r="P7">
-        <v>1277.051900892353</v>
+        <v>1277.713938392367</v>
       </c>
       <c r="Q7">
-        <v>2291.051900892353</v>
+        <v>2291.713938392367</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08429728236775683</v>
+        <v>0.08427253203800819</v>
       </c>
       <c r="T7">
         <v>0.8885111325175101</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2113,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>53.23522267597945</v>
+        <v>54.71691873455543</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2124,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08185832984873767</v>
+        <v>0.08177187656158598</v>
       </c>
       <c r="C8">
-        <v>11877.56691668486</v>
+        <v>11899.55151557937</v>
       </c>
       <c r="D8">
-        <v>11729.18120241475</v>
+        <v>11751.16580130926</v>
       </c>
       <c r="E8">
         <v>-9289.323809768217</v>
@@ -1937,37 +2157,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M8">
-        <v>39.11695857223512</v>
+        <v>38.05769857221328</v>
       </c>
       <c r="N8">
-        <v>1696.216374761098</v>
+        <v>1697.27563476112</v>
       </c>
       <c r="O8">
-        <v>424.0540936902746</v>
+        <v>424.3189086902801</v>
       </c>
       <c r="P8">
-        <v>1272.162281070824</v>
+        <v>1272.95672607084</v>
       </c>
       <c r="Q8">
-        <v>2286.162281070824</v>
+        <v>2286.95672607084</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08460832962631668</v>
+        <v>0.08458337932083615</v>
       </c>
       <c r="T8">
         <v>0.8956900535989873</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2195,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.36268556331622</v>
+        <v>45.5974322787962</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2206,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08169549144810635</v>
+        <v>0.08159859768706418</v>
       </c>
       <c r="C9">
-        <v>11804.67347731736</v>
+        <v>11830.32926166651</v>
       </c>
       <c r="D9">
-        <v>11782.39014400223</v>
+        <v>11808.04592835138</v>
       </c>
       <c r="E9">
         <v>-9163.221428813235</v>
@@ -2019,37 +2239,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M9">
-        <v>45.63645166760764</v>
+        <v>44.40064833424882</v>
       </c>
       <c r="N9">
-        <v>1689.696881665726</v>
+        <v>1690.932684999085</v>
       </c>
       <c r="O9">
-        <v>422.4242204164315</v>
+        <v>422.7331712497711</v>
       </c>
       <c r="P9">
-        <v>1267.272661249294</v>
+        <v>1268.199513749313</v>
       </c>
       <c r="Q9">
-        <v>2281.272661249294</v>
+        <v>2282.199513749313</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08492606607323264</v>
+        <v>0.08490091149146686</v>
       </c>
       <c r="T9">
         <v>0.9030233600800663</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2277,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.02515905427104</v>
+        <v>39.08351338182531</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2288,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08153265304747506</v>
+        <v>0.0814253188125424</v>
       </c>
       <c r="C10">
-        <v>11732.26499824294</v>
+        <v>11761.66032908381</v>
       </c>
       <c r="D10">
-        <v>11836.08404588279</v>
+        <v>11865.47937672366</v>
       </c>
       <c r="E10">
         <v>-9037.119047858254</v>
@@ -2101,37 +2321,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M10">
-        <v>52.15594476298016</v>
+        <v>50.74359809628437</v>
       </c>
       <c r="N10">
-        <v>1683.177388570353</v>
+        <v>1684.589735237049</v>
       </c>
       <c r="O10">
-        <v>420.7943471425883</v>
+        <v>421.1474338092623</v>
       </c>
       <c r="P10">
-        <v>1262.383041427765</v>
+        <v>1263.442301427787</v>
       </c>
       <c r="Q10">
-        <v>2276.383041427765</v>
+        <v>2277.442301427787</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08525070983421201</v>
+        <v>0.08522534653537217</v>
       </c>
       <c r="T10">
         <v>0.9105160862672559</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2359,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.27201417248717</v>
+        <v>34.19807420909715</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2370,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08136981464684374</v>
+        <v>0.08125203993802062</v>
       </c>
       <c r="C11">
-        <v>11660.34813989766</v>
+        <v>11693.55283123442</v>
       </c>
       <c r="D11">
-        <v>11890.26956849249</v>
+        <v>11923.47425982925</v>
       </c>
       <c r="E11">
         <v>-8911.016666903273</v>
@@ -2183,37 +2403,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M11">
-        <v>58.67543785835268</v>
+        <v>57.08654785831991</v>
       </c>
       <c r="N11">
-        <v>1676.657895474981</v>
+        <v>1678.246785475014</v>
       </c>
       <c r="O11">
-        <v>419.1644738687452</v>
+        <v>419.5616963687534</v>
       </c>
       <c r="P11">
-        <v>1257.493421606236</v>
+        <v>1258.68508910626</v>
       </c>
       <c r="Q11">
-        <v>2271.493421606236</v>
+        <v>2272.68508910626</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08558248862290521</v>
+        <v>0.08555691201980287</v>
       </c>
       <c r="T11">
         <v>0.9181734877552625</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2441,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.57512370887748</v>
+        <v>30.39828818586413</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2452,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08120697624621243</v>
+        <v>0.08107876106349882</v>
       </c>
       <c r="C12">
-        <v>11588.92968524422</v>
+        <v>11626.01504092405</v>
       </c>
       <c r="D12">
-        <v>11944.95349479403</v>
+        <v>11982.03885047386</v>
       </c>
       <c r="E12">
         <v>-8784.914285948293</v>
@@ -2265,37 +2485,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M12">
-        <v>65.1949309537252</v>
+        <v>63.42949762035546</v>
       </c>
       <c r="N12">
-        <v>1670.138402379608</v>
+        <v>1671.903835712978</v>
       </c>
       <c r="O12">
-        <v>417.5346005949021</v>
+        <v>417.9759589282445</v>
       </c>
       <c r="P12">
-        <v>1252.603801784706</v>
+        <v>1253.927876784734</v>
       </c>
       <c r="Q12">
-        <v>2266.603801784706</v>
+        <v>2267.927876784734</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08592164027356936</v>
+        <v>0.0858958456261098</v>
       </c>
       <c r="T12">
         <v>0.9260010537207805</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2523,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.61761133798973</v>
+        <v>27.35845936727771</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2534,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08104413784558111</v>
+        <v>0.08090548218897703</v>
       </c>
       <c r="C13">
-        <v>11518.01654260258</v>
+        <v>11559.055394295</v>
       </c>
       <c r="D13">
-        <v>12000.14273310737</v>
+        <v>12041.18158479979</v>
       </c>
       <c r="E13">
         <v>-8658.811904993312</v>
@@ -2347,37 +2567,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M13">
-        <v>71.71442404909772</v>
+        <v>69.77244738239099</v>
       </c>
       <c r="N13">
-        <v>1663.618909284236</v>
+        <v>1665.560885950943</v>
       </c>
       <c r="O13">
-        <v>415.9047273210589</v>
+        <v>416.3902214877356</v>
       </c>
       <c r="P13">
-        <v>1247.714181963177</v>
+        <v>1249.170664463207</v>
       </c>
       <c r="Q13">
-        <v>2261.714181963177</v>
+        <v>2263.170664463207</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08626841330964169</v>
+        <v>0.08624239571795173</v>
       </c>
       <c r="T13">
         <v>0.9340045200450743</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2605,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.19782848908157</v>
+        <v>24.8713266975252</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2616,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0808812994449498</v>
+        <v>0.08073220331445524</v>
       </c>
       <c r="C14">
-        <v>11447.61574855925</v>
+        <v>11492.68249487728</v>
       </c>
       <c r="D14">
-        <v>12055.84432001902</v>
+        <v>12100.91106633705</v>
       </c>
       <c r="E14">
         <v>-8532.70952403833</v>
@@ -2429,37 +2649,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M14">
-        <v>78.23391714447024</v>
+        <v>76.11539714442655</v>
       </c>
       <c r="N14">
-        <v>1657.099416188863</v>
+        <v>1659.217936188907</v>
       </c>
       <c r="O14">
-        <v>414.2748540472158</v>
+        <v>414.8044840472267</v>
       </c>
       <c r="P14">
-        <v>1242.824562141647</v>
+        <v>1244.41345214168</v>
       </c>
       <c r="Q14">
-        <v>2256.824562141647</v>
+        <v>2258.41345214168</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08662306755107932</v>
+        <v>0.08659682194824458</v>
       </c>
       <c r="T14">
         <v>0.9421898833312837</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2687,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.18134278165811</v>
+        <v>22.7987161393981</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2698,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08071846104431848</v>
+        <v>0.08055892443993344</v>
       </c>
       <c r="C15">
-        <v>11377.73447095818</v>
+        <v>11426.90511776086</v>
       </c>
       <c r="D15">
-        <v>12112.06542337293</v>
+        <v>12161.23607017561</v>
       </c>
       <c r="E15">
         <v>-8406.607143083349</v>
@@ -2511,37 +2731,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M15">
-        <v>84.75341023984276</v>
+        <v>82.4583469064621</v>
       </c>
       <c r="N15">
-        <v>1650.579923093491</v>
+        <v>1652.874986426871</v>
       </c>
       <c r="O15">
-        <v>412.6449807733727</v>
+        <v>413.2187466067178</v>
       </c>
       <c r="P15">
-        <v>1237.934942320118</v>
+        <v>1239.656239820154</v>
       </c>
       <c r="Q15">
-        <v>2251.934942320118</v>
+        <v>2253.656239820154</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08698587476358446</v>
+        <v>0.08695939590796947</v>
       </c>
       <c r="T15">
         <v>0.9505634158884405</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2769,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.47508564460749</v>
+        <v>21.04496874405978</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2780,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08055562264368717</v>
+        <v>0.08038564556541164</v>
       </c>
       <c r="C16">
-        <v>11308.38001197553</v>
+        <v>11361.73221389338</v>
       </c>
       <c r="D16">
-        <v>12168.81334534526</v>
+        <v>12222.16554726311</v>
       </c>
       <c r="E16">
         <v>-8280.504762128368</v>
@@ -2593,37 +2813,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M16">
-        <v>91.27290333521528</v>
+        <v>88.80129666849764</v>
       </c>
       <c r="N16">
-        <v>1644.060429998118</v>
+        <v>1646.532036664836</v>
       </c>
       <c r="O16">
-        <v>411.0151074995296</v>
+        <v>411.633009166209</v>
       </c>
       <c r="P16">
-        <v>1233.045322498589</v>
+        <v>1234.899027498627</v>
       </c>
       <c r="Q16">
-        <v>2247.045322498589</v>
+        <v>2248.899027498627</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08735711935312461</v>
+        <v>0.0873304018202461</v>
       </c>
       <c r="T16">
         <v>0.95913168176088</v>
       </c>
       <c r="U16">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2851,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.01257952713552</v>
+        <v>19.54175669091266</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2862,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08039278424305583</v>
+        <v>0.08021236669088985</v>
       </c>
       <c r="C17">
-        <v>11239.55981128145</v>
+        <v>11297.17291450766</v>
       </c>
       <c r="D17">
-        <v>12226.09552560617</v>
+        <v>12283.70862883237</v>
       </c>
       <c r="E17">
         <v>-8154.402381173388</v>
@@ -2675,37 +2895,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M17">
-        <v>97.79239643058779</v>
+        <v>95.14424643053319</v>
       </c>
       <c r="N17">
-        <v>1637.540936902746</v>
+        <v>1640.1890869028</v>
       </c>
       <c r="O17">
-        <v>409.3852342256864</v>
+        <v>410.0472717257001</v>
       </c>
       <c r="P17">
-        <v>1228.155702677059</v>
+        <v>1230.1418151771</v>
       </c>
       <c r="Q17">
-        <v>2242.155702677059</v>
+        <v>2244.1418151771</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08773709910947747</v>
+        <v>0.08771013728339982</v>
       </c>
       <c r="T17">
         <v>0.9679015538891417</v>
       </c>
       <c r="U17">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2933,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.74507422532649</v>
+        <v>18.23897291151848</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2944,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08022994584242454</v>
+        <v>0.08003908781636807</v>
       </c>
       <c r="C18">
-        <v>11171.28144929144</v>
+        <v>11233.23653568373</v>
       </c>
       <c r="D18">
-        <v>12283.91954457113</v>
+        <v>12345.87463096342</v>
       </c>
       <c r="E18">
         <v>-8028.300000218406</v>
@@ -2757,37 +2977,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M18">
-        <v>104.3118895259603</v>
+        <v>101.4871961925687</v>
       </c>
       <c r="N18">
-        <v>1631.021443807373</v>
+        <v>1633.846137140765</v>
       </c>
       <c r="O18">
-        <v>407.7553609518433</v>
+        <v>408.4615342851912</v>
       </c>
       <c r="P18">
-        <v>1223.26608285553</v>
+        <v>1225.384602855574</v>
       </c>
       <c r="Q18">
-        <v>2237.26608285553</v>
+        <v>2239.384602855574</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08812612600288636</v>
+        <v>0.08809891406710484</v>
       </c>
       <c r="T18">
         <v>0.9768802324966476</v>
       </c>
       <c r="U18">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +3015,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.63600708624358</v>
+        <v>17.09903710454858</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +3026,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08006710744179324</v>
+        <v>0.07986580894184628</v>
       </c>
       <c r="C19">
-        <v>11103.55265051054</v>
+        <v>11169.93258305001</v>
       </c>
       <c r="D19">
-        <v>12342.29312674521</v>
+        <v>12408.67305928469</v>
       </c>
       <c r="E19">
         <v>-7902.197619263425</v>
@@ -2839,37 +3059,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M19">
-        <v>110.8313826213328</v>
+        <v>107.8301459546043</v>
       </c>
       <c r="N19">
-        <v>1624.501950712001</v>
+        <v>1627.503187378729</v>
       </c>
       <c r="O19">
-        <v>406.1254876780002</v>
+        <v>406.8757968446823</v>
       </c>
       <c r="P19">
-        <v>1218.376463034001</v>
+        <v>1220.627390534047</v>
       </c>
       <c r="Q19">
-        <v>2232.376463034001</v>
+        <v>2234.627390534047</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.0885245270383051</v>
+        <v>0.08849705896607986</v>
       </c>
       <c r="T19">
         <v>0.9860752648055394</v>
       </c>
       <c r="U19">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +3097,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.65741843411161</v>
+        <v>16.09321139251631</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3108,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07990426904116191</v>
+        <v>0.07969253006732449</v>
       </c>
       <c r="C20">
-        <v>11036.38128697324</v>
+        <v>11107.27075662874</v>
       </c>
       <c r="D20">
-        <v>12401.2241441629</v>
+        <v>12472.1136138184</v>
       </c>
       <c r="E20">
         <v>-7776.095238308444</v>
@@ -2921,37 +3141,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M20">
-        <v>117.3508757167054</v>
+        <v>114.1730957166398</v>
       </c>
       <c r="N20">
-        <v>1617.982457616628</v>
+        <v>1621.160237616694</v>
       </c>
       <c r="O20">
-        <v>404.495614404157</v>
+        <v>405.2900594041734</v>
       </c>
       <c r="P20">
-        <v>1213.486843212471</v>
+        <v>1215.87017821252</v>
       </c>
       <c r="Q20">
-        <v>2227.486843212471</v>
+        <v>2229.87017821252</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08893264517214866</v>
+        <v>0.08890491471624937</v>
       </c>
       <c r="T20">
         <v>0.9954945661951355</v>
       </c>
       <c r="U20">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +3179,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.78756185443874</v>
+        <v>15.19914409293207</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3190,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07974143064053062</v>
+        <v>0.0795192511928027</v>
       </c>
       <c r="C21">
-        <v>10969.77538178243</v>
+        <v>11045.26095583081</v>
       </c>
       <c r="D21">
-        <v>12460.72061992707</v>
+        <v>12536.20619397545</v>
       </c>
       <c r="E21">
         <v>-7649.992857353463</v>
@@ -3003,37 +3223,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M21">
-        <v>123.8703688120779</v>
+        <v>120.5160454786754</v>
       </c>
       <c r="N21">
-        <v>1611.462964521256</v>
+        <v>1614.817287854658</v>
       </c>
       <c r="O21">
-        <v>402.8657411303139</v>
+        <v>403.7043219636645</v>
       </c>
       <c r="P21">
-        <v>1208.597223390942</v>
+        <v>1211.112965890994</v>
       </c>
       <c r="Q21">
-        <v>2222.597223390942</v>
+        <v>2225.112965890994</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.08935084029695137</v>
+        <v>0.08932284097876876</v>
       </c>
       <c r="T21">
         <v>1.005146442927685</v>
       </c>
       <c r="U21">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3261,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.00926912525775</v>
+        <v>14.39918914067248</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3272,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.0795785922398993</v>
+        <v>0.0793459723182809</v>
       </c>
       <c r="C22">
-        <v>10903.74311275076</v>
+        <v>10983.91328460536</v>
       </c>
       <c r="D22">
-        <v>12520.79073185038</v>
+        <v>12600.96090370498</v>
       </c>
       <c r="E22">
         <v>-7523.890476398482</v>
@@ -3085,37 +3305,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M22">
-        <v>130.3898619074504</v>
+        <v>126.8589952407109</v>
       </c>
       <c r="N22">
-        <v>1604.943471425883</v>
+        <v>1608.474338092622</v>
       </c>
       <c r="O22">
-        <v>401.2358678564707</v>
+        <v>402.1185845231556</v>
       </c>
       <c r="P22">
-        <v>1203.707603569412</v>
+        <v>1206.355753569467</v>
       </c>
       <c r="Q22">
-        <v>2217.707603569412</v>
+        <v>2220.355753569467</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.08977949029987412</v>
+        <v>0.08975121539785114</v>
       </c>
       <c r="T22">
         <v>1.015039616578548</v>
       </c>
       <c r="U22">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.038775</v>
+        <v>0.037725</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3343,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.30880566899486</v>
+        <v>13.67922968363886</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3354,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07958900383926798</v>
+        <v>0.07917269344375912</v>
       </c>
       <c r="C23">
-        <v>10773.78262880171</v>
+        <v>10923.23805674987</v>
       </c>
       <c r="D23">
-        <v>12516.93262885631</v>
+        <v>12666.38805680447</v>
       </c>
       <c r="E23">
         <v>-7397.788095443501</v>
@@ -3167,45 +3387,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M23">
-        <v>139.8223200028829</v>
+        <v>133.2019450027464</v>
       </c>
       <c r="N23">
-        <v>1595.511013330451</v>
+        <v>1602.131388330587</v>
       </c>
       <c r="O23">
-        <v>398.8777533326127</v>
+        <v>400.5328470826468</v>
       </c>
       <c r="P23">
-        <v>1196.633259997838</v>
+        <v>1201.59854124794</v>
       </c>
       <c r="Q23">
-        <v>2210.633259997838</v>
+        <v>2215.59854124794</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09021899220160502</v>
+        <v>0.09019043473893558</v>
       </c>
       <c r="T23">
         <v>1.025183250321838</v>
       </c>
       <c r="U23">
-        <v>0.05280000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.0396</v>
+        <v>0.037725</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.4109894135468</v>
+        <v>13.02783779394177</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3436,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07943441543863665</v>
+        <v>0.07924691456923731</v>
       </c>
       <c r="C24">
-        <v>10705.20979223364</v>
+        <v>10769.02804346385</v>
       </c>
       <c r="D24">
-        <v>12574.46217324323</v>
+        <v>12638.28042447344</v>
       </c>
       <c r="E24">
         <v>-7271.68571448852</v>
@@ -3249,37 +3469,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M24">
-        <v>146.480525717306</v>
+        <v>143.7062733362964</v>
       </c>
       <c r="N24">
-        <v>1588.852807616028</v>
+        <v>1591.627059997037</v>
       </c>
       <c r="O24">
-        <v>397.2132019040069</v>
+        <v>397.9067649992593</v>
       </c>
       <c r="P24">
-        <v>1191.639605712021</v>
+        <v>1193.720294997778</v>
       </c>
       <c r="Q24">
-        <v>2205.639605712021</v>
+        <v>2207.720294997778</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.0906697633828675</v>
+        <v>0.09064091611440681</v>
       </c>
       <c r="T24">
         <v>1.035586977238033</v>
       </c>
       <c r="U24">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.0396</v>
+        <v>0.03885</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3507,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.84685353111285</v>
+        <v>12.07555726723473</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3518,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07927982703800535</v>
+        <v>0.07908488569471553</v>
       </c>
       <c r="C25">
-        <v>10637.16822485317</v>
+        <v>10704.44807156414</v>
       </c>
       <c r="D25">
-        <v>12632.52298681774</v>
+        <v>12699.8028335287</v>
       </c>
       <c r="E25">
         <v>-7145.583333533539</v>
@@ -3331,37 +3551,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M25">
-        <v>153.138731431729</v>
+        <v>150.2383766697644</v>
       </c>
       <c r="N25">
-        <v>1582.194601901605</v>
+        <v>1585.094956663569</v>
       </c>
       <c r="O25">
-        <v>395.5486504754011</v>
+        <v>396.2737391658923</v>
       </c>
       <c r="P25">
-        <v>1186.645951426203</v>
+        <v>1188.821217497677</v>
       </c>
       <c r="Q25">
-        <v>2200.645951426203</v>
+        <v>2202.821217497677</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09113224290650043</v>
+        <v>0.09110309830482535</v>
       </c>
       <c r="T25">
         <v>1.046260930827375</v>
       </c>
       <c r="U25">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.0396</v>
+        <v>0.03885</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3589,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.3317729428036</v>
+        <v>11.55053303822452</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3600,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07912523863737403</v>
+        <v>0.07892285682019375</v>
       </c>
       <c r="C26">
-        <v>10569.66531998057</v>
+        <v>10640.47000467227</v>
       </c>
       <c r="D26">
-        <v>12691.12246290012</v>
+        <v>12761.92714759182</v>
       </c>
       <c r="E26">
         <v>-7019.480952578559</v>
@@ -3413,37 +3633,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M26">
-        <v>159.796937146152</v>
+        <v>156.7704800032324</v>
       </c>
       <c r="N26">
-        <v>1575.536396187181</v>
+        <v>1578.562853330101</v>
       </c>
       <c r="O26">
-        <v>393.8840990467954</v>
+        <v>394.6407133325253</v>
       </c>
       <c r="P26">
-        <v>1181.652297140386</v>
+        <v>1183.922139997576</v>
       </c>
       <c r="Q26">
-        <v>2195.652297140386</v>
+        <v>2197.922139997576</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09160689294391319</v>
+        <v>0.09157744318446545</v>
       </c>
       <c r="T26">
         <v>1.057215777932227</v>
       </c>
       <c r="U26">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.0396</v>
+        <v>0.03885</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3671,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.85961573685345</v>
+        <v>11.0692608282985</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3682,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07897065023674273</v>
+        <v>0.07876082794567194</v>
       </c>
       <c r="C27">
-        <v>10502.70860875933</v>
+        <v>10577.10271932417</v>
       </c>
       <c r="D27">
-        <v>12750.26813263386</v>
+        <v>12824.66224319869</v>
       </c>
       <c r="E27">
         <v>-6893.378571623577</v>
@@ -3495,37 +3715,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M27">
-        <v>166.455142860575</v>
+        <v>163.3025833367004</v>
       </c>
       <c r="N27">
-        <v>1568.878190472758</v>
+        <v>1572.030749996633</v>
       </c>
       <c r="O27">
-        <v>392.2195476181896</v>
+        <v>393.0076874991582</v>
       </c>
       <c r="P27">
-        <v>1176.658642854569</v>
+        <v>1179.023062497475</v>
       </c>
       <c r="Q27">
-        <v>2190.658642854569</v>
+        <v>2193.023062497475</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09209420031565696</v>
+        <v>0.09206443726089591</v>
       </c>
       <c r="T27">
         <v>1.068462754293208</v>
       </c>
       <c r="U27">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.0396</v>
+        <v>0.03885</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3753,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.42523110737931</v>
+        <v>10.62649039516656</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3764,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07881606183611141</v>
+        <v>0.07859879907115015</v>
       </c>
       <c r="C28">
-        <v>10436.30576338277</v>
+        <v>10514.35526745912</v>
       </c>
       <c r="D28">
-        <v>12809.96766821228</v>
+        <v>12888.01717228862</v>
       </c>
       <c r="E28">
         <v>-6767.276190668596</v>
@@ -3577,37 +3797,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M28">
-        <v>173.113348574998</v>
+        <v>169.8346866701685</v>
       </c>
       <c r="N28">
-        <v>1562.219984758336</v>
+        <v>1565.498646663165</v>
       </c>
       <c r="O28">
-        <v>390.5549961895839</v>
+        <v>391.3746616657913</v>
       </c>
       <c r="P28">
-        <v>1171.664988568752</v>
+        <v>1174.123984997374</v>
       </c>
       <c r="Q28">
-        <v>2185.664988568752</v>
+        <v>2188.123984997374</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09259467815690731</v>
+        <v>0.0925645933393921</v>
       </c>
       <c r="T28">
         <v>1.08001370298827</v>
       </c>
       <c r="U28">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.0396</v>
+        <v>0.03885</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3835,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.02426068017242</v>
+        <v>10.21777922612169</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3846,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07910697343548009</v>
+        <v>0.07843677019662836</v>
       </c>
       <c r="C29">
-        <v>10198.31785823149</v>
+        <v>10452.23688077386</v>
       </c>
       <c r="D29">
-        <v>12698.08214401598</v>
+        <v>12952.00116655835</v>
       </c>
       <c r="E29">
         <v>-6641.173809713615</v>
@@ -3659,45 +3879,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M29">
-        <v>187.2620357181468</v>
+        <v>176.3667900036365</v>
       </c>
       <c r="N29">
-        <v>1548.071297615187</v>
+        <v>1558.966543329697</v>
       </c>
       <c r="O29">
-        <v>387.0178244037967</v>
+        <v>389.7416358324243</v>
       </c>
       <c r="P29">
-        <v>1161.05347321139</v>
+        <v>1169.224907497273</v>
       </c>
       <c r="Q29">
-        <v>2175.05347321139</v>
+        <v>2183.224907497273</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09310886771983573</v>
+        <v>0.09307845232414844</v>
       </c>
       <c r="T29">
         <v>1.091881116031142</v>
       </c>
       <c r="U29">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04125000000000001</v>
+        <v>0.03885</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.266872095448276</v>
+        <v>9.839342958487553</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3928,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07896888503484878</v>
+        <v>0.07863174132210657</v>
       </c>
       <c r="C30">
-        <v>10125.08001741737</v>
+        <v>10249.2191080989</v>
       </c>
       <c r="D30">
-        <v>12750.94668415684</v>
+        <v>12875.08577483837</v>
       </c>
       <c r="E30">
         <v>-6515.071428758634</v>
@@ -3741,37 +3961,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M30">
-        <v>194.1976666706708</v>
+        <v>188.9013666705616</v>
       </c>
       <c r="N30">
-        <v>1541.135666662663</v>
+        <v>1546.431966662772</v>
       </c>
       <c r="O30">
-        <v>385.2839166656657</v>
+        <v>386.607991665693</v>
       </c>
       <c r="P30">
-        <v>1155.851749996997</v>
+        <v>1159.823974997079</v>
       </c>
       <c r="Q30">
-        <v>2169.851749996997</v>
+        <v>2173.823974997079</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09363734032617885</v>
+        <v>0.09360658516959244</v>
       </c>
       <c r="T30">
         <v>1.104078179436315</v>
       </c>
       <c r="U30">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04125000000000001</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3999,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.935912377753695</v>
+        <v>9.186451977129966</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +4010,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07883079663421745</v>
+        <v>0.07848246244758476</v>
       </c>
       <c r="C31">
-        <v>10052.28418712325</v>
+        <v>10181.92436187836</v>
       </c>
       <c r="D31">
-        <v>12804.2532348177</v>
+        <v>12933.89340957281</v>
       </c>
       <c r="E31">
         <v>-6388.969047803654</v>
@@ -3823,37 +4043,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M31">
-        <v>201.1332976231947</v>
+        <v>195.6478440516531</v>
       </c>
       <c r="N31">
-        <v>1534.200035710139</v>
+        <v>1539.68548928168</v>
       </c>
       <c r="O31">
-        <v>383.5500089275347</v>
+        <v>384.9213723204201</v>
       </c>
       <c r="P31">
-        <v>1150.650026782604</v>
+        <v>1154.76411696126</v>
       </c>
       <c r="Q31">
-        <v>2164.650026782604</v>
+        <v>2168.76411696126</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09418069948481331</v>
+        <v>0.09414959499659827</v>
       </c>
       <c r="T31">
         <v>1.116618822092339</v>
       </c>
       <c r="U31">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04125000000000001</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +4081,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.627777468175982</v>
+        <v>8.869677771022038</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +4092,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07869270823358614</v>
+        <v>0.07833318357306297</v>
       </c>
       <c r="C32">
-        <v>9979.935934223588</v>
+        <v>10115.16929462939</v>
       </c>
       <c r="D32">
-        <v>12858.00736287302</v>
+        <v>12993.24072327882</v>
       </c>
       <c r="E32">
         <v>-6262.866666848672</v>
@@ -3905,37 +4125,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M32">
-        <v>208.0689285757187</v>
+        <v>202.3943214327445</v>
       </c>
       <c r="N32">
-        <v>1527.264404757615</v>
+        <v>1532.939011900589</v>
       </c>
       <c r="O32">
-        <v>381.8161011894037</v>
+        <v>383.2347529751472</v>
       </c>
       <c r="P32">
-        <v>1145.448303568211</v>
+        <v>1149.704258925442</v>
       </c>
       <c r="Q32">
-        <v>2159.448303568211</v>
+        <v>2163.704258925442</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09473958319083735</v>
+        <v>0.09470811939008997</v>
       </c>
       <c r="T32">
         <v>1.129517768824249</v>
       </c>
       <c r="U32">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04125000000000001</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4163,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.340184885903451</v>
+        <v>8.574021845321305</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4174,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.07855461983295484</v>
+        <v>0.07818390469854118</v>
       </c>
       <c r="C33">
-        <v>9908.040919469149</v>
+        <v>10048.96136956592</v>
       </c>
       <c r="D33">
-        <v>12912.21472907356</v>
+        <v>13053.13517917033</v>
       </c>
       <c r="E33">
         <v>-6136.764285893691</v>
@@ -3987,37 +4207,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M33">
-        <v>215.0045595282427</v>
+        <v>209.140798813836</v>
       </c>
       <c r="N33">
-        <v>1520.328773805091</v>
+        <v>1526.192534519497</v>
       </c>
       <c r="O33">
-        <v>380.0821934512727</v>
+        <v>381.5481336298744</v>
       </c>
       <c r="P33">
-        <v>1140.246580353818</v>
+        <v>1144.644400889623</v>
       </c>
       <c r="Q33">
-        <v>2154.246580353818</v>
+        <v>2158.644400889623</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09531466642457222</v>
+        <v>0.09528283289643651</v>
       </c>
       <c r="T33">
         <v>1.142790598070127</v>
       </c>
       <c r="U33">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04125000000000001</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4245,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.071146663777533</v>
+        <v>8.29744049547223</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4256,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07841653143232352</v>
+        <v>0.0780346258240194</v>
       </c>
       <c r="C34">
-        <v>9836.60489947427</v>
+        <v>9983.308188150746</v>
       </c>
       <c r="D34">
-        <v>12966.88109003366</v>
+        <v>13113.58437871014</v>
       </c>
       <c r="E34">
         <v>-6010.66190493871</v>
@@ -4069,37 +4289,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M34">
-        <v>221.9401904807666</v>
+        <v>215.8872761949275</v>
       </c>
       <c r="N34">
-        <v>1513.393142852567</v>
+        <v>1519.446057138406</v>
       </c>
       <c r="O34">
-        <v>378.3482857131417</v>
+        <v>379.8615142846015</v>
       </c>
       <c r="P34">
-        <v>1135.044857139425</v>
+        <v>1139.584542853804</v>
       </c>
       <c r="Q34">
-        <v>2149.044857139425</v>
+        <v>2153.584542853804</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.095906663871064</v>
+        <v>0.095874449741205</v>
       </c>
       <c r="T34">
         <v>1.156453804646767</v>
       </c>
       <c r="U34">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04125000000000001</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4327,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.818923330534484</v>
+        <v>8.038145479988721</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4338,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0786496930316922</v>
+        <v>0.07788534694949761</v>
       </c>
       <c r="C35">
-        <v>9618.465776171081</v>
+        <v>9918.2174933116</v>
       </c>
       <c r="D35">
-        <v>12874.84434768545</v>
+        <v>13174.59606482597</v>
       </c>
       <c r="E35">
         <v>-5884.559523983728</v>
@@ -4151,45 +4371,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M35">
-        <v>235.1178892905622</v>
+        <v>222.633753576019</v>
       </c>
       <c r="N35">
-        <v>1500.215444042771</v>
+        <v>1512.699579757314</v>
       </c>
       <c r="O35">
-        <v>375.0538610106928</v>
+        <v>378.1748949393286</v>
       </c>
       <c r="P35">
-        <v>1125.161583032078</v>
+        <v>1134.524684817986</v>
       </c>
       <c r="Q35">
-        <v>2139.161583032078</v>
+        <v>2148.524684817986</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.0965163328831227</v>
+        <v>0.09648372679029493</v>
       </c>
       <c r="T35">
         <v>1.170524868136142</v>
       </c>
       <c r="U35">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04237500000000001</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.380694589295087</v>
+        <v>7.794565313928457</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4420,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07852285463106089</v>
+        <v>0.0779400680749758</v>
       </c>
       <c r="C36">
-        <v>9542.268108110169</v>
+        <v>9769.684272362563</v>
       </c>
       <c r="D36">
-        <v>12924.74906057952</v>
+        <v>13152.16522483192</v>
       </c>
       <c r="E36">
         <v>-5758.457143028748</v>
@@ -4233,37 +4453,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M36">
-        <v>242.2426738145186</v>
+        <v>232.810215719086</v>
       </c>
       <c r="N36">
-        <v>1493.090659518815</v>
+        <v>1502.523117614247</v>
       </c>
       <c r="O36">
-        <v>373.2726648797037</v>
+        <v>375.6307794035619</v>
       </c>
       <c r="P36">
-        <v>1119.817994639111</v>
+        <v>1126.892338210685</v>
       </c>
       <c r="Q36">
-        <v>2133.817994639111</v>
+        <v>2140.892338210685</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09714447671372863</v>
+        <v>0.09711146678026639</v>
       </c>
       <c r="T36">
         <v>1.185022327488831</v>
       </c>
       <c r="U36">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04237500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4491,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.163615336668761</v>
+        <v>7.453853895428822</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4502,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07839601623042958</v>
+        <v>0.07779678920045402</v>
       </c>
       <c r="C37">
-        <v>9466.458820882221</v>
+        <v>9702.47615792704</v>
       </c>
       <c r="D37">
-        <v>12975.04215430656</v>
+        <v>13211.05949135138</v>
       </c>
       <c r="E37">
         <v>-5632.354762073766</v>
@@ -4315,37 +4535,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M37">
-        <v>249.367458338475</v>
+        <v>239.6575750049415</v>
       </c>
       <c r="N37">
-        <v>1485.965874994858</v>
+        <v>1495.675758328392</v>
       </c>
       <c r="O37">
-        <v>371.4914687487146</v>
+        <v>373.918939582098</v>
       </c>
       <c r="P37">
-        <v>1114.474406246144</v>
+        <v>1121.756818746294</v>
       </c>
       <c r="Q37">
-        <v>2128.474406246144</v>
+        <v>2135.756818746294</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09779194804681474</v>
+        <v>0.09775852184685234</v>
       </c>
       <c r="T37">
         <v>1.199965862513911</v>
       </c>
       <c r="U37">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04237500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4573,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.958940612763939</v>
+        <v>7.240886641273712</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4584,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.07826917782979827</v>
+        <v>0.07765351032593223</v>
       </c>
       <c r="C38">
-        <v>9391.042466028761</v>
+        <v>9635.797862914016</v>
       </c>
       <c r="D38">
-        <v>13025.72818040808</v>
+        <v>13270.48357729333</v>
       </c>
       <c r="E38">
         <v>-5506.252381118786</v>
@@ -4397,37 +4617,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M38">
-        <v>256.4922428624315</v>
+        <v>246.5049342907969</v>
       </c>
       <c r="N38">
-        <v>1478.841090470902</v>
+        <v>1488.828399042537</v>
       </c>
       <c r="O38">
-        <v>369.7102726177255</v>
+        <v>372.2070997606342</v>
       </c>
       <c r="P38">
-        <v>1109.130817853177</v>
+        <v>1116.621299281902</v>
       </c>
       <c r="Q38">
-        <v>2123.130817853177</v>
+        <v>2130.621299281902</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09845965285905978</v>
+        <v>0.0984257973842691</v>
       </c>
       <c r="T38">
         <v>1.215376383008524</v>
       </c>
       <c r="U38">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04237500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4655,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.76563670685383</v>
+        <v>7.039750901238332</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4666,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07814233942916696</v>
+        <v>0.07751023145141045</v>
       </c>
       <c r="C39">
-        <v>9316.023666491245</v>
+        <v>9569.656569099881</v>
       </c>
       <c r="D39">
-        <v>13076.81176182554</v>
+        <v>13330.44466443418</v>
       </c>
       <c r="E39">
         <v>-5380.150000163805</v>
@@ -4479,37 +4699,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M39">
-        <v>263.6170273863879</v>
+        <v>253.3522935766524</v>
       </c>
       <c r="N39">
-        <v>1471.716305946946</v>
+        <v>1481.981039756681</v>
       </c>
       <c r="O39">
-        <v>367.9290764867364</v>
+        <v>370.4952599391703</v>
       </c>
       <c r="P39">
-        <v>1103.787229460209</v>
+        <v>1111.485779817511</v>
       </c>
       <c r="Q39">
-        <v>2117.787229460209</v>
+        <v>2125.485779817511</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09914855464947134</v>
+        <v>0.09911425627208006</v>
       </c>
       <c r="T39">
         <v>1.231276126375983</v>
       </c>
       <c r="U39">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04237500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4737,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.582781660722645</v>
+        <v>6.849487363367026</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4748,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07801550102853563</v>
+        <v>0.07736695257688865</v>
       </c>
       <c r="C40">
-        <v>9241.407118016647</v>
+        <v>9504.059588650161</v>
       </c>
       <c r="D40">
-        <v>13128.29759430593</v>
+        <v>13390.95006493944</v>
       </c>
       <c r="E40">
         <v>-5254.047619208824</v>
@@ -4561,37 +4781,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M40">
-        <v>270.7418119103443</v>
+        <v>260.1996528625079</v>
       </c>
       <c r="N40">
-        <v>1464.591521422989</v>
+        <v>1475.133680470826</v>
       </c>
       <c r="O40">
-        <v>366.1478803557473</v>
+        <v>368.7834201177064</v>
       </c>
       <c r="P40">
-        <v>1098.443641067242</v>
+        <v>1106.350260353119</v>
       </c>
       <c r="Q40">
-        <v>2112.443641067242</v>
+        <v>2120.350260353119</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.09985967907828328</v>
+        <v>0.09982492351111072</v>
       </c>
       <c r="T40">
         <v>1.247688764690779</v>
       </c>
       <c r="U40">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04237500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4819,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.409550564387839</v>
+        <v>6.669237695909998</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4830,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07788866262790431</v>
+        <v>0.07722367370236685</v>
       </c>
       <c r="C41">
-        <v>9167.197590596355</v>
+        <v>9439.014367092099</v>
       </c>
       <c r="D41">
-        <v>13180.19044784061</v>
+        <v>13452.00722433636</v>
       </c>
       <c r="E41">
         <v>-5127.945238253843</v>
@@ -4643,37 +4863,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M41">
-        <v>277.8665964343007</v>
+        <v>267.0470121483633</v>
       </c>
       <c r="N41">
-        <v>1457.466736899033</v>
+        <v>1468.28632118497</v>
       </c>
       <c r="O41">
-        <v>364.3666842247582</v>
+        <v>367.0715802962425</v>
       </c>
       <c r="P41">
-        <v>1093.100052674275</v>
+        <v>1101.214740888728</v>
       </c>
       <c r="Q41">
-        <v>2107.100052674275</v>
+        <v>2115.214740888728</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1005941190621382</v>
+        <v>0.1005588913153555</v>
       </c>
       <c r="T41">
         <v>1.264639522294584</v>
       </c>
       <c r="U41">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04237500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4901,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.24520311401892</v>
+        <v>6.498231601143076</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4912,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.078181824227273</v>
+        <v>0.07708039482784505</v>
       </c>
       <c r="C42">
-        <v>8921.77130483126</v>
+        <v>9374.528486368958</v>
       </c>
       <c r="D42">
-        <v>13060.8665430305</v>
+        <v>13513.6237245682</v>
       </c>
       <c r="E42">
         <v>-5001.842857298861</v>
@@ -4725,45 +4945,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M42">
-        <v>292.0531142917361</v>
+        <v>273.8943714342188</v>
       </c>
       <c r="N42">
-        <v>1443.280219041597</v>
+        <v>1461.438961899115</v>
       </c>
       <c r="O42">
-        <v>360.8200547603993</v>
+        <v>365.3597404747787</v>
       </c>
       <c r="P42">
-        <v>1082.460164281198</v>
+        <v>1096.079221424336</v>
       </c>
       <c r="Q42">
-        <v>2096.460164281198</v>
+        <v>2110.079221424336</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1013530403787883</v>
+        <v>0.1013173247130751</v>
       </c>
       <c r="T42">
         <v>1.28215530515185</v>
       </c>
       <c r="U42">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04342500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>5.941841563791317</v>
+        <v>6.335775811114498</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4994,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.07806548582664169</v>
+        <v>0.07693711595332327</v>
       </c>
       <c r="C43">
-        <v>8842.761979677118</v>
+        <v>9310.609667978653</v>
       </c>
       <c r="D43">
-        <v>13107.95959883134</v>
+        <v>13575.80728713287</v>
       </c>
       <c r="E43">
         <v>-4875.740476343881</v>
@@ -4807,45 +5027,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M43">
-        <v>299.3544421490295</v>
+        <v>280.7417307200743</v>
       </c>
       <c r="N43">
-        <v>1435.978891184304</v>
+        <v>1454.591602613259</v>
       </c>
       <c r="O43">
-        <v>358.994722796076</v>
+        <v>363.6479006533148</v>
       </c>
       <c r="P43">
-        <v>1076.984168388228</v>
+        <v>1090.943701959945</v>
       </c>
       <c r="Q43">
-        <v>2090.984168388228</v>
+        <v>2104.943701959945</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1021376878417656</v>
+        <v>0.1021014677174971</v>
       </c>
       <c r="T43">
         <v>1.30026484336021</v>
       </c>
       <c r="U43">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.04342500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y43">
-        <v>5.796918598820798</v>
+        <v>6.181244693770243</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +5076,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07794914742601038</v>
+        <v>0.07710883707880149</v>
       </c>
       <c r="C44">
-        <v>8764.093486627797</v>
+        <v>9110.047386109612</v>
       </c>
       <c r="D44">
-        <v>13155.393486737</v>
+        <v>13501.34738621881</v>
       </c>
       <c r="E44">
         <v>-4749.6380953889</v>
@@ -4889,37 +5109,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M44">
-        <v>306.6557700063228</v>
+        <v>292.885390006039</v>
       </c>
       <c r="N44">
-        <v>1428.677563327011</v>
+        <v>1442.447943327295</v>
       </c>
       <c r="O44">
-        <v>357.1693908317527</v>
+        <v>360.6119858318236</v>
       </c>
       <c r="P44">
-        <v>1071.508172495258</v>
+        <v>1081.835957495471</v>
       </c>
       <c r="Q44">
-        <v>2085.508172495258</v>
+        <v>2095.835957495471</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.102949392113811</v>
+        <v>0.1029126501358646</v>
       </c>
       <c r="T44">
         <v>1.31899884840334</v>
       </c>
       <c r="U44">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5147,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.658896727420303</v>
+        <v>5.924956971385813</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5158,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07783280902537906</v>
+        <v>0.07697305820427969</v>
       </c>
       <c r="C45">
-        <v>8685.769539237914</v>
+        <v>9042.752124450264</v>
       </c>
       <c r="D45">
-        <v>13203.1719203021</v>
+        <v>13560.15450551445</v>
       </c>
       <c r="E45">
         <v>-4623.535714433919</v>
@@ -4971,37 +5191,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M45">
-        <v>313.9570978636163</v>
+        <v>299.8588516728494</v>
       </c>
       <c r="N45">
-        <v>1421.376235469717</v>
+        <v>1435.474481660484</v>
       </c>
       <c r="O45">
-        <v>355.3440588674293</v>
+        <v>358.868620415121</v>
       </c>
       <c r="P45">
-        <v>1066.032176602288</v>
+        <v>1076.605861245363</v>
       </c>
       <c r="Q45">
-        <v>2080.032176602288</v>
+        <v>2090.605861245363</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1037895772375071</v>
+        <v>0.1037522950952275</v>
       </c>
       <c r="T45">
         <v>1.338390186956756</v>
       </c>
       <c r="U45">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5229,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.527294477945412</v>
+        <v>5.787167274376841</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5240,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07771647062474776</v>
+        <v>0.0768372793297579</v>
       </c>
       <c r="C46">
-        <v>8607.793905207043</v>
+        <v>8975.971390136361</v>
       </c>
       <c r="D46">
-        <v>13251.29866722621</v>
+        <v>13619.47615215552</v>
       </c>
       <c r="E46">
         <v>-4497.433333478938</v>
@@ -5053,37 +5273,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M46">
-        <v>321.2584257209097</v>
+        <v>306.8323133396598</v>
       </c>
       <c r="N46">
-        <v>1414.074907612424</v>
+        <v>1428.501019993674</v>
       </c>
       <c r="O46">
-        <v>353.518726903106</v>
+        <v>357.1252549984184</v>
       </c>
       <c r="P46">
-        <v>1060.556180709318</v>
+        <v>1071.375764995255</v>
       </c>
       <c r="Q46">
-        <v>2074.556180709318</v>
+        <v>2085.375764995255</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1046597689727638</v>
+        <v>0.1046219273745677</v>
       </c>
       <c r="T46">
         <v>1.358474073315651</v>
       </c>
       <c r="U46">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5311,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.401674148901199</v>
+        <v>5.655640745413732</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5322,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07760013222411644</v>
+        <v>0.07670150045523612</v>
       </c>
       <c r="C47">
-        <v>8530.170407370166</v>
+        <v>8909.711965551562</v>
       </c>
       <c r="D47">
-        <v>13299.77755034431</v>
+        <v>13679.31910852571</v>
       </c>
       <c r="E47">
         <v>-4371.330952523957</v>
@@ -5135,37 +5355,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M47">
-        <v>328.5597535782031</v>
+        <v>313.8057750064703</v>
       </c>
       <c r="N47">
-        <v>1406.77357975513</v>
+        <v>1421.527558326863</v>
       </c>
       <c r="O47">
-        <v>351.6933949387826</v>
+        <v>355.3818895817158</v>
       </c>
       <c r="P47">
-        <v>1055.080184816348</v>
+        <v>1066.145668745147</v>
       </c>
       <c r="Q47">
-        <v>2069.080184816348</v>
+        <v>2080.145668745147</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1055616040438481</v>
+        <v>0.1055231826458838</v>
       </c>
       <c r="T47">
         <v>1.379288282814869</v>
       </c>
       <c r="U47">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5393,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.281636945592282</v>
+        <v>5.529959839960092</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5404,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07748379382348514</v>
+        <v>0.07656572158071431</v>
       </c>
       <c r="C48">
-        <v>8452.902924709852</v>
+        <v>8843.98075281077</v>
       </c>
       <c r="D48">
-        <v>13348.61244863898</v>
+        <v>13739.6902767399</v>
       </c>
       <c r="E48">
         <v>-4245.228571568975</v>
@@ -5217,37 +5437,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M48">
-        <v>335.8610814354965</v>
+        <v>320.7792366732808</v>
       </c>
       <c r="N48">
-        <v>1399.472251897837</v>
+        <v>1414.554096660053</v>
       </c>
       <c r="O48">
-        <v>349.8680629744592</v>
+        <v>353.6385241650132</v>
       </c>
       <c r="P48">
-        <v>1049.604188923378</v>
+        <v>1060.915572495039</v>
       </c>
       <c r="Q48">
-        <v>2063.604188923377</v>
+        <v>2074.91557249504</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1064968404138613</v>
+        <v>0.1064578177420635</v>
       </c>
       <c r="T48">
         <v>1.400873388962206</v>
       </c>
       <c r="U48">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5475,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.166818751122884</v>
+        <v>5.40974332170009</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5486,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07736745542285381</v>
+        <v>0.07642994270619252</v>
       </c>
       <c r="C49">
-        <v>8375.995393390986</v>
+        <v>8778.784776413857</v>
       </c>
       <c r="D49">
-        <v>13397.80729827509</v>
+        <v>13800.59668129796</v>
       </c>
       <c r="E49">
         <v>-4119.126190613994</v>
@@ -5299,37 +5519,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M49">
-        <v>343.1624092927899</v>
+        <v>327.7526983400912</v>
       </c>
       <c r="N49">
-        <v>1392.170924040543</v>
+        <v>1407.580634993242</v>
       </c>
       <c r="O49">
-        <v>348.0427310101359</v>
+        <v>351.8951587483106</v>
       </c>
       <c r="P49">
-        <v>1044.128193030408</v>
+        <v>1055.685476244932</v>
       </c>
       <c r="Q49">
-        <v>2058.128193030408</v>
+        <v>2069.685476244932</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1074673687223657</v>
+        <v>0.1074277220871557</v>
       </c>
       <c r="T49">
         <v>1.423273027416991</v>
       </c>
       <c r="U49">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5557,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.056886437269206</v>
+        <v>5.29464239996179</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5568,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07725111702222251</v>
+        <v>0.07629416383167073</v>
       </c>
       <c r="C50">
-        <v>8299.451807818263</v>
+        <v>8714.131185970378</v>
       </c>
       <c r="D50">
-        <v>13447.36609365735</v>
+        <v>13862.04547180947</v>
       </c>
       <c r="E50">
         <v>-3993.023809659014</v>
@@ -5381,37 +5601,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M50">
-        <v>350.4637371500833</v>
+        <v>334.7261600069016</v>
       </c>
       <c r="N50">
-        <v>1384.86959618325</v>
+        <v>1400.607173326432</v>
       </c>
       <c r="O50">
-        <v>346.2173990458126</v>
+        <v>350.151793331608</v>
       </c>
       <c r="P50">
-        <v>1038.652197137438</v>
+        <v>1050.455379994824</v>
       </c>
       <c r="Q50">
-        <v>2052.652197137438</v>
+        <v>2064.455379994824</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1084752250427356</v>
+        <v>0.1084349304455206</v>
       </c>
       <c r="T50">
         <v>1.446534190427728</v>
       </c>
       <c r="U50">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5639,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.951534636492765</v>
+        <v>5.184337349962587</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5650,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07713477862159117</v>
+        <v>0.07615838495714893</v>
       </c>
       <c r="C51">
-        <v>8223.276221717424</v>
+        <v>8650.027258997357</v>
       </c>
       <c r="D51">
-        <v>13497.29288851149</v>
+        <v>13924.04392579143</v>
       </c>
       <c r="E51">
         <v>-3866.921428704033</v>
@@ -5463,37 +5683,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M51">
-        <v>357.7650650073767</v>
+        <v>341.6996216737121</v>
       </c>
       <c r="N51">
-        <v>1377.568268325957</v>
+        <v>1393.633711659621</v>
       </c>
       <c r="O51">
-        <v>344.3920670814892</v>
+        <v>348.4084279149054</v>
       </c>
       <c r="P51">
-        <v>1033.176201244468</v>
+        <v>1045.225283744716</v>
       </c>
       <c r="Q51">
-        <v>2047.176201244468</v>
+        <v>2059.225283744716</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1095226051403748</v>
+        <v>0.1094816371708802</v>
       </c>
       <c r="T51">
         <v>1.470707555909475</v>
       </c>
       <c r="U51">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5721,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.850482909217402</v>
+        <v>5.078534546902127</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5732,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07701844022095988</v>
+        <v>0.07602260608262715</v>
       </c>
       <c r="C52">
-        <v>8147.472749240491</v>
+        <v>8586.480403792437</v>
       </c>
       <c r="D52">
-        <v>13547.59179698954</v>
+        <v>13986.59945154149</v>
       </c>
       <c r="E52">
         <v>-3740.819047749052</v>
@@ -5545,37 +5765,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M52">
-        <v>365.0663928646701</v>
+        <v>348.6730833405226</v>
       </c>
       <c r="N52">
-        <v>1370.266940468664</v>
+        <v>1386.660249992811</v>
       </c>
       <c r="O52">
-        <v>342.5667351171659</v>
+        <v>346.6650624982027</v>
       </c>
       <c r="P52">
-        <v>1027.700205351498</v>
+        <v>1039.995187494608</v>
       </c>
       <c r="Q52">
-        <v>2041.700205351498</v>
+        <v>2053.995187494608</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1106118804419197</v>
+        <v>0.1105702121652543</v>
       </c>
       <c r="T52">
         <v>1.495847856010492</v>
       </c>
       <c r="U52">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5803,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.753473251033054</v>
+        <v>4.976963855964083</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5814,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.07690210182032856</v>
+        <v>0.07588682720810536</v>
       </c>
       <c r="C53">
-        <v>8072.045566096022</v>
+        <v>8523.498162384964</v>
       </c>
       <c r="D53">
-        <v>13598.26699480005</v>
+        <v>14049.719591089</v>
       </c>
       <c r="E53">
         <v>-3614.71666679407</v>
@@ -5627,37 +5847,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M53">
-        <v>372.3677207219635</v>
+        <v>355.646545007333</v>
       </c>
       <c r="N53">
-        <v>1362.96561261137</v>
+        <v>1379.686788326</v>
       </c>
       <c r="O53">
-        <v>340.7414031528425</v>
+        <v>344.9216970815001</v>
       </c>
       <c r="P53">
-        <v>1022.224209458528</v>
+        <v>1034.7650912445</v>
       </c>
       <c r="Q53">
-        <v>2036.224209458528</v>
+        <v>2048.765091244501</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1117456159598542</v>
+        <v>0.1117032187920518</v>
       </c>
       <c r="T53">
         <v>1.522014290809509</v>
       </c>
       <c r="U53">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5885,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.660267893169661</v>
+        <v>4.879376329376552</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5896,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.07678576341969726</v>
+        <v>0.07575104833358356</v>
       </c>
       <c r="C54">
-        <v>7996.998910704567</v>
+        <v>8461.088213567185</v>
       </c>
       <c r="D54">
-        <v>13649.32272036358</v>
+        <v>14113.4120232262</v>
       </c>
       <c r="E54">
         <v>-3488.614285839089</v>
@@ -5709,37 +5929,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M54">
-        <v>379.6690485792569</v>
+        <v>362.6200066741435</v>
       </c>
       <c r="N54">
-        <v>1355.664284754077</v>
+        <v>1372.71332665919</v>
       </c>
       <c r="O54">
-        <v>338.9160711885191</v>
+        <v>343.1783316647975</v>
       </c>
       <c r="P54">
-        <v>1016.748213565557</v>
+        <v>1029.534994994392</v>
       </c>
       <c r="Q54">
-        <v>2030.748213565557</v>
+        <v>2043.534994994392</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1129265904577026</v>
+        <v>0.1128834340282991</v>
       </c>
       <c r="T54">
         <v>1.549270993725152</v>
       </c>
       <c r="U54">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.04342500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5967,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.570647356762551</v>
+        <v>4.785542169196233</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5978,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07770292501906592</v>
+        <v>0.07561526945906177</v>
       </c>
       <c r="C55">
-        <v>7478.498821732959</v>
+        <v>8399.258376008371</v>
       </c>
       <c r="D55">
-        <v>13256.92501234695</v>
+        <v>14177.68456662237</v>
       </c>
       <c r="E55">
         <v>-3362.511904884108</v>
@@ -5791,45 +6011,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M55">
-        <v>404.3472845321467</v>
+        <v>369.593468340954</v>
       </c>
       <c r="N55">
-        <v>1330.986048801187</v>
+        <v>1365.73986499238</v>
       </c>
       <c r="O55">
-        <v>332.7465122002967</v>
+        <v>341.4349662480949</v>
       </c>
       <c r="P55">
-        <v>998.2395366008901</v>
+        <v>1024.304898744285</v>
       </c>
       <c r="Q55">
-        <v>2012.23953660089</v>
+        <v>2038.304898744285</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.114157819189502</v>
+        <v>0.1141138711894931</v>
       </c>
       <c r="T55">
         <v>1.577687556339333</v>
       </c>
       <c r="U55">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V55">
         <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.04537500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.291690335799373</v>
+        <v>4.695248920720833</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +6060,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.07760608661843461</v>
+        <v>0.07547949058453997</v>
       </c>
       <c r="C56">
-        <v>7392.759137103554</v>
+        <v>8338.016611454397</v>
       </c>
       <c r="D56">
-        <v>13297.28770867253</v>
+        <v>14242.54518302337</v>
       </c>
       <c r="E56">
         <v>-3236.409523929127</v>
@@ -5873,45 +6093,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M56">
-        <v>411.976478579923</v>
+        <v>376.5669300077644</v>
       </c>
       <c r="N56">
-        <v>1323.356854753411</v>
+        <v>1358.766403325569</v>
       </c>
       <c r="O56">
-        <v>330.8392136883526</v>
+        <v>339.6916008313923</v>
       </c>
       <c r="P56">
-        <v>992.5176410650579</v>
+        <v>1019.074802494177</v>
       </c>
       <c r="Q56">
-        <v>2006.517641065058</v>
+        <v>2033.074802494177</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1154425796052926</v>
+        <v>0.1153978056185652</v>
       </c>
       <c r="T56">
         <v>1.60733962167587</v>
       </c>
       <c r="U56">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04537500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.212214588840126</v>
+        <v>4.608299866633411</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6142,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.07750924821780331</v>
+        <v>0.07534371171001819</v>
       </c>
       <c r="C57">
-        <v>7307.265983639475</v>
+        <v>8277.37102801551</v>
       </c>
       <c r="D57">
-        <v>13337.89693616343</v>
+        <v>14308.00198053947</v>
       </c>
       <c r="E57">
         <v>-3110.307142974146</v>
@@ -5955,45 +6175,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M57">
-        <v>419.6056726276994</v>
+        <v>383.5403916745749</v>
       </c>
       <c r="N57">
-        <v>1315.727660705634</v>
+        <v>1351.792941658759</v>
       </c>
       <c r="O57">
-        <v>328.9319151764086</v>
+        <v>337.9482354146896</v>
       </c>
       <c r="P57">
-        <v>986.7957455292257</v>
+        <v>1013.844706244069</v>
       </c>
       <c r="Q57">
-        <v>2000.795745529226</v>
+        <v>2027.844706244069</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1167844404840074</v>
+        <v>0.1167388038000404</v>
       </c>
       <c r="T57">
         <v>1.63830955658292</v>
       </c>
       <c r="U57">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.04537500000000001</v>
+        <v>0.041475</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.135628869043034</v>
+        <v>4.524512596330984</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6224,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07741240981717198</v>
+        <v>0.07625793283549639</v>
       </c>
       <c r="C58">
-        <v>7222.021626939951</v>
+        <v>7721.801626280031</v>
       </c>
       <c r="D58">
-        <v>13378.75496041889</v>
+        <v>13878.53495975897</v>
       </c>
       <c r="E58">
         <v>-2984.204762019165</v>
@@ -6037,37 +6257,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M58">
-        <v>427.2348666754758</v>
+        <v>408.1681866750826</v>
       </c>
       <c r="N58">
-        <v>1308.098466657858</v>
+        <v>1327.165146658251</v>
       </c>
       <c r="O58">
-        <v>327.0246166644644</v>
+        <v>331.7912866645627</v>
       </c>
       <c r="P58">
-        <v>981.0738499933932</v>
+        <v>995.3738599936883</v>
       </c>
       <c r="Q58">
-        <v>1995.073849993393</v>
+        <v>2009.373859993688</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1181872950390272</v>
+        <v>0.11814075644431</v>
       </c>
       <c r="T58">
         <v>1.670687215803926</v>
       </c>
       <c r="U58">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.04537500000000001</v>
+        <v>0.04335</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6295,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.061778353524407</v>
+        <v>4.2515154046406</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6306,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07846982141654066</v>
+        <v>0.0761409039609746</v>
       </c>
       <c r="C59">
-        <v>6662.894207375619</v>
+        <v>7649.230587978551</v>
       </c>
       <c r="D59">
-        <v>12945.72992180954</v>
+        <v>13932.06630241247</v>
       </c>
       <c r="E59">
         <v>-2858.102381064184</v>
@@ -6119,45 +6339,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M59">
-        <v>454.2712171522237</v>
+        <v>415.4569042942805</v>
       </c>
       <c r="N59">
-        <v>1281.06211618111</v>
+        <v>1319.876429039053</v>
       </c>
       <c r="O59">
-        <v>320.2655290452774</v>
+        <v>329.9691072597632</v>
       </c>
       <c r="P59">
-        <v>960.7965871358324</v>
+        <v>989.9073217792898</v>
       </c>
       <c r="Q59">
-        <v>1974.796587135832</v>
+        <v>2003.90732177929</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1196553986431178</v>
+        <v>0.119607916188313</v>
       </c>
       <c r="T59">
         <v>1.704570812663118</v>
       </c>
       <c r="U59">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V59">
         <v>0.25</v>
       </c>
       <c r="W59">
-        <v>0.0474</v>
+        <v>0.04335</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.820038047340854</v>
+        <v>4.176927415085501</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6388,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07839323301590936</v>
+        <v>0.07602387508645281</v>
       </c>
       <c r="C60">
-        <v>6567.212028958759</v>
+        <v>7577.074103586158</v>
       </c>
       <c r="D60">
-        <v>12976.15012434766</v>
+        <v>13986.01219897506</v>
       </c>
       <c r="E60">
         <v>-2732.000000109204</v>
@@ -6201,45 +6421,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M60">
-        <v>462.2408876285784</v>
+        <v>422.7456219134784</v>
       </c>
       <c r="N60">
-        <v>1273.092445704755</v>
+        <v>1312.587711419855</v>
       </c>
       <c r="O60">
-        <v>318.2731114261887</v>
+        <v>328.1469278549638</v>
       </c>
       <c r="P60">
-        <v>954.8193342785662</v>
+        <v>984.4407835648914</v>
       </c>
       <c r="Q60">
-        <v>1968.819334278566</v>
+        <v>1998.440783564891</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1211934119426413</v>
+        <v>0.1211449406820305</v>
       </c>
       <c r="T60">
         <v>1.740067914134654</v>
       </c>
       <c r="U60">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.0474</v>
+        <v>0.04335</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.754175322386701</v>
+        <v>4.104911425170235</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6470,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07831664461527804</v>
+        <v>0.07590684621193101</v>
       </c>
       <c r="C61">
-        <v>6471.673151591991</v>
+        <v>7505.337007363176</v>
       </c>
       <c r="D61">
-        <v>13006.71362793587</v>
+        <v>14040.37748370706</v>
       </c>
       <c r="E61">
         <v>-2605.897619154222</v>
@@ -6283,45 +6503,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M61">
-        <v>470.2105581049333</v>
+        <v>430.0343395326763</v>
       </c>
       <c r="N61">
-        <v>1265.1227752284</v>
+        <v>1305.298993800657</v>
       </c>
       <c r="O61">
-        <v>316.2806938071001</v>
+        <v>326.3247484501643</v>
       </c>
       <c r="P61">
-        <v>948.8420814213002</v>
+        <v>978.9742453504929</v>
       </c>
       <c r="Q61">
-        <v>1962.8420814213</v>
+        <v>1992.974245350493</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1228064502811659</v>
+        <v>0.1227569419803196</v>
       </c>
       <c r="T61">
         <v>1.777296581531629</v>
       </c>
       <c r="U61">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.0474</v>
+        <v>0.04335</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.690545232176757</v>
+        <v>4.035336655252094</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6552,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07824005621464672</v>
+        <v>0.07736481733740923</v>
       </c>
       <c r="C62">
-        <v>6376.278590242558</v>
+        <v>6730.71305432868</v>
       </c>
       <c r="D62">
-        <v>13037.42144754142</v>
+        <v>13391.85591162754</v>
       </c>
       <c r="E62">
         <v>-2479.795238199242</v>
@@ -6365,37 +6585,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M62">
-        <v>478.180228581288</v>
+        <v>463.8045571524202</v>
       </c>
       <c r="N62">
-        <v>1257.153104752045</v>
+        <v>1271.528776180913</v>
       </c>
       <c r="O62">
-        <v>314.2882761880114</v>
+        <v>317.8821940452283</v>
       </c>
       <c r="P62">
-        <v>942.864828564034</v>
+        <v>953.6465821356849</v>
       </c>
       <c r="Q62">
-        <v>1956.864828564034</v>
+        <v>1967.646582135685</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1245001405366168</v>
+        <v>0.1244495433435231</v>
       </c>
       <c r="T62">
         <v>1.816386682298454</v>
       </c>
       <c r="U62">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.0474</v>
+        <v>0.045975</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6623,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.629036144973811</v>
+        <v>3.741518505095348</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6634,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07816346781401542</v>
+        <v>0.07727403846288744</v>
       </c>
       <c r="C63">
-        <v>6281.029369485413</v>
+        <v>6643.2360823389</v>
       </c>
       <c r="D63">
-        <v>13068.27460773925</v>
+        <v>13430.48132059274</v>
       </c>
       <c r="E63">
         <v>-2353.69285724426</v>
@@ -6447,37 +6667,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M63">
-        <v>486.1498990576429</v>
+        <v>471.5346331049606</v>
       </c>
       <c r="N63">
-        <v>1249.183434275691</v>
+        <v>1263.798700228373</v>
       </c>
       <c r="O63">
-        <v>312.2958585689227</v>
+        <v>315.9496750570933</v>
       </c>
       <c r="P63">
-        <v>936.887575706768</v>
+        <v>947.8490251712798</v>
       </c>
       <c r="Q63">
-        <v>1950.887575706768</v>
+        <v>1961.84902517128</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1262806867026036</v>
+        <v>0.1262289447766345</v>
       </c>
       <c r="T63">
         <v>1.857481403617424</v>
       </c>
       <c r="U63">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.0474</v>
+        <v>0.045975</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6705,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.569543749154569</v>
+        <v>3.68018213615936</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6716,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.0780868794133841</v>
+        <v>0.07718325958836564</v>
       </c>
       <c r="C64">
-        <v>6185.92652361721</v>
+        <v>6555.982565222827</v>
       </c>
       <c r="D64">
-        <v>13099.27414282603</v>
+        <v>13469.33018443165</v>
       </c>
       <c r="E64">
         <v>-2227.59047628928</v>
@@ -6529,37 +6749,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M64">
-        <v>494.1195695339977</v>
+        <v>479.2647090575009</v>
       </c>
       <c r="N64">
-        <v>1241.213763799336</v>
+        <v>1256.068624275832</v>
       </c>
       <c r="O64">
-        <v>310.3034409498339</v>
+        <v>314.0171560689581</v>
       </c>
       <c r="P64">
-        <v>930.9103228495019</v>
+        <v>942.0514682068743</v>
       </c>
       <c r="Q64">
-        <v>1944.910322849502</v>
+        <v>1956.051468206874</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.128154945824695</v>
+        <v>0.1281019989167517</v>
       </c>
       <c r="T64">
         <v>1.900739005005813</v>
       </c>
       <c r="U64">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V64">
         <v>0.25</v>
       </c>
       <c r="W64">
-        <v>0.0474</v>
+        <v>0.045975</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6787,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.511970462877882</v>
+        <v>3.620824359769692</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6798,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.08023104101275279</v>
+        <v>0.07709248071384385</v>
       </c>
       <c r="C65">
-        <v>5244.078821855699</v>
+        <v>6468.954447695101</v>
       </c>
       <c r="D65">
-        <v>12283.5288220195</v>
+        <v>13508.40444785891</v>
       </c>
       <c r="E65">
         <v>-2101.488095334298</v>
@@ -6611,45 +6831,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M65">
-        <v>539.4281550111225</v>
+        <v>486.9947850100413</v>
       </c>
       <c r="N65">
-        <v>1195.905178322211</v>
+        <v>1248.338548323292</v>
       </c>
       <c r="O65">
-        <v>298.9762945805527</v>
+        <v>312.0846370808231</v>
       </c>
       <c r="P65">
-        <v>896.9288837416582</v>
+        <v>936.2539112424693</v>
       </c>
       <c r="Q65">
-        <v>1910.928883741658</v>
+        <v>1950.253911242469</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1301305162506832</v>
+        <v>0.130076299226605</v>
       </c>
       <c r="T65">
         <v>1.946334855117898</v>
       </c>
       <c r="U65">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V65">
         <v>0.25</v>
       </c>
       <c r="W65">
-        <v>0.05092500000000001</v>
+        <v>0.045975</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.216986946663087</v>
+        <v>3.563350957233665</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6880,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.08018970261212148</v>
+        <v>0.07700170183932206</v>
       </c>
       <c r="C66">
-        <v>5132.741949091878</v>
+        <v>6382.153697102356</v>
       </c>
       <c r="D66">
-        <v>12298.29433021066</v>
+        <v>13547.70607822114</v>
       </c>
       <c r="E66">
         <v>-1975.385714379318</v>
@@ -6693,45 +6913,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M66">
-        <v>547.9905066779656</v>
+        <v>494.7248609625816</v>
       </c>
       <c r="N66">
-        <v>1187.342826655368</v>
+        <v>1240.608472370752</v>
       </c>
       <c r="O66">
-        <v>296.835706663842</v>
+        <v>310.1521180926879</v>
       </c>
       <c r="P66">
-        <v>890.5071199915259</v>
+        <v>930.4563542780638</v>
       </c>
       <c r="Q66">
-        <v>1904.507119991526</v>
+        <v>1944.456354278064</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1322158405892263</v>
+        <v>0.1321602828870057</v>
       </c>
       <c r="T66">
         <v>1.994463808013989</v>
       </c>
       <c r="U66">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.05092500000000001</v>
+        <v>0.045975</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.166721525621477</v>
+        <v>3.507673598526889</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6962,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.08014836421149016</v>
+        <v>0.07827592296480028</v>
       </c>
       <c r="C67">
-        <v>5021.440617030345</v>
+        <v>5724.495267521763</v>
       </c>
       <c r="D67">
-        <v>12313.09537910411</v>
+        <v>13016.15002959553</v>
       </c>
       <c r="E67">
         <v>-1849.283333424337</v>
@@ -6775,37 +6995,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M67">
-        <v>556.5528583448088</v>
+        <v>525.4055702489284</v>
       </c>
       <c r="N67">
-        <v>1178.780474988525</v>
+        <v>1209.927763084405</v>
       </c>
       <c r="O67">
-        <v>294.6951187471312</v>
+        <v>302.4819407711013</v>
       </c>
       <c r="P67">
-        <v>884.0853562413936</v>
+        <v>907.4458223133038</v>
       </c>
       <c r="Q67">
-        <v>1898.085356241394</v>
+        <v>1921.445822313304</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1344203263185433</v>
+        <v>0.1343633513280008</v>
       </c>
       <c r="T67">
         <v>2.045342986789856</v>
       </c>
       <c r="U67">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.05092500000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +7033,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.118002732919608</v>
+        <v>3.302845328630912</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +7044,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.08010702581085885</v>
+        <v>0.07820614409027848</v>
       </c>
       <c r="C68">
-        <v>4910.174954145856</v>
+        <v>5626.420050092986</v>
       </c>
       <c r="D68">
-        <v>12327.9320971746</v>
+        <v>13044.17719312173</v>
       </c>
       <c r="E68">
         <v>-1723.180952469354</v>
@@ -6857,37 +7077,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M68">
-        <v>565.1152100116522</v>
+        <v>533.4887328681427</v>
       </c>
       <c r="N68">
-        <v>1170.218123321681</v>
+        <v>1201.844600465191</v>
       </c>
       <c r="O68">
-        <v>292.5545308304203</v>
+        <v>300.4611501162977</v>
       </c>
       <c r="P68">
-        <v>877.6635924912609</v>
+        <v>901.3834503488931</v>
       </c>
       <c r="Q68">
-        <v>1891.663592491261</v>
+        <v>1915.383450348893</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1367544876789966</v>
+        <v>0.1366960120302308</v>
       </c>
       <c r="T68">
         <v>2.099215058434892</v>
       </c>
       <c r="U68">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V68">
         <v>0.25</v>
       </c>
       <c r="W68">
-        <v>0.05092500000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +7115,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.070760267269311</v>
+        <v>3.252802217591049</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7126,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.08006568741022754</v>
+        <v>0.07813636521575669</v>
       </c>
       <c r="C69">
-        <v>4798.94508953317</v>
+        <v>5528.465792698764</v>
       </c>
       <c r="D69">
-        <v>12342.8046135169</v>
+        <v>13072.32531668249</v>
       </c>
       <c r="E69">
         <v>-1597.078571514374</v>
@@ -6939,37 +7159,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M69">
-        <v>573.6775616784953</v>
+        <v>541.5718954873571</v>
       </c>
       <c r="N69">
-        <v>1161.655771654838</v>
+        <v>1193.761437845976</v>
       </c>
       <c r="O69">
-        <v>290.4139429137095</v>
+        <v>298.4403594614941</v>
       </c>
       <c r="P69">
-        <v>871.2418287411286</v>
+        <v>895.3210783844822</v>
       </c>
       <c r="Q69">
-        <v>1885.241828741129</v>
+        <v>1909.321078384482</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1392301133643259</v>
+        <v>0.1391700461083536</v>
       </c>
       <c r="T69">
         <v>2.156352104119021</v>
       </c>
       <c r="U69">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.25</v>
       </c>
       <c r="W69">
-        <v>0.05092500000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +7197,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.024928024474247</v>
+        <v>3.204252930761331</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7208,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.08476734900959622</v>
+        <v>0.07806658634123489</v>
       </c>
       <c r="C70">
-        <v>3183.603846945805</v>
+        <v>5430.633280094102</v>
       </c>
       <c r="D70">
-        <v>10853.56575188451</v>
+        <v>13100.59518503281</v>
       </c>
       <c r="E70">
         <v>-1470.976190559393</v>
@@ -7021,45 +7241,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M70">
-        <v>661.9870590612684</v>
+        <v>549.6550581065713</v>
       </c>
       <c r="N70">
-        <v>1073.346274272065</v>
+        <v>1185.678275226762</v>
       </c>
       <c r="O70">
-        <v>268.3365685680163</v>
+        <v>296.4195688066906</v>
       </c>
       <c r="P70">
-        <v>805.0097057040489</v>
+        <v>889.2587064200717</v>
       </c>
       <c r="Q70">
-        <v>1819.009705704049</v>
+        <v>1903.258706420072</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1418604656549882</v>
+        <v>0.141798707316359</v>
       </c>
       <c r="T70">
         <v>2.217060215158408</v>
       </c>
       <c r="U70">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V70">
         <v>0.25</v>
       </c>
       <c r="W70">
-        <v>0.05790000000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.621400689907935</v>
+        <v>3.157131564132489</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7290,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0847957606089649</v>
+        <v>0.0779968074667131</v>
       </c>
       <c r="C71">
-        <v>3049.593756100088</v>
+        <v>5332.923303837077</v>
       </c>
       <c r="D71">
-        <v>10845.65804199378</v>
+        <v>13128.98758973077</v>
       </c>
       <c r="E71">
         <v>-1344.873809604411</v>
@@ -7103,45 +7323,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M71">
-        <v>671.7221628709931</v>
+        <v>557.7382207257857</v>
       </c>
       <c r="N71">
-        <v>1063.61117046234</v>
+        <v>1177.595112607548</v>
       </c>
       <c r="O71">
-        <v>265.9027926155851</v>
+        <v>294.398778151887</v>
       </c>
       <c r="P71">
-        <v>797.7083778467553</v>
+        <v>883.1963344556609</v>
       </c>
       <c r="Q71">
-        <v>1811.708377846755</v>
+        <v>1897.196334455661</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1446605180934352</v>
+        <v>0.1445969595700423</v>
       </c>
       <c r="T71">
         <v>2.281684978522916</v>
       </c>
       <c r="U71">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.05790000000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.583409375561442</v>
+        <v>3.111376034217525</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7372,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08482417220833359</v>
+        <v>0.07792702859219131</v>
       </c>
       <c r="C72">
-        <v>2915.595179691329</v>
+        <v>5235.336662362739</v>
       </c>
       <c r="D72">
-        <v>10837.76184654</v>
+        <v>13157.50332921141</v>
       </c>
       <c r="E72">
         <v>-1218.77142864943</v>
@@ -7185,45 +7405,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M72">
-        <v>681.4572666807176</v>
+        <v>565.821383345</v>
       </c>
       <c r="N72">
-        <v>1053.876066652616</v>
+        <v>1169.511949988334</v>
       </c>
       <c r="O72">
-        <v>263.469016663154</v>
+        <v>292.3779874970834</v>
       </c>
       <c r="P72">
-        <v>790.4070499894619</v>
+        <v>877.1339624912501</v>
       </c>
       <c r="Q72">
-        <v>1804.407049989462</v>
+        <v>1891.13396249125</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1476472406944453</v>
+        <v>0.147581761973971</v>
       </c>
       <c r="T72">
         <v>2.350618059445059</v>
       </c>
       <c r="U72">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V72">
         <v>0.25</v>
       </c>
       <c r="W72">
-        <v>0.05790000000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>2.546503527339136</v>
+        <v>3.066927805157274</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7454,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.08485258380770228</v>
+        <v>0.07785724971766952</v>
       </c>
       <c r="C73">
-        <v>2781.608092588524</v>
+        <v>5137.874161057913</v>
       </c>
       <c r="D73">
-        <v>10829.87714039217</v>
+        <v>13186.14320886156</v>
       </c>
       <c r="E73">
         <v>-1092.669047694451</v>
@@ -7267,45 +7487,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M73">
-        <v>691.1923704904419</v>
+        <v>573.9045459642141</v>
       </c>
       <c r="N73">
-        <v>1044.140962842891</v>
+        <v>1161.428787369119</v>
       </c>
       <c r="O73">
-        <v>261.0352407107229</v>
+        <v>290.3571968422798</v>
       </c>
       <c r="P73">
-        <v>783.1057221321686</v>
+        <v>871.0715905268396</v>
       </c>
       <c r="Q73">
-        <v>1797.105722132168</v>
+        <v>1885.07159052684</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1508399441644906</v>
+        <v>0.1507724128195501</v>
       </c>
       <c r="T73">
         <v>2.424305145948038</v>
       </c>
       <c r="U73">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.05790000000000001</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.510637280475205</v>
+        <v>3.023731638887454</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7536,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.08741899540707096</v>
+        <v>0.08199947084314772</v>
       </c>
       <c r="C74">
-        <v>1987.687518498631</v>
+        <v>3502.912128535223</v>
       </c>
       <c r="D74">
-        <v>10162.05894725726</v>
+        <v>11677.28355729386</v>
       </c>
       <c r="E74">
         <v>-966.5666667394689</v>
@@ -7349,45 +7569,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M74">
-        <v>743.6005200153321</v>
+        <v>652.8068057277458</v>
       </c>
       <c r="N74">
-        <v>991.7328133180014</v>
+        <v>1082.526527605588</v>
       </c>
       <c r="O74">
-        <v>247.9332033295003</v>
+        <v>270.6316319013969</v>
       </c>
       <c r="P74">
-        <v>743.7996099885011</v>
+        <v>811.8948957041907</v>
       </c>
       <c r="Q74">
-        <v>1757.799609988501</v>
+        <v>1825.894895704191</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1542606978823963</v>
+        <v>0.1541909672969561</v>
       </c>
       <c r="T74">
         <v>2.503255595772659</v>
       </c>
       <c r="U74">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.25</v>
       </c>
       <c r="W74">
-        <v>0.061425</v>
+        <v>0.053925</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.333690317077176</v>
+        <v>2.658264770078175</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7618,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.08748265700643965</v>
+        <v>0.08198819196862593</v>
       </c>
       <c r="C75">
-        <v>1846.06470358088</v>
+        <v>3380.449239050618</v>
       </c>
       <c r="D75">
-        <v>10146.53851329449</v>
+        <v>11680.92304876423</v>
       </c>
       <c r="E75">
         <v>-840.4642857844883</v>
@@ -7431,45 +7651,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M75">
-        <v>753.928305015545</v>
+        <v>661.8735669184089</v>
       </c>
       <c r="N75">
-        <v>981.4050283177885</v>
+        <v>1073.459766414925</v>
       </c>
       <c r="O75">
-        <v>245.3512570794471</v>
+        <v>268.3649416037312</v>
       </c>
       <c r="P75">
-        <v>736.0537712383414</v>
+        <v>805.0948248111935</v>
       </c>
       <c r="Q75">
-        <v>1750.053771238341</v>
+        <v>1819.094824811194</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1579348407645913</v>
+        <v>0.1578627480319479</v>
       </c>
       <c r="T75">
         <v>2.588054227065771</v>
       </c>
       <c r="U75">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V75">
         <v>0.25</v>
       </c>
       <c r="W75">
-        <v>0.061425</v>
+        <v>0.053925</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.30172195656927</v>
+        <v>2.621850184186693</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7700,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.08754631860580833</v>
+        <v>0.08197691309410414</v>
       </c>
       <c r="C76">
-        <v>1704.489224844232</v>
+        <v>3257.988618934187</v>
       </c>
       <c r="D76">
-        <v>10131.06541551283</v>
+        <v>11684.56480960278</v>
       </c>
       <c r="E76">
         <v>-714.3619048295077</v>
@@ -7513,45 +7733,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M76">
-        <v>764.2560900157579</v>
+        <v>670.940328109072</v>
       </c>
       <c r="N76">
-        <v>971.0772433175756</v>
+        <v>1064.393005224262</v>
       </c>
       <c r="O76">
-        <v>242.7693108293939</v>
+        <v>266.0982513060654</v>
       </c>
       <c r="P76">
-        <v>728.3079324881817</v>
+        <v>798.2947539181962</v>
       </c>
       <c r="Q76">
-        <v>1742.307932488182</v>
+        <v>1812.294753918196</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1618916100223397</v>
+        <v>0.1618169734388621</v>
       </c>
       <c r="T76">
         <v>2.679375829996814</v>
       </c>
       <c r="U76">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.061425</v>
+        <v>0.053925</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.27061760580482</v>
+        <v>2.586419776292278</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7782,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.08760998020517702</v>
+        <v>0.08196563421958235</v>
       </c>
       <c r="C77">
-        <v>1562.960866060626</v>
+        <v>3135.530270309153</v>
       </c>
       <c r="D77">
-        <v>10115.6394376842</v>
+        <v>11688.20884193273</v>
       </c>
       <c r="E77">
         <v>-588.2595238745271</v>
@@ -7595,45 +7815,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M77">
-        <v>774.5838750159709</v>
+        <v>680.0070892997351</v>
       </c>
       <c r="N77">
-        <v>960.7494583173626</v>
+        <v>1055.326244033598</v>
       </c>
       <c r="O77">
-        <v>240.1873645793407</v>
+        <v>263.8315610083996</v>
       </c>
       <c r="P77">
-        <v>720.562093738022</v>
+        <v>791.4946830251988</v>
       </c>
       <c r="Q77">
-        <v>1734.562093738022</v>
+        <v>1805.494683025199</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1661649208207081</v>
+        <v>0.1660875368783294</v>
       </c>
       <c r="T77">
         <v>2.778003161162342</v>
       </c>
       <c r="U77">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.25</v>
       </c>
       <c r="W77">
-        <v>0.061425</v>
+        <v>0.053925</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.240342704394089</v>
+        <v>2.551934179275047</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7864,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.0876736418045457</v>
+        <v>0.08195435534506054</v>
       </c>
       <c r="C78">
-        <v>1421.479412316947</v>
+        <v>3013.074195301399</v>
       </c>
       <c r="D78">
-        <v>10100.2603648955</v>
+        <v>11691.85514787996</v>
       </c>
       <c r="E78">
         <v>-462.1571429195446</v>
@@ -7677,45 +7897,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M78">
-        <v>784.9116600161839</v>
+        <v>689.0738504903984</v>
       </c>
       <c r="N78">
-        <v>950.4216733171496</v>
+        <v>1046.259482842935</v>
       </c>
       <c r="O78">
-        <v>237.6054183292874</v>
+        <v>261.5648707107338</v>
       </c>
       <c r="P78">
-        <v>712.8162549878622</v>
+        <v>784.6946121322013</v>
       </c>
       <c r="Q78">
-        <v>1726.816254987862</v>
+        <v>1798.694612132201</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1707943408522738</v>
+        <v>0.170713980604419</v>
       </c>
       <c r="T78">
         <v>2.884849436591662</v>
       </c>
       <c r="U78">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.061425</v>
+        <v>0.053925</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.210864510915219</v>
+        <v>2.518356097968796</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7946,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.08773730340391439</v>
+        <v>0.08419532647053878</v>
       </c>
       <c r="C79">
-        <v>1280.044650005053</v>
+        <v>2204.568193953255</v>
       </c>
       <c r="D79">
-        <v>10084.92798353859</v>
+        <v>11009.45152748679</v>
       </c>
       <c r="E79">
         <v>-336.054761964564</v>
@@ -7759,37 +7979,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M79">
-        <v>795.2394450163968</v>
+        <v>736.0091566818422</v>
       </c>
       <c r="N79">
-        <v>940.0938883169367</v>
+        <v>999.3241766514913</v>
       </c>
       <c r="O79">
-        <v>235.0234720792342</v>
+        <v>249.8310441628728</v>
       </c>
       <c r="P79">
-        <v>705.0704162377026</v>
+        <v>749.4931324886185</v>
       </c>
       <c r="Q79">
-        <v>1719.070416237703</v>
+        <v>1763.493132488618</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1758263191474539</v>
+        <v>0.1757427237849512</v>
       </c>
       <c r="T79">
         <v>3.000986692493099</v>
       </c>
       <c r="U79">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +8017,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.182151984799438</v>
+        <v>2.357760521834749</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +8028,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.08780096500328308</v>
+        <v>0.08421329759601698</v>
       </c>
       <c r="C80">
-        <v>1138.656366811876</v>
+        <v>2073.315194664818</v>
       </c>
       <c r="D80">
-        <v>10069.6420813004</v>
+        <v>11004.30090915334</v>
       </c>
       <c r="E80">
         <v>-209.9523810095834</v>
@@ -7841,37 +8061,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M80">
-        <v>805.5672300166098</v>
+        <v>745.5677171582298</v>
       </c>
       <c r="N80">
-        <v>929.7661033167237</v>
+        <v>989.7656161751037</v>
       </c>
       <c r="O80">
-        <v>232.4415258291809</v>
+        <v>247.4414040437759</v>
       </c>
       <c r="P80">
-        <v>697.3245774875428</v>
+        <v>742.3242121313277</v>
       </c>
       <c r="Q80">
-        <v>1711.324577487543</v>
+        <v>1756.324212131328</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1813157500149231</v>
+        <v>0.1812286254364408</v>
       </c>
       <c r="T80">
         <v>3.12768188074921</v>
       </c>
       <c r="U80">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.25</v>
       </c>
       <c r="W80">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +8099,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.154175677302009</v>
+        <v>2.327532822836867</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8110,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.08786462660265176</v>
+        <v>0.08423126872149519</v>
       </c>
       <c r="C81">
-        <v>997.3143517096269</v>
+        <v>1942.067012412677</v>
       </c>
       <c r="D81">
-        <v>10054.40244715313</v>
+        <v>10999.15510785618</v>
       </c>
       <c r="E81">
         <v>-83.85000005460097</v>
@@ -7923,37 +8143,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M81">
-        <v>815.8950150168228</v>
+        <v>755.1262776346175</v>
       </c>
       <c r="N81">
-        <v>919.4383183165107</v>
+        <v>980.207055698716</v>
       </c>
       <c r="O81">
-        <v>229.8595795791277</v>
+        <v>245.051763924679</v>
       </c>
       <c r="P81">
-        <v>689.578738737383</v>
+        <v>735.155291774037</v>
       </c>
       <c r="Q81">
-        <v>1703.578738737383</v>
+        <v>1749.155291774037</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1873279838221513</v>
+        <v>0.1872369939118818</v>
       </c>
       <c r="T81">
         <v>3.266443277410666</v>
       </c>
       <c r="U81">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V81">
         <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +8181,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.126907630753882</v>
+        <v>2.298070382041463</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8192,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.08792828820202045</v>
+        <v>0.0842492398469734</v>
       </c>
       <c r="C82">
-        <v>856.0183949460879</v>
+        <v>1810.823640442421</v>
       </c>
       <c r="D82">
-        <v>10039.20887134457</v>
+        <v>10994.0141168409</v>
       </c>
       <c r="E82">
         <v>42.25238090037965</v>
@@ -8005,37 +8225,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M82">
-        <v>826.2228000170356</v>
+        <v>764.684838111005</v>
       </c>
       <c r="N82">
-        <v>909.1105333162978</v>
+        <v>970.6484952223285</v>
       </c>
       <c r="O82">
-        <v>227.2776333290745</v>
+        <v>242.6621238055821</v>
       </c>
       <c r="P82">
-        <v>681.8328999872234</v>
+        <v>727.9863714167464</v>
       </c>
       <c r="Q82">
-        <v>1695.832899987223</v>
+        <v>1741.986371416746</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1939414410101023</v>
+        <v>0.193846199234867</v>
       </c>
       <c r="T82">
         <v>3.419080813738268</v>
       </c>
       <c r="U82">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.25</v>
       </c>
       <c r="W82">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8263,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.100321285369459</v>
+        <v>2.269344502265946</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8274,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08799194980138914</v>
+        <v>0.0842672109724516</v>
       </c>
       <c r="C83">
-        <v>714.7682880349803</v>
+        <v>1679.585072012233</v>
       </c>
       <c r="D83">
-        <v>10024.06114538844</v>
+        <v>10988.8779293657</v>
       </c>
       <c r="E83">
         <v>168.3547618553603</v>
@@ -8087,37 +8307,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M83">
-        <v>836.5505850172486</v>
+        <v>774.2433985873926</v>
       </c>
       <c r="N83">
-        <v>898.7827483160848</v>
+        <v>961.0899347459409</v>
       </c>
       <c r="O83">
-        <v>224.6956870790212</v>
+        <v>240.2724836864852</v>
       </c>
       <c r="P83">
-        <v>674.0870612370636</v>
+        <v>720.8174510594557</v>
       </c>
       <c r="Q83">
-        <v>1688.087061237064</v>
+        <v>1734.817451059456</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2012510515862586</v>
+        <v>0.2011511103813242</v>
       </c>
       <c r="T83">
         <v>3.587785459152985</v>
       </c>
       <c r="U83">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
         <v>0.25</v>
       </c>
       <c r="W83">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8345,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.07439139295749</v>
+        <v>2.241327903472539</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8356,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08805561140075782</v>
+        <v>0.0842851820979298</v>
       </c>
       <c r="C84">
-        <v>573.5638237464354</v>
+        <v>1548.351300392897</v>
       </c>
       <c r="D84">
-        <v>10008.95906205488</v>
+        <v>10983.74653870134</v>
       </c>
       <c r="E84">
         <v>294.4571428103409</v>
@@ -8169,37 +8389,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M84">
-        <v>846.8783700174615</v>
+        <v>783.80195906378</v>
       </c>
       <c r="N84">
-        <v>888.454963315872</v>
+        <v>951.5313742695535</v>
       </c>
       <c r="O84">
-        <v>222.113740828968</v>
+        <v>237.8828435673884</v>
       </c>
       <c r="P84">
-        <v>666.3412224869039</v>
+        <v>713.6485307021651</v>
       </c>
       <c r="Q84">
-        <v>1680.341222486904</v>
+        <v>1727.648530702165</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2093728411153213</v>
+        <v>0.2092676783218323</v>
       </c>
       <c r="T84">
         <v>3.775235065169337</v>
       </c>
       <c r="U84">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.25</v>
       </c>
       <c r="W84">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8427,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.049093936945813</v>
+        <v>2.21399463635702</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8438,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08811927300012651</v>
+        <v>0.08430315322340801</v>
       </c>
       <c r="C85">
-        <v>432.4047960975422</v>
+        <v>1417.122318867763</v>
       </c>
       <c r="D85">
-        <v>9993.902415360968</v>
+        <v>10978.61993813119</v>
       </c>
       <c r="E85">
         <v>420.5595237653233</v>
@@ -8251,37 +8471,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M85">
-        <v>857.2061550176746</v>
+        <v>793.3605195401677</v>
       </c>
       <c r="N85">
-        <v>878.1271783156589</v>
+        <v>941.9728137931658</v>
       </c>
       <c r="O85">
-        <v>219.5317945789147</v>
+        <v>235.4932034482914</v>
       </c>
       <c r="P85">
-        <v>658.5953837367441</v>
+        <v>706.4796103448743</v>
       </c>
       <c r="Q85">
-        <v>1672.595383736744</v>
+        <v>1720.479610344874</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2184501352948619</v>
+        <v>0.2183391366082825</v>
       </c>
       <c r="T85">
         <v>3.984737566011143</v>
       </c>
       <c r="U85">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V85">
         <v>0.25</v>
       </c>
       <c r="W85">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8509,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.02440605818743</v>
+        <v>2.187320002184043</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8520,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.08818293459949519</v>
+        <v>0.08432112434888622</v>
       </c>
       <c r="C86">
-        <v>291.2910003429843</v>
+        <v>1285.898120732712</v>
       </c>
       <c r="D86">
-        <v>9978.891000561389</v>
+        <v>10973.49812095112</v>
       </c>
       <c r="E86">
         <v>546.6619047203021</v>
@@ -8333,37 +8553,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M86">
-        <v>867.5339400178873</v>
+        <v>802.9190800165551</v>
       </c>
       <c r="N86">
-        <v>867.7993933154462</v>
+        <v>932.4142533167784</v>
       </c>
       <c r="O86">
-        <v>216.9498483288615</v>
+        <v>233.1035633291946</v>
       </c>
       <c r="P86">
-        <v>650.8495449865846</v>
+        <v>699.3106899875838</v>
       </c>
       <c r="Q86">
-        <v>1664.849544986585</v>
+        <v>1713.310689987584</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2286620912468449</v>
+        <v>0.2285445271805389</v>
       </c>
       <c r="T86">
         <v>4.220427879458172</v>
       </c>
       <c r="U86">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.061425</v>
+        <v>0.05685</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8591,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.000305986066151</v>
+        <v>2.16128047834852</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8602,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.0986378461988639</v>
+        <v>0.08433909547436444</v>
       </c>
       <c r="C87">
-        <v>-1809.313196563166</v>
+        <v>1154.67869929613</v>
       </c>
       <c r="D87">
-        <v>8004.389184610221</v>
+        <v>10968.38108046952</v>
       </c>
       <c r="E87">
         <v>672.7642856752846</v>
@@ -8415,45 +8635,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M87">
-        <v>1052.576573831227</v>
+        <v>812.4776404929428</v>
       </c>
       <c r="N87">
-        <v>682.7567595021069</v>
+        <v>922.8556928403907</v>
       </c>
       <c r="O87">
-        <v>170.6891898755267</v>
+        <v>230.7139232100977</v>
       </c>
       <c r="P87">
-        <v>512.0675696265802</v>
+        <v>692.1417696302931</v>
       </c>
       <c r="Q87">
-        <v>1526.06756962658</v>
+        <v>1706.141769630293</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2402356413257592</v>
+        <v>0.2401106364957629</v>
       </c>
       <c r="T87">
         <v>4.487543568031475</v>
       </c>
       <c r="U87">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V87">
         <v>0.25</v>
       </c>
       <c r="W87">
-        <v>0.07365000000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.648652816789349</v>
+        <v>2.135853649191478</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8684,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09882375779823258</v>
+        <v>0.08435706659984264</v>
       </c>
       <c r="C88">
-        <v>-1963.480521555928</v>
+        <v>1023.464047878886</v>
       </c>
       <c r="D88">
-        <v>7976.32424057244</v>
+        <v>10963.26881000725</v>
       </c>
       <c r="E88">
         <v>798.8666666302652</v>
@@ -8497,45 +8717,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M88">
-        <v>1064.959827641006</v>
+        <v>822.0362009693304</v>
       </c>
       <c r="N88">
-        <v>670.3735056923276</v>
+        <v>913.2971323640031</v>
       </c>
       <c r="O88">
-        <v>167.5933764230819</v>
+        <v>228.3242830910008</v>
       </c>
       <c r="P88">
-        <v>502.7801292692457</v>
+        <v>684.9728492730023</v>
       </c>
       <c r="Q88">
-        <v>1516.780129269246</v>
+        <v>1698.972849273002</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2534625557016612</v>
+        <v>0.2533290471417331</v>
       </c>
       <c r="T88">
         <v>4.792818640686677</v>
       </c>
       <c r="U88">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.07365000000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.629482435198775</v>
+        <v>2.11101814164274</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8766,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09900966939760125</v>
+        <v>0.08437503772532085</v>
       </c>
       <c r="C89">
-        <v>-2117.451731869109</v>
+        <v>892.2541598142852</v>
       </c>
       <c r="D89">
-        <v>7948.45541121424</v>
+        <v>10958.16130289763</v>
       </c>
       <c r="E89">
         <v>924.9690475852458</v>
@@ -8579,45 +8799,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M89">
-        <v>1077.343081450785</v>
+        <v>831.5947614457178</v>
       </c>
       <c r="N89">
-        <v>657.9902518825486</v>
+        <v>903.7385718876156</v>
       </c>
       <c r="O89">
-        <v>164.4975629706371</v>
+        <v>225.9346429719039</v>
       </c>
       <c r="P89">
-        <v>493.4926889119114</v>
+        <v>677.8039289157117</v>
       </c>
       <c r="Q89">
-        <v>1507.492688911912</v>
+        <v>1691.803928915712</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.268724379981548</v>
+        <v>0.2685810594255449</v>
       </c>
       <c r="T89">
         <v>5.145059109134987</v>
       </c>
       <c r="U89">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V89">
         <v>0.25</v>
       </c>
       <c r="W89">
-        <v>0.07365000000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.61075275203557</v>
+        <v>2.086753565302019</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8848,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.09919558099696994</v>
+        <v>0.08439300885079906</v>
       </c>
       <c r="C90">
-        <v>-2271.228875986484</v>
+        <v>761.0490284480529</v>
       </c>
       <c r="D90">
-        <v>7920.780648051846</v>
+        <v>10953.05855248638</v>
       </c>
       <c r="E90">
         <v>1051.071428540226</v>
@@ -8661,45 +8881,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M90">
-        <v>1089.726335260564</v>
+        <v>841.1533219221054</v>
       </c>
       <c r="N90">
-        <v>645.6069980727696</v>
+        <v>894.1800114112281</v>
       </c>
       <c r="O90">
-        <v>161.4017495181924</v>
+        <v>223.545002852807</v>
       </c>
       <c r="P90">
-        <v>484.2052485545772</v>
+        <v>670.6350085584211</v>
       </c>
       <c r="Q90">
-        <v>1498.205248554577</v>
+        <v>1684.635008558421</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2865298416414161</v>
+        <v>0.2863750737566588</v>
       </c>
       <c r="T90">
         <v>5.556006322324683</v>
       </c>
       <c r="U90">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.25</v>
       </c>
       <c r="W90">
-        <v>0.07365000000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.592448743489712</v>
+        <v>2.063040456605405</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8930,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.09938149259633863</v>
+        <v>0.08441097997627726</v>
       </c>
       <c r="C91">
-        <v>-2424.813973961343</v>
+        <v>629.8486471383076</v>
       </c>
       <c r="D91">
-        <v>7893.297931031968</v>
+        <v>10947.96055213162</v>
       </c>
       <c r="E91">
         <v>1177.173809495209</v>
@@ -8743,45 +8963,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M91">
-        <v>1102.109589070343</v>
+        <v>850.7118823984931</v>
       </c>
       <c r="N91">
-        <v>633.2237442629903</v>
+        <v>884.6214509348404</v>
       </c>
       <c r="O91">
-        <v>158.3059360657476</v>
+        <v>221.1553627337101</v>
       </c>
       <c r="P91">
-        <v>474.9178081972427</v>
+        <v>663.4660882011303</v>
       </c>
       <c r="Q91">
-        <v>1488.917808197243</v>
+        <v>1677.46608820113</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3075726599667148</v>
+        <v>0.3074043634207024</v>
       </c>
       <c r="T91">
         <v>6.041671210639779</v>
       </c>
       <c r="U91">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.25</v>
       </c>
       <c r="W91">
-        <v>0.07365000000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.574556060978591</v>
+        <v>2.039860226755906</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +9012,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.09956740419570731</v>
+        <v>0.08442895110175547</v>
       </c>
       <c r="C92">
-        <v>-2578.209017908017</v>
+        <v>498.653009255524</v>
       </c>
       <c r="D92">
-        <v>7866.005268040275</v>
+        <v>10942.86729520382</v>
       </c>
       <c r="E92">
         <v>1303.276190450189</v>
@@ -8825,45 +9045,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M92">
-        <v>1114.492842880122</v>
+        <v>860.2704428748806</v>
       </c>
       <c r="N92">
-        <v>620.840490453211</v>
+        <v>875.0628904584529</v>
       </c>
       <c r="O92">
-        <v>155.2101226133028</v>
+        <v>218.7657226146132</v>
       </c>
       <c r="P92">
-        <v>465.6303678399083</v>
+        <v>656.2971678438397</v>
       </c>
       <c r="Q92">
-        <v>1479.630367839908</v>
+        <v>1670.29716784384</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3328240419570732</v>
+        <v>0.3326395110175547</v>
       </c>
       <c r="T92">
         <v>6.624469076617893</v>
       </c>
       <c r="U92">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.07365000000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.557060993634384</v>
+        <v>2.017195113125285</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +9094,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.099753315795076</v>
+        <v>0.09413842222723368</v>
       </c>
       <c r="C93">
-        <v>-2731.415972483243</v>
+        <v>-1825.482512567278</v>
       </c>
       <c r="D93">
-        <v>7838.900694420031</v>
+        <v>8744.834154335995</v>
       </c>
       <c r="E93">
         <v>1429.37857140517</v>
@@ -8907,37 +9127,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M93">
-        <v>1126.876096689901</v>
+        <v>1032.778500021295</v>
       </c>
       <c r="N93">
-        <v>608.457236643432</v>
+        <v>702.5548333120389</v>
       </c>
       <c r="O93">
-        <v>152.114309160858</v>
+        <v>175.6387083280097</v>
       </c>
       <c r="P93">
-        <v>456.342927482574</v>
+        <v>526.9161249840292</v>
       </c>
       <c r="Q93">
-        <v>1470.342927482574</v>
+        <v>1540.916124984029</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3636868421675111</v>
+        <v>0.3634824691914854</v>
       </c>
       <c r="T93">
         <v>7.336777579480033</v>
       </c>
       <c r="U93">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V93">
         <v>0.25</v>
       </c>
       <c r="W93">
-        <v>0.07365000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +9165,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.539950433264776</v>
+        <v>1.680257028295567</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9176,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.09993922739444469</v>
+        <v>0.0942628933527119</v>
       </c>
       <c r="C94">
-        <v>-2884.436775357586</v>
+        <v>-1974.044950568146</v>
       </c>
       <c r="D94">
-        <v>7811.982272500669</v>
+        <v>8722.374097290109</v>
       </c>
       <c r="E94">
         <v>1555.480952360153</v>
@@ -8989,37 +9209,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M94">
-        <v>1139.259350499681</v>
+        <v>1044.127714307243</v>
       </c>
       <c r="N94">
-        <v>596.0739828336527</v>
+        <v>691.2056190260905</v>
       </c>
       <c r="O94">
-        <v>149.0184957084132</v>
+        <v>172.8014047565226</v>
       </c>
       <c r="P94">
-        <v>447.0554871252396</v>
+        <v>518.4042142695679</v>
       </c>
       <c r="Q94">
-        <v>1461.05548712524</v>
+        <v>1532.404214269568</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4022653424305587</v>
+        <v>0.4020361669088988</v>
       </c>
       <c r="T94">
         <v>8.227163208057709</v>
       </c>
       <c r="U94">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V94">
         <v>0.25</v>
       </c>
       <c r="W94">
-        <v>0.07365000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9247,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.523211841598854</v>
+        <v>1.661993364944528</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9258,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1001251389938134</v>
+        <v>0.0943873644781901</v>
       </c>
       <c r="C95">
-        <v>-3037.273337677218</v>
+        <v>-2122.492312206716</v>
       </c>
       <c r="D95">
-        <v>7785.248091136017</v>
+        <v>8700.02911660652</v>
       </c>
       <c r="E95">
         <v>1681.583333315133</v>
@@ -9071,37 +9291,37 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M95">
-        <v>1151.64260430946</v>
+        <v>1055.476928593191</v>
       </c>
       <c r="N95">
-        <v>583.6907290238737</v>
+        <v>679.8564047401421</v>
       </c>
       <c r="O95">
-        <v>145.9226822559684</v>
+        <v>169.9641011850355</v>
       </c>
       <c r="P95">
-        <v>437.7680467679053</v>
+        <v>509.8923035551066</v>
       </c>
       <c r="Q95">
-        <v>1451.768046767905</v>
+        <v>1523.892303555107</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4518662713401913</v>
+        <v>0.4516052068312874</v>
       </c>
       <c r="T95">
         <v>9.37194473051472</v>
       </c>
       <c r="U95">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V95">
         <v>0.25</v>
       </c>
       <c r="W95">
-        <v>0.07365000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9329,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.506833219646179</v>
+        <v>1.644122468547275</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9340,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1513759727432461</v>
+        <v>0.0945118356036683</v>
       </c>
       <c r="C96">
-        <v>-6942.64902532712</v>
+        <v>-2270.825479631083</v>
       </c>
       <c r="D96">
-        <v>4005.974784441096</v>
+        <v>8677.798330137133</v>
       </c>
       <c r="E96">
         <v>1807.685714270114</v>
@@ -9153,45 +9373,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M96">
-        <v>1939.25285527808</v>
+        <v>1066.82614287914</v>
       </c>
       <c r="N96">
-        <v>-203.919521944747</v>
+        <v>668.507190454194</v>
       </c>
       <c r="O96">
-        <v>-50.97988048618674</v>
+        <v>167.1267976135485</v>
       </c>
       <c r="P96">
-        <v>-152.9396414585602</v>
+        <v>501.3803928406455</v>
       </c>
       <c r="Q96">
-        <v>861.0603585414398</v>
+        <v>1515.380392840646</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5332539232932978</v>
+        <v>0.5176972600611387</v>
       </c>
       <c r="T96">
-        <v>11.25035874735352</v>
+        <v>10.89832009379073</v>
       </c>
       <c r="U96">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V96">
-        <v>0.2237115867343269</v>
+        <v>0.25</v>
       </c>
       <c r="W96">
-        <v>0.1270007844102641</v>
+        <v>0.0675</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.8948463469373076</v>
+        <v>1.626631803988261</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9422,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1525539727432461</v>
+        <v>0.09463630672914652</v>
       </c>
       <c r="C97">
-        <v>-7112.956208921356</v>
+        <v>-2419.045325995885</v>
       </c>
       <c r="D97">
-        <v>3961.76998180184</v>
+        <v>8655.680864727312</v>
       </c>
       <c r="E97">
         <v>1933.788095225094</v>
@@ -9235,45 +9455,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M97">
-        <v>1959.883204802315</v>
+        <v>1078.175357165088</v>
       </c>
       <c r="N97">
-        <v>-224.5498714689818</v>
+        <v>657.1579761682456</v>
       </c>
       <c r="O97">
-        <v>-56.13746786724545</v>
+        <v>164.2894940420614</v>
       </c>
       <c r="P97">
-        <v>-168.4124036017363</v>
+        <v>492.8684821261842</v>
       </c>
       <c r="Q97">
-        <v>845.5875963982637</v>
+        <v>1506.868482126184</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.6307447079519576</v>
+        <v>0.610226134582931</v>
       </c>
       <c r="T97">
-        <v>13.50043049682423</v>
+        <v>13.03524560237716</v>
       </c>
       <c r="U97">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V97">
-        <v>0.2213567279265971</v>
+        <v>0.25</v>
       </c>
       <c r="W97">
-        <v>0.1273860393112087</v>
+        <v>0.0675</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8854269117063885</v>
+        <v>1.60950936394628</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9504,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1537319727432461</v>
+        <v>0.09476077785462472</v>
       </c>
       <c r="C98">
-        <v>-7282.2984651417</v>
+        <v>-2567.15271557658</v>
       </c>
       <c r="D98">
-        <v>3918.530106536477</v>
+        <v>8633.675856101598</v>
       </c>
       <c r="E98">
         <v>2059.890476180075</v>
@@ -9317,45 +9537,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M98">
-        <v>1980.51355432655</v>
+        <v>1089.524571451036</v>
       </c>
       <c r="N98">
-        <v>-245.1802209932166</v>
+        <v>645.8087618822974</v>
       </c>
       <c r="O98">
-        <v>-61.29505524830415</v>
+        <v>161.4521904705744</v>
       </c>
       <c r="P98">
-        <v>-183.8851657449125</v>
+        <v>484.3565714117231</v>
       </c>
       <c r="Q98">
-        <v>830.1148342550875</v>
+        <v>1498.356571411723</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.7769808849399453</v>
+        <v>0.7490194463656173</v>
       </c>
       <c r="T98">
-        <v>16.87553812103025</v>
+        <v>16.24063386525675</v>
       </c>
       <c r="U98">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V98">
-        <v>0.2190509286773618</v>
+        <v>0.25</v>
       </c>
       <c r="W98">
-        <v>0.1277632680683836</v>
+        <v>0.0675</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.876203714709447</v>
+        <v>1.592743641405173</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9586,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1549099727432461</v>
+        <v>0.09488524898010293</v>
       </c>
       <c r="C99">
-        <v>-7450.7070473489</v>
+        <v>-2715.148503882077</v>
       </c>
       <c r="D99">
-        <v>3876.223905284257</v>
+        <v>8611.782448751081</v>
       </c>
       <c r="E99">
         <v>2185.992857135056</v>
@@ -9399,45 +9619,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M99">
-        <v>2001.143903850785</v>
+        <v>1100.873785736984</v>
       </c>
       <c r="N99">
-        <v>-265.8105705174514</v>
+        <v>634.4595475963492</v>
       </c>
       <c r="O99">
-        <v>-66.45264262936286</v>
+        <v>158.6148868990873</v>
       </c>
       <c r="P99">
-        <v>-199.3579278880886</v>
+        <v>475.8446606972619</v>
       </c>
       <c r="Q99">
-        <v>814.6420721119114</v>
+        <v>1489.844660697262</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.020707846586594</v>
+        <v>0.9803416326700967</v>
       </c>
       <c r="T99">
-        <v>22.500717494707</v>
+        <v>21.58294763672279</v>
       </c>
       <c r="U99">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V99">
-        <v>0.2167926716806879</v>
+        <v>0.25</v>
       </c>
       <c r="W99">
-        <v>0.1281327189130395</v>
+        <v>0.0675</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8671706867227518</v>
+        <v>1.576323603864914</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9668,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1560879727432462</v>
+        <v>0.09500972010558115</v>
       </c>
       <c r="C100">
-        <v>-7618.211873619068</v>
+        <v>-2863.033537765581</v>
       </c>
       <c r="D100">
-        <v>3834.821459969071</v>
+        <v>8589.999795822558</v>
       </c>
       <c r="E100">
         <v>2312.095238090036</v>
@@ -9481,45 +9701,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M100">
-        <v>2021.77425337502</v>
+        <v>1112.223000022933</v>
       </c>
       <c r="N100">
-        <v>-286.4409200416862</v>
+        <v>623.1103333104008</v>
       </c>
       <c r="O100">
-        <v>-71.61023001042156</v>
+        <v>155.7775833276002</v>
       </c>
       <c r="P100">
-        <v>-214.8306900312647</v>
+        <v>467.3327499828006</v>
       </c>
       <c r="Q100">
-        <v>799.1693099687353</v>
+        <v>1481.332749982801</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.508161769879891</v>
+        <v>1.442986005279056</v>
       </c>
       <c r="T100">
-        <v>33.7510762420605</v>
+        <v>32.26757517965487</v>
       </c>
       <c r="U100">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V100">
-        <v>0.2145805015614972</v>
+        <v>0.25</v>
       </c>
       <c r="W100">
-        <v>0.1284946299445391</v>
+        <v>0.0675</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8583220062459891</v>
+        <v>1.560238669131598</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9750,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1572659727432461</v>
+        <v>0.09513419123105935</v>
       </c>
       <c r="C101">
-        <v>-7784.841597301763</v>
+        <v>-3010.808655533778</v>
       </c>
       <c r="D101">
-        <v>3794.294117241358</v>
+        <v>8568.327059009343</v>
       </c>
       <c r="E101">
         <v>2438.197619045019</v>
@@ -9563,45 +9783,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M101">
-        <v>2042.404602899255</v>
+        <v>1123.572214308881</v>
       </c>
       <c r="N101">
-        <v>-307.0712695659215</v>
+        <v>611.7611190244525</v>
       </c>
       <c r="O101">
-        <v>-76.76781739148038</v>
+        <v>152.9402797561131</v>
       </c>
       <c r="P101">
-        <v>-230.3034521744411</v>
+        <v>458.8208392683393</v>
       </c>
       <c r="Q101">
-        <v>783.6965478255588</v>
+        <v>1472.820839268339</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.970523539759781</v>
+        <v>2.830919123105932</v>
       </c>
       <c r="T101">
-        <v>67.502152484121</v>
+        <v>64.32145780845109</v>
       </c>
       <c r="U101">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V101">
-        <v>0.2124130217477447</v>
+        <v>0.25</v>
       </c>
       <c r="W101">
-        <v>0.128849229642069</v>
+        <v>0.0675</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.8496520869909789</v>
+        <v>1.544478682574713</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/united_states/united_states_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_rubber_tires.xlsx
@@ -1492,7 +1492,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1629,22 +1629,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08281154980871674</v>
+        <v>0.08263827093419493</v>
       </c>
       <c r="C2">
-        <v>12326.06958082238</v>
+        <v>12253.68932179694</v>
       </c>
       <c r="D2">
-        <v>11421.06958082238</v>
+        <v>11474.79170275192</v>
       </c>
       <c r="E2">
-        <v>-10045.9380954981</v>
+        <v>-9919.835714543122</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>126.102380954981</v>
       </c>
       <c r="G2">
         <v>905</v>
@@ -1665,28 +1665,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.342949762035546</v>
       </c>
       <c r="N2">
-        <v>1735.333333333333</v>
+        <v>1728.990383571298</v>
       </c>
       <c r="O2">
-        <v>433.8333333333334</v>
+        <v>432.2475958928245</v>
       </c>
       <c r="P2">
-        <v>1301.5</v>
+        <v>1296.742787678474</v>
       </c>
       <c r="Q2">
-        <v>2315.5</v>
+        <v>2310.742787678474</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08281154980871674</v>
+        <v>0.08309194033757064</v>
       </c>
       <c r="T2">
-        <v>0.8547702034345667</v>
+        <v>0.8612457352787679</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>273.5845936727772</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1711,22 +1711,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08263827093419493</v>
+        <v>0.08246499205967316</v>
       </c>
       <c r="C3">
-        <v>12253.68932179694</v>
+        <v>12181.81684462562</v>
       </c>
       <c r="D3">
-        <v>11474.79170275192</v>
+        <v>11529.02160653558</v>
       </c>
       <c r="E3">
-        <v>-9919.835714543122</v>
+        <v>-9793.733333588141</v>
       </c>
       <c r="F3">
-        <v>126.102380954981</v>
+        <v>252.204761909962</v>
       </c>
       <c r="G3">
         <v>905</v>
@@ -1747,28 +1747,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M3">
-        <v>6.342949762035546</v>
+        <v>12.68589952407109</v>
       </c>
       <c r="N3">
-        <v>1728.990383571298</v>
+        <v>1722.647433809262</v>
       </c>
       <c r="O3">
-        <v>432.2475958928245</v>
+        <v>430.6618584523156</v>
       </c>
       <c r="P3">
-        <v>1296.742787678474</v>
+        <v>1291.985575356947</v>
       </c>
       <c r="Q3">
-        <v>2310.742787678474</v>
+        <v>2305.985575356947</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08309194033757064</v>
+        <v>0.08337805312211546</v>
       </c>
       <c r="T3">
-        <v>0.8612457352787679</v>
+        <v>0.8678534208340754</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>273.5845936727772</v>
+        <v>136.7922968363886</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1793,22 +1793,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08246499205967316</v>
+        <v>0.08229171318515134</v>
       </c>
       <c r="C4">
-        <v>12181.81684462562</v>
+        <v>12110.45938283028</v>
       </c>
       <c r="D4">
-        <v>11529.02160653558</v>
+        <v>11583.76652569523</v>
       </c>
       <c r="E4">
-        <v>-9793.733333588141</v>
+        <v>-9667.630952633159</v>
       </c>
       <c r="F4">
-        <v>252.204761909962</v>
+        <v>378.307142864943</v>
       </c>
       <c r="G4">
         <v>905</v>
@@ -1829,28 +1829,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M4">
-        <v>12.68589952407109</v>
+        <v>19.02884928610664</v>
       </c>
       <c r="N4">
-        <v>1722.647433809262</v>
+        <v>1716.304484047227</v>
       </c>
       <c r="O4">
-        <v>430.6618584523156</v>
+        <v>429.0761210118067</v>
       </c>
       <c r="P4">
-        <v>1291.985575356947</v>
+        <v>1287.22836303542</v>
       </c>
       <c r="Q4">
-        <v>2305.985575356947</v>
+        <v>2301.22836303542</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08337805312211546</v>
+        <v>0.08367006513933128</v>
       </c>
       <c r="T4">
-        <v>0.8678534208340754</v>
+        <v>0.8745973473286673</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>136.7922968363886</v>
+        <v>91.1948645575924</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1875,22 +1875,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08229171318515134</v>
+        <v>0.08211843431062957</v>
       </c>
       <c r="C5">
-        <v>12110.45938283028</v>
+        <v>12039.62430798018</v>
       </c>
       <c r="D5">
-        <v>11583.76652569523</v>
+        <v>11639.0338318001</v>
       </c>
       <c r="E5">
-        <v>-9667.630952633159</v>
+        <v>-9541.528571678178</v>
       </c>
       <c r="F5">
-        <v>378.307142864943</v>
+        <v>504.4095238199241</v>
       </c>
       <c r="G5">
         <v>905</v>
@@ -1911,28 +1911,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M5">
-        <v>19.02884928610664</v>
+        <v>25.37179904814218</v>
       </c>
       <c r="N5">
-        <v>1716.304484047227</v>
+        <v>1709.961534285191</v>
       </c>
       <c r="O5">
-        <v>429.0761210118067</v>
+        <v>427.4903835712978</v>
       </c>
       <c r="P5">
-        <v>1287.22836303542</v>
+        <v>1282.471150713893</v>
       </c>
       <c r="Q5">
-        <v>2301.22836303542</v>
+        <v>2296.471150713894</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08367006513933128</v>
+        <v>0.08396816074023913</v>
       </c>
       <c r="T5">
-        <v>0.8745973473286673</v>
+        <v>0.8814817722918968</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>91.1948645575924</v>
+        <v>68.39614841819429</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1957,22 +1957,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08211843431062957</v>
+        <v>0.08194515543610778</v>
       </c>
       <c r="C6">
-        <v>12039.62430798018</v>
+        <v>11969.31913300099</v>
       </c>
       <c r="D6">
-        <v>11639.0338318001</v>
+        <v>11694.83103777589</v>
       </c>
       <c r="E6">
-        <v>-9541.528571678178</v>
+        <v>-9415.426190723198</v>
       </c>
       <c r="F6">
-        <v>504.4095238199241</v>
+        <v>630.5119047749051</v>
       </c>
       <c r="G6">
         <v>905</v>
@@ -1993,28 +1993,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M6">
-        <v>25.37179904814218</v>
+        <v>31.71474881017773</v>
       </c>
       <c r="N6">
-        <v>1709.961534285191</v>
+        <v>1703.618584523156</v>
       </c>
       <c r="O6">
-        <v>427.4903835712978</v>
+        <v>425.9046461307889</v>
       </c>
       <c r="P6">
-        <v>1282.471150713893</v>
+        <v>1277.713938392367</v>
       </c>
       <c r="Q6">
-        <v>2296.471150713894</v>
+        <v>2291.713938392367</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08396816074023913</v>
+        <v>0.08427253203800819</v>
       </c>
       <c r="T6">
-        <v>0.8814817722918968</v>
+        <v>0.8885111325175101</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>68.39614841819429</v>
+        <v>54.71691873455543</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08194515543610778</v>
+        <v>0.08177187656158598</v>
       </c>
       <c r="C7">
-        <v>11969.31913300099</v>
+        <v>11899.55151557937</v>
       </c>
       <c r="D7">
-        <v>11694.83103777589</v>
+        <v>11751.16580130926</v>
       </c>
       <c r="E7">
-        <v>-9415.426190723198</v>
+        <v>-9289.323809768217</v>
       </c>
       <c r="F7">
-        <v>630.5119047749051</v>
+        <v>756.6142857298862</v>
       </c>
       <c r="G7">
         <v>905</v>
@@ -2075,28 +2075,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M7">
-        <v>31.71474881017773</v>
+        <v>38.05769857221328</v>
       </c>
       <c r="N7">
-        <v>1703.618584523156</v>
+        <v>1697.27563476112</v>
       </c>
       <c r="O7">
-        <v>425.9046461307889</v>
+        <v>424.3189086902801</v>
       </c>
       <c r="P7">
-        <v>1277.713938392367</v>
+        <v>1272.95672607084</v>
       </c>
       <c r="Q7">
-        <v>2291.713938392367</v>
+        <v>2286.95672607084</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08427253203800819</v>
+        <v>0.08458337932083615</v>
       </c>
       <c r="T7">
-        <v>0.8885111325175101</v>
+        <v>0.8956900535989873</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.71691873455543</v>
+        <v>45.5974322787962</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2121,22 +2121,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08177187656158598</v>
+        <v>0.08159859768706418</v>
       </c>
       <c r="C8">
-        <v>11899.55151557937</v>
+        <v>11830.32926166651</v>
       </c>
       <c r="D8">
-        <v>11751.16580130926</v>
+        <v>11808.04592835138</v>
       </c>
       <c r="E8">
-        <v>-9289.323809768217</v>
+        <v>-9163.221428813235</v>
       </c>
       <c r="F8">
-        <v>756.6142857298861</v>
+        <v>882.7166666848671</v>
       </c>
       <c r="G8">
         <v>905</v>
@@ -2157,28 +2157,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M8">
-        <v>38.05769857221328</v>
+        <v>44.40064833424881</v>
       </c>
       <c r="N8">
-        <v>1697.27563476112</v>
+        <v>1690.932684999085</v>
       </c>
       <c r="O8">
-        <v>424.3189086902801</v>
+        <v>422.7331712497711</v>
       </c>
       <c r="P8">
-        <v>1272.95672607084</v>
+        <v>1268.199513749313</v>
       </c>
       <c r="Q8">
-        <v>2286.95672607084</v>
+        <v>2282.199513749313</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08458337932083615</v>
+        <v>0.08490091149146686</v>
       </c>
       <c r="T8">
-        <v>0.8956900535989873</v>
+        <v>0.9030233600800663</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.5974322787962</v>
+        <v>39.08351338182531</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2203,22 +2203,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08159859768706418</v>
+        <v>0.0814253188125424</v>
       </c>
       <c r="C9">
-        <v>11830.32926166651</v>
+        <v>11761.66032908381</v>
       </c>
       <c r="D9">
-        <v>11808.04592835138</v>
+        <v>11865.47937672366</v>
       </c>
       <c r="E9">
-        <v>-9163.221428813235</v>
+        <v>-9037.119047858254</v>
       </c>
       <c r="F9">
-        <v>882.7166666848672</v>
+        <v>1008.819047639848</v>
       </c>
       <c r="G9">
         <v>905</v>
@@ -2239,28 +2239,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M9">
-        <v>44.40064833424882</v>
+        <v>50.74359809628437</v>
       </c>
       <c r="N9">
-        <v>1690.932684999085</v>
+        <v>1684.589735237049</v>
       </c>
       <c r="O9">
-        <v>422.7331712497711</v>
+        <v>421.1474338092623</v>
       </c>
       <c r="P9">
-        <v>1268.199513749313</v>
+        <v>1263.442301427787</v>
       </c>
       <c r="Q9">
-        <v>2282.199513749313</v>
+        <v>2277.442301427787</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08490091149146686</v>
+        <v>0.08522534653537217</v>
       </c>
       <c r="T9">
-        <v>0.9030233600800663</v>
+        <v>0.9105160862672559</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.08351338182531</v>
+        <v>34.19807420909715</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2285,22 +2285,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0814253188125424</v>
+        <v>0.08125203993802062</v>
       </c>
       <c r="C10">
-        <v>11761.66032908381</v>
+        <v>11693.55283123442</v>
       </c>
       <c r="D10">
-        <v>11865.47937672366</v>
+        <v>11923.47425982925</v>
       </c>
       <c r="E10">
-        <v>-9037.119047858254</v>
+        <v>-8911.016666903273</v>
       </c>
       <c r="F10">
-        <v>1008.819047639848</v>
+        <v>1134.921428594829</v>
       </c>
       <c r="G10">
         <v>905</v>
@@ -2321,28 +2321,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M10">
-        <v>50.74359809628437</v>
+        <v>57.08654785831991</v>
       </c>
       <c r="N10">
-        <v>1684.589735237049</v>
+        <v>1678.246785475014</v>
       </c>
       <c r="O10">
-        <v>421.1474338092623</v>
+        <v>419.5616963687534</v>
       </c>
       <c r="P10">
-        <v>1263.442301427787</v>
+        <v>1258.68508910626</v>
       </c>
       <c r="Q10">
-        <v>2277.442301427787</v>
+        <v>2272.68508910626</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08522534653537217</v>
+        <v>0.08555691201980287</v>
       </c>
       <c r="T10">
-        <v>0.9105160862672559</v>
+        <v>0.9181734877552625</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.19807420909715</v>
+        <v>30.39828818586413</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08125203993802062</v>
+        <v>0.08107876106349882</v>
       </c>
       <c r="C11">
-        <v>11693.55283123442</v>
+        <v>11626.01504092405</v>
       </c>
       <c r="D11">
-        <v>11923.47425982925</v>
+        <v>11982.03885047386</v>
       </c>
       <c r="E11">
-        <v>-8911.016666903273</v>
+        <v>-8784.914285948293</v>
       </c>
       <c r="F11">
-        <v>1134.921428594829</v>
+        <v>1261.02380954981</v>
       </c>
       <c r="G11">
         <v>905</v>
@@ -2403,28 +2403,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M11">
-        <v>57.08654785831991</v>
+        <v>63.42949762035545</v>
       </c>
       <c r="N11">
-        <v>1678.246785475014</v>
+        <v>1671.903835712978</v>
       </c>
       <c r="O11">
-        <v>419.5616963687534</v>
+        <v>417.9759589282445</v>
       </c>
       <c r="P11">
-        <v>1258.68508910626</v>
+        <v>1253.927876784734</v>
       </c>
       <c r="Q11">
-        <v>2272.68508910626</v>
+        <v>2267.927876784734</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08555691201980287</v>
+        <v>0.0858958456261098</v>
       </c>
       <c r="T11">
-        <v>0.9181734877552625</v>
+        <v>0.9260010537207805</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.39828818586413</v>
+        <v>27.35845936727772</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2449,22 +2449,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08107876106349882</v>
+        <v>0.08090548218897703</v>
       </c>
       <c r="C12">
-        <v>11626.01504092405</v>
+        <v>11559.055394295</v>
       </c>
       <c r="D12">
-        <v>11982.03885047386</v>
+        <v>12041.18158479979</v>
       </c>
       <c r="E12">
-        <v>-8784.914285948293</v>
+        <v>-8658.811904993312</v>
       </c>
       <c r="F12">
-        <v>1261.02380954981</v>
+        <v>1387.126190504791</v>
       </c>
       <c r="G12">
         <v>905</v>
@@ -2485,28 +2485,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M12">
-        <v>63.42949762035546</v>
+        <v>69.77244738239099</v>
       </c>
       <c r="N12">
-        <v>1671.903835712978</v>
+        <v>1665.560885950943</v>
       </c>
       <c r="O12">
-        <v>417.9759589282445</v>
+        <v>416.3902214877356</v>
       </c>
       <c r="P12">
-        <v>1253.927876784734</v>
+        <v>1249.170664463207</v>
       </c>
       <c r="Q12">
-        <v>2267.927876784734</v>
+        <v>2263.170664463207</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0858958456261098</v>
+        <v>0.08624239571795173</v>
       </c>
       <c r="T12">
-        <v>0.9260010537207805</v>
+        <v>0.9340045200450743</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.35845936727771</v>
+        <v>24.8713266975252</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08090548218897703</v>
+        <v>0.08073220331445524</v>
       </c>
       <c r="C13">
-        <v>11559.055394295</v>
+        <v>11492.68249487728</v>
       </c>
       <c r="D13">
-        <v>12041.18158479979</v>
+        <v>12100.91106633705</v>
       </c>
       <c r="E13">
-        <v>-8658.811904993312</v>
+        <v>-8532.70952403833</v>
       </c>
       <c r="F13">
-        <v>1387.126190504791</v>
+        <v>1513.228571459772</v>
       </c>
       <c r="G13">
         <v>905</v>
@@ -2567,28 +2567,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M13">
-        <v>69.77244738239099</v>
+        <v>76.11539714442655</v>
       </c>
       <c r="N13">
-        <v>1665.560885950943</v>
+        <v>1659.217936188907</v>
       </c>
       <c r="O13">
-        <v>416.3902214877356</v>
+        <v>414.8044840472267</v>
       </c>
       <c r="P13">
-        <v>1249.170664463207</v>
+        <v>1244.41345214168</v>
       </c>
       <c r="Q13">
-        <v>2263.170664463207</v>
+        <v>2258.41345214168</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08624239571795173</v>
+        <v>0.08659682194824458</v>
       </c>
       <c r="T13">
-        <v>0.9340045200450743</v>
+        <v>0.9421898833312837</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.8713266975252</v>
+        <v>22.7987161393981</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2613,22 +2613,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08073220331445524</v>
+        <v>0.08055892443993344</v>
       </c>
       <c r="C14">
-        <v>11492.68249487728</v>
+        <v>11426.90511776086</v>
       </c>
       <c r="D14">
-        <v>12100.91106633705</v>
+        <v>12161.23607017561</v>
       </c>
       <c r="E14">
-        <v>-8532.70952403833</v>
+        <v>-8406.607143083349</v>
       </c>
       <c r="F14">
-        <v>1513.228571459772</v>
+        <v>1639.330952414753</v>
       </c>
       <c r="G14">
         <v>905</v>
@@ -2649,28 +2649,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M14">
-        <v>76.11539714442655</v>
+        <v>82.4583469064621</v>
       </c>
       <c r="N14">
-        <v>1659.217936188907</v>
+        <v>1652.874986426871</v>
       </c>
       <c r="O14">
-        <v>414.8044840472267</v>
+        <v>413.2187466067178</v>
       </c>
       <c r="P14">
-        <v>1244.41345214168</v>
+        <v>1239.656239820154</v>
       </c>
       <c r="Q14">
-        <v>2258.41345214168</v>
+        <v>2253.656239820154</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08659682194824458</v>
+        <v>0.08695939590796947</v>
       </c>
       <c r="T14">
-        <v>0.9421898833312837</v>
+        <v>0.9505634158884405</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.7987161393981</v>
+        <v>21.04496874405978</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2695,22 +2695,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08055892443993344</v>
+        <v>0.08038564556541164</v>
       </c>
       <c r="C15">
-        <v>11426.90511776086</v>
+        <v>11361.73221389338</v>
       </c>
       <c r="D15">
-        <v>12161.23607017561</v>
+        <v>12222.16554726311</v>
       </c>
       <c r="E15">
-        <v>-8406.607143083349</v>
+        <v>-8280.504762128368</v>
       </c>
       <c r="F15">
-        <v>1639.330952414753</v>
+        <v>1765.433333369734</v>
       </c>
       <c r="G15">
         <v>905</v>
@@ -2731,28 +2731,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M15">
-        <v>82.4583469064621</v>
+        <v>88.80129666849764</v>
       </c>
       <c r="N15">
-        <v>1652.874986426871</v>
+        <v>1646.532036664836</v>
       </c>
       <c r="O15">
-        <v>413.2187466067178</v>
+        <v>411.633009166209</v>
       </c>
       <c r="P15">
-        <v>1239.656239820154</v>
+        <v>1234.899027498627</v>
       </c>
       <c r="Q15">
-        <v>2253.656239820154</v>
+        <v>2248.899027498627</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08695939590796947</v>
+        <v>0.0873304018202461</v>
       </c>
       <c r="T15">
-        <v>0.9505634158884405</v>
+        <v>0.95913168176088</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.04496874405978</v>
+        <v>19.54175669091266</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2777,22 +2777,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08038564556541164</v>
+        <v>0.08021236669088985</v>
       </c>
       <c r="C16">
-        <v>11361.73221389338</v>
+        <v>11297.17291450765</v>
       </c>
       <c r="D16">
-        <v>12222.16554726311</v>
+        <v>12283.70862883237</v>
       </c>
       <c r="E16">
-        <v>-8280.504762128368</v>
+        <v>-8154.402381173387</v>
       </c>
       <c r="F16">
-        <v>1765.433333369734</v>
+        <v>1891.535714324716</v>
       </c>
       <c r="G16">
         <v>905</v>
@@ -2813,28 +2813,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M16">
-        <v>88.80129666849764</v>
+        <v>95.1442464305332</v>
       </c>
       <c r="N16">
-        <v>1646.532036664836</v>
+        <v>1640.1890869028</v>
       </c>
       <c r="O16">
-        <v>411.633009166209</v>
+        <v>410.0472717257001</v>
       </c>
       <c r="P16">
-        <v>1234.899027498627</v>
+        <v>1230.1418151771</v>
       </c>
       <c r="Q16">
-        <v>2248.899027498627</v>
+        <v>2244.1418151771</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0873304018202461</v>
+        <v>0.08771013728339982</v>
       </c>
       <c r="T16">
-        <v>0.95913168176088</v>
+        <v>0.9679015538891417</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.54175669091266</v>
+        <v>18.23897291151847</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2859,22 +2859,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08021236669088985</v>
+        <v>0.08003908781636807</v>
       </c>
       <c r="C17">
-        <v>11297.17291450766</v>
+        <v>11233.23653568373</v>
       </c>
       <c r="D17">
-        <v>12283.70862883237</v>
+        <v>12345.87463096342</v>
       </c>
       <c r="E17">
-        <v>-8154.402381173388</v>
+        <v>-8028.300000218406</v>
       </c>
       <c r="F17">
-        <v>1891.535714324715</v>
+        <v>2017.638095279696</v>
       </c>
       <c r="G17">
         <v>905</v>
@@ -2895,28 +2895,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M17">
-        <v>95.14424643053319</v>
+        <v>101.4871961925687</v>
       </c>
       <c r="N17">
-        <v>1640.1890869028</v>
+        <v>1633.846137140765</v>
       </c>
       <c r="O17">
-        <v>410.0472717257001</v>
+        <v>408.4615342851912</v>
       </c>
       <c r="P17">
-        <v>1230.1418151771</v>
+        <v>1225.384602855574</v>
       </c>
       <c r="Q17">
-        <v>2244.1418151771</v>
+        <v>2239.384602855574</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08771013728339982</v>
+        <v>0.08809891406710484</v>
       </c>
       <c r="T17">
-        <v>0.9679015538891417</v>
+        <v>0.9768802324966476</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.23897291151848</v>
+        <v>17.09903710454858</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08003908781636807</v>
+        <v>0.07986580894184628</v>
       </c>
       <c r="C18">
-        <v>11233.23653568373</v>
+        <v>11169.93258305001</v>
       </c>
       <c r="D18">
-        <v>12345.87463096342</v>
+        <v>12408.67305928469</v>
       </c>
       <c r="E18">
-        <v>-8028.300000218406</v>
+        <v>-7902.197619263425</v>
       </c>
       <c r="F18">
-        <v>2017.638095279696</v>
+        <v>2143.740476234677</v>
       </c>
       <c r="G18">
         <v>905</v>
@@ -2977,28 +2977,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M18">
-        <v>101.4871961925687</v>
+        <v>107.8301459546043</v>
       </c>
       <c r="N18">
-        <v>1633.846137140765</v>
+        <v>1627.503187378729</v>
       </c>
       <c r="O18">
-        <v>408.4615342851912</v>
+        <v>406.8757968446823</v>
       </c>
       <c r="P18">
-        <v>1225.384602855574</v>
+        <v>1220.627390534047</v>
       </c>
       <c r="Q18">
-        <v>2239.384602855574</v>
+        <v>2234.627390534047</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08809891406710484</v>
+        <v>0.08849705896607986</v>
       </c>
       <c r="T18">
-        <v>0.9768802324966476</v>
+        <v>0.9860752648055394</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.09903710454858</v>
+        <v>16.09321139251631</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3023,22 +3023,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07986580894184628</v>
+        <v>0.07969253006732448</v>
       </c>
       <c r="C19">
-        <v>11169.93258305001</v>
+        <v>11107.27075662875</v>
       </c>
       <c r="D19">
-        <v>12408.67305928469</v>
+        <v>12472.11361381841</v>
       </c>
       <c r="E19">
-        <v>-7902.197619263425</v>
+        <v>-7776.095238308444</v>
       </c>
       <c r="F19">
-        <v>2143.740476234677</v>
+        <v>2269.842857189658</v>
       </c>
       <c r="G19">
         <v>905</v>
@@ -3059,28 +3059,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M19">
-        <v>107.8301459546043</v>
+        <v>114.1730957166398</v>
       </c>
       <c r="N19">
-        <v>1627.503187378729</v>
+        <v>1621.160237616694</v>
       </c>
       <c r="O19">
-        <v>406.8757968446823</v>
+        <v>405.2900594041734</v>
       </c>
       <c r="P19">
-        <v>1220.627390534047</v>
+        <v>1215.87017821252</v>
       </c>
       <c r="Q19">
-        <v>2234.627390534047</v>
+        <v>2229.87017821252</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08849705896607986</v>
+        <v>0.08890491471624937</v>
       </c>
       <c r="T19">
-        <v>0.9860752648055394</v>
+        <v>0.9954945661951355</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.09321139251631</v>
+        <v>15.19914409293207</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3105,22 +3105,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07969253006732449</v>
+        <v>0.0795192511928027</v>
       </c>
       <c r="C20">
-        <v>11107.27075662874</v>
+        <v>11045.26095583081</v>
       </c>
       <c r="D20">
-        <v>12472.1136138184</v>
+        <v>12536.20619397545</v>
       </c>
       <c r="E20">
-        <v>-7776.095238308444</v>
+        <v>-7649.992857353463</v>
       </c>
       <c r="F20">
-        <v>2269.842857189658</v>
+        <v>2395.945238144639</v>
       </c>
       <c r="G20">
         <v>905</v>
@@ -3141,28 +3141,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M20">
-        <v>114.1730957166398</v>
+        <v>120.5160454786754</v>
       </c>
       <c r="N20">
-        <v>1621.160237616694</v>
+        <v>1614.817287854658</v>
       </c>
       <c r="O20">
-        <v>405.2900594041734</v>
+        <v>403.7043219636645</v>
       </c>
       <c r="P20">
-        <v>1215.87017821252</v>
+        <v>1211.112965890994</v>
       </c>
       <c r="Q20">
-        <v>2229.87017821252</v>
+        <v>2225.112965890994</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08890491471624937</v>
+        <v>0.08932284097876876</v>
       </c>
       <c r="T20">
-        <v>0.9954945661951355</v>
+        <v>1.005146442927685</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.19914409293207</v>
+        <v>14.39918914067248</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3187,22 +3187,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0795192511928027</v>
+        <v>0.0793459723182809</v>
       </c>
       <c r="C21">
-        <v>11045.26095583081</v>
+        <v>10983.91328460536</v>
       </c>
       <c r="D21">
-        <v>12536.20619397545</v>
+        <v>12600.96090370498</v>
       </c>
       <c r="E21">
-        <v>-7649.992857353463</v>
+        <v>-7523.890476398482</v>
       </c>
       <c r="F21">
-        <v>2395.945238144639</v>
+        <v>2522.047619099621</v>
       </c>
       <c r="G21">
         <v>905</v>
@@ -3223,28 +3223,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M21">
-        <v>120.5160454786754</v>
+        <v>126.8589952407109</v>
       </c>
       <c r="N21">
-        <v>1614.817287854658</v>
+        <v>1608.474338092622</v>
       </c>
       <c r="O21">
-        <v>403.7043219636645</v>
+        <v>402.1185845231556</v>
       </c>
       <c r="P21">
-        <v>1211.112965890994</v>
+        <v>1206.355753569467</v>
       </c>
       <c r="Q21">
-        <v>2225.112965890994</v>
+        <v>2220.355753569467</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08932284097876876</v>
+        <v>0.08975121539785114</v>
       </c>
       <c r="T21">
-        <v>1.005146442927685</v>
+        <v>1.015039616578548</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.39918914067248</v>
+        <v>13.67922968363886</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3269,22 +3269,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0793459723182809</v>
+        <v>0.07917269344375912</v>
       </c>
       <c r="C22">
-        <v>10983.91328460536</v>
+        <v>10923.23805674987</v>
       </c>
       <c r="D22">
-        <v>12600.96090370498</v>
+        <v>12666.38805680447</v>
       </c>
       <c r="E22">
-        <v>-7523.890476398482</v>
+        <v>-7397.7880954435</v>
       </c>
       <c r="F22">
-        <v>2522.047619099621</v>
+        <v>2648.150000054602</v>
       </c>
       <c r="G22">
         <v>905</v>
@@ -3305,28 +3305,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M22">
-        <v>126.8589952407109</v>
+        <v>133.2019450027465</v>
       </c>
       <c r="N22">
-        <v>1608.474338092622</v>
+        <v>1602.131388330587</v>
       </c>
       <c r="O22">
-        <v>402.1185845231556</v>
+        <v>400.5328470826468</v>
       </c>
       <c r="P22">
-        <v>1206.355753569467</v>
+        <v>1201.59854124794</v>
       </c>
       <c r="Q22">
-        <v>2220.355753569467</v>
+        <v>2215.59854124794</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08975121539785114</v>
+        <v>0.09019043473893558</v>
       </c>
       <c r="T22">
-        <v>1.015039616578548</v>
+        <v>1.025183250321838</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.67922968363886</v>
+        <v>13.02783779394177</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3351,22 +3351,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07917269344375912</v>
+        <v>0.07924691456923731</v>
       </c>
       <c r="C23">
-        <v>10923.23805674987</v>
+        <v>10769.02804346385</v>
       </c>
       <c r="D23">
-        <v>12666.38805680447</v>
+        <v>12638.28042447344</v>
       </c>
       <c r="E23">
-        <v>-7397.788095443501</v>
+        <v>-7271.68571448852</v>
       </c>
       <c r="F23">
-        <v>2648.150000054601</v>
+        <v>2774.252381009582</v>
       </c>
       <c r="G23">
         <v>905</v>
@@ -3387,45 +3387,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M23">
-        <v>133.2019450027464</v>
+        <v>143.7062733362964</v>
       </c>
       <c r="N23">
-        <v>1602.131388330587</v>
+        <v>1591.627059997037</v>
       </c>
       <c r="O23">
-        <v>400.5328470826468</v>
+        <v>397.9067649992593</v>
       </c>
       <c r="P23">
-        <v>1201.59854124794</v>
+        <v>1193.720294997778</v>
       </c>
       <c r="Q23">
-        <v>2215.59854124794</v>
+        <v>2207.720294997778</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09019043473893558</v>
+        <v>0.09064091611440681</v>
       </c>
       <c r="T23">
-        <v>1.025183250321838</v>
+        <v>1.035586977238033</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.037725</v>
+        <v>0.03885</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.02783779394177</v>
+        <v>12.07555726723473</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07924691456923731</v>
+        <v>0.07908488569471553</v>
       </c>
       <c r="C24">
-        <v>10769.02804346385</v>
+        <v>10704.44807156414</v>
       </c>
       <c r="D24">
-        <v>12638.28042447344</v>
+        <v>12699.8028335287</v>
       </c>
       <c r="E24">
-        <v>-7271.68571448852</v>
+        <v>-7145.583333533539</v>
       </c>
       <c r="F24">
-        <v>2774.252381009582</v>
+        <v>2900.354761964564</v>
       </c>
       <c r="G24">
         <v>905</v>
@@ -3469,28 +3469,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M24">
-        <v>143.7062733362964</v>
+        <v>150.2383766697644</v>
       </c>
       <c r="N24">
-        <v>1591.627059997037</v>
+        <v>1585.094956663569</v>
       </c>
       <c r="O24">
-        <v>397.9067649992593</v>
+        <v>396.2737391658923</v>
       </c>
       <c r="P24">
-        <v>1193.720294997778</v>
+        <v>1188.821217497677</v>
       </c>
       <c r="Q24">
-        <v>2207.720294997778</v>
+        <v>2202.821217497677</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09064091611440681</v>
+        <v>0.09110309830482535</v>
       </c>
       <c r="T24">
-        <v>1.035586977238033</v>
+        <v>1.046260930827375</v>
       </c>
       <c r="U24">
         <v>0.05180000000000001</v>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.07555726723473</v>
+        <v>11.55053303822452</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3515,22 +3515,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07908488569471553</v>
+        <v>0.07892285682019375</v>
       </c>
       <c r="C25">
-        <v>10704.44807156414</v>
+        <v>10640.47000467227</v>
       </c>
       <c r="D25">
-        <v>12699.8028335287</v>
+        <v>12761.92714759182</v>
       </c>
       <c r="E25">
-        <v>-7145.583333533539</v>
+        <v>-7019.480952578558</v>
       </c>
       <c r="F25">
-        <v>2900.354761964564</v>
+        <v>3026.457142919545</v>
       </c>
       <c r="G25">
         <v>905</v>
@@ -3551,28 +3551,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M25">
-        <v>150.2383766697644</v>
+        <v>156.7704800032324</v>
       </c>
       <c r="N25">
-        <v>1585.094956663569</v>
+        <v>1578.562853330101</v>
       </c>
       <c r="O25">
-        <v>396.2737391658923</v>
+        <v>394.6407133325253</v>
       </c>
       <c r="P25">
-        <v>1188.821217497677</v>
+        <v>1183.922139997576</v>
       </c>
       <c r="Q25">
-        <v>2202.821217497677</v>
+        <v>2197.922139997576</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09110309830482535</v>
+        <v>0.09157744318446545</v>
       </c>
       <c r="T25">
-        <v>1.046260930827375</v>
+        <v>1.057215777932227</v>
       </c>
       <c r="U25">
         <v>0.05180000000000001</v>
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.55053303822452</v>
+        <v>11.06926082829849</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3597,22 +3597,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07892285682019375</v>
+        <v>0.07876082794567194</v>
       </c>
       <c r="C26">
-        <v>10640.47000467227</v>
+        <v>10577.10271932417</v>
       </c>
       <c r="D26">
-        <v>12761.92714759182</v>
+        <v>12824.66224319869</v>
       </c>
       <c r="E26">
-        <v>-7019.480952578559</v>
+        <v>-6893.378571623577</v>
       </c>
       <c r="F26">
-        <v>3026.457142919544</v>
+        <v>3152.559523874525</v>
       </c>
       <c r="G26">
         <v>905</v>
@@ -3633,28 +3633,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M26">
-        <v>156.7704800032324</v>
+        <v>163.3025833367004</v>
       </c>
       <c r="N26">
-        <v>1578.562853330101</v>
+        <v>1572.030749996633</v>
       </c>
       <c r="O26">
-        <v>394.6407133325253</v>
+        <v>393.0076874991582</v>
       </c>
       <c r="P26">
-        <v>1183.922139997576</v>
+        <v>1179.023062497475</v>
       </c>
       <c r="Q26">
-        <v>2197.922139997576</v>
+        <v>2193.023062497475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09157744318446545</v>
+        <v>0.09206443726089591</v>
       </c>
       <c r="T26">
-        <v>1.057215777932227</v>
+        <v>1.068462754293208</v>
       </c>
       <c r="U26">
         <v>0.05180000000000001</v>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.0692608282985</v>
+        <v>10.62649039516656</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3679,22 +3679,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07876082794567194</v>
+        <v>0.07859879907115015</v>
       </c>
       <c r="C27">
-        <v>10577.10271932417</v>
+        <v>10514.35526745912</v>
       </c>
       <c r="D27">
-        <v>12824.66224319869</v>
+        <v>12888.01717228862</v>
       </c>
       <c r="E27">
-        <v>-6893.378571623577</v>
+        <v>-6767.276190668596</v>
       </c>
       <c r="F27">
-        <v>3152.559523874525</v>
+        <v>3278.661904829507</v>
       </c>
       <c r="G27">
         <v>905</v>
@@ -3715,28 +3715,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M27">
-        <v>163.3025833367004</v>
+        <v>169.8346866701685</v>
       </c>
       <c r="N27">
-        <v>1572.030749996633</v>
+        <v>1565.498646663165</v>
       </c>
       <c r="O27">
-        <v>393.0076874991582</v>
+        <v>391.3746616657913</v>
       </c>
       <c r="P27">
-        <v>1179.023062497475</v>
+        <v>1174.123984997374</v>
       </c>
       <c r="Q27">
-        <v>2193.023062497475</v>
+        <v>2188.123984997374</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09206443726089591</v>
+        <v>0.0925645933393921</v>
       </c>
       <c r="T27">
-        <v>1.068462754293208</v>
+        <v>1.08001370298827</v>
       </c>
       <c r="U27">
         <v>0.05180000000000001</v>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.62649039516656</v>
+        <v>10.21777922612169</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3761,22 +3761,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07859879907115015</v>
+        <v>0.07843677019662836</v>
       </c>
       <c r="C28">
-        <v>10514.35526745912</v>
+        <v>10452.23688077386</v>
       </c>
       <c r="D28">
-        <v>12888.01717228862</v>
+        <v>12952.00116655835</v>
       </c>
       <c r="E28">
-        <v>-6767.276190668596</v>
+        <v>-6641.173809713615</v>
       </c>
       <c r="F28">
-        <v>3278.661904829507</v>
+        <v>3404.764285784488</v>
       </c>
       <c r="G28">
         <v>905</v>
@@ -3797,28 +3797,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M28">
-        <v>169.8346866701685</v>
+        <v>176.3667900036365</v>
       </c>
       <c r="N28">
-        <v>1565.498646663165</v>
+        <v>1558.966543329697</v>
       </c>
       <c r="O28">
-        <v>391.3746616657913</v>
+        <v>389.7416358324243</v>
       </c>
       <c r="P28">
-        <v>1174.123984997374</v>
+        <v>1169.224907497273</v>
       </c>
       <c r="Q28">
-        <v>2188.123984997374</v>
+        <v>2183.224907497273</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0925645933393921</v>
+        <v>0.09307845232414844</v>
       </c>
       <c r="T28">
-        <v>1.08001370298827</v>
+        <v>1.091881116031142</v>
       </c>
       <c r="U28">
         <v>0.05180000000000001</v>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.21777922612169</v>
+        <v>9.839342958487553</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3843,22 +3843,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07843677019662836</v>
+        <v>0.07863174132210657</v>
       </c>
       <c r="C29">
-        <v>10452.23688077386</v>
+        <v>10249.2191080989</v>
       </c>
       <c r="D29">
-        <v>12952.00116655835</v>
+        <v>12875.08577483837</v>
       </c>
       <c r="E29">
-        <v>-6641.173809713615</v>
+        <v>-6515.071428758634</v>
       </c>
       <c r="F29">
-        <v>3404.764285784488</v>
+        <v>3530.866666739469</v>
       </c>
       <c r="G29">
         <v>905</v>
@@ -3879,45 +3879,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M29">
-        <v>176.3667900036365</v>
+        <v>188.9013666705616</v>
       </c>
       <c r="N29">
-        <v>1558.966543329697</v>
+        <v>1546.431966662772</v>
       </c>
       <c r="O29">
-        <v>389.7416358324243</v>
+        <v>386.607991665693</v>
       </c>
       <c r="P29">
-        <v>1169.224907497273</v>
+        <v>1159.823974997079</v>
       </c>
       <c r="Q29">
-        <v>2183.224907497273</v>
+        <v>2173.823974997079</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09307845232414844</v>
+        <v>0.09360658516959244</v>
       </c>
       <c r="T29">
-        <v>1.091881116031142</v>
+        <v>1.104078179436315</v>
       </c>
       <c r="U29">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.03885</v>
+        <v>0.04012500000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.839342958487553</v>
+        <v>9.186451977129966</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3925,22 +3925,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07863174132210657</v>
+        <v>0.07848246244758476</v>
       </c>
       <c r="C30">
-        <v>10249.2191080989</v>
+        <v>10181.92436187835</v>
       </c>
       <c r="D30">
-        <v>12875.08577483837</v>
+        <v>12933.89340957281</v>
       </c>
       <c r="E30">
-        <v>-6515.071428758634</v>
+        <v>-6388.969047803652</v>
       </c>
       <c r="F30">
-        <v>3530.866666739469</v>
+        <v>3656.96904769445</v>
       </c>
       <c r="G30">
         <v>905</v>
@@ -3961,28 +3961,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M30">
-        <v>188.9013666705616</v>
+        <v>195.6478440516531</v>
       </c>
       <c r="N30">
-        <v>1546.431966662772</v>
+        <v>1539.68548928168</v>
       </c>
       <c r="O30">
-        <v>386.607991665693</v>
+        <v>384.9213723204201</v>
       </c>
       <c r="P30">
-        <v>1159.823974997079</v>
+        <v>1154.76411696126</v>
       </c>
       <c r="Q30">
-        <v>2173.823974997079</v>
+        <v>2168.76411696126</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09360658516959244</v>
+        <v>0.09414959499659827</v>
       </c>
       <c r="T30">
-        <v>1.104078179436315</v>
+        <v>1.116618822092339</v>
       </c>
       <c r="U30">
         <v>0.05350000000000001</v>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.186451977129966</v>
+        <v>8.869677771022037</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4007,22 +4007,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07848246244758476</v>
+        <v>0.07833318357306297</v>
       </c>
       <c r="C31">
-        <v>10181.92436187836</v>
+        <v>10115.16929462939</v>
       </c>
       <c r="D31">
-        <v>12933.89340957281</v>
+        <v>12993.24072327882</v>
       </c>
       <c r="E31">
-        <v>-6388.969047803654</v>
+        <v>-6262.866666848672</v>
       </c>
       <c r="F31">
-        <v>3656.969047694449</v>
+        <v>3783.07142864943</v>
       </c>
       <c r="G31">
         <v>905</v>
@@ -4043,28 +4043,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M31">
-        <v>195.6478440516531</v>
+        <v>202.3943214327445</v>
       </c>
       <c r="N31">
-        <v>1539.68548928168</v>
+        <v>1532.939011900589</v>
       </c>
       <c r="O31">
-        <v>384.9213723204201</v>
+        <v>383.2347529751472</v>
       </c>
       <c r="P31">
-        <v>1154.76411696126</v>
+        <v>1149.704258925442</v>
       </c>
       <c r="Q31">
-        <v>2168.76411696126</v>
+        <v>2163.704258925442</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09414959499659827</v>
+        <v>0.09470811939008997</v>
       </c>
       <c r="T31">
-        <v>1.116618822092339</v>
+        <v>1.129517768824249</v>
       </c>
       <c r="U31">
         <v>0.05350000000000001</v>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.869677771022038</v>
+        <v>8.574021845321305</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4089,22 +4089,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07833318357306297</v>
+        <v>0.07818390469854118</v>
       </c>
       <c r="C32">
-        <v>10115.16929462939</v>
+        <v>10048.96136956592</v>
       </c>
       <c r="D32">
-        <v>12993.24072327882</v>
+        <v>13053.13517917033</v>
       </c>
       <c r="E32">
-        <v>-6262.866666848672</v>
+        <v>-6136.764285893691</v>
       </c>
       <c r="F32">
-        <v>3783.07142864943</v>
+        <v>3909.173809604411</v>
       </c>
       <c r="G32">
         <v>905</v>
@@ -4125,28 +4125,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M32">
-        <v>202.3943214327445</v>
+        <v>209.140798813836</v>
       </c>
       <c r="N32">
-        <v>1532.939011900589</v>
+        <v>1526.192534519497</v>
       </c>
       <c r="O32">
-        <v>383.2347529751472</v>
+        <v>381.5481336298744</v>
       </c>
       <c r="P32">
-        <v>1149.704258925442</v>
+        <v>1144.644400889623</v>
       </c>
       <c r="Q32">
-        <v>2163.704258925442</v>
+        <v>2158.644400889623</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09470811939008997</v>
+        <v>0.09528283289643651</v>
       </c>
       <c r="T32">
-        <v>1.129517768824249</v>
+        <v>1.142790598070127</v>
       </c>
       <c r="U32">
         <v>0.05350000000000001</v>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.574021845321305</v>
+        <v>8.29744049547223</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4171,22 +4171,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07818390469854118</v>
+        <v>0.0780346258240194</v>
       </c>
       <c r="C33">
-        <v>10048.96136956592</v>
+        <v>9983.308188150746</v>
       </c>
       <c r="D33">
-        <v>13053.13517917033</v>
+        <v>13113.58437871014</v>
       </c>
       <c r="E33">
-        <v>-6136.764285893691</v>
+        <v>-6010.66190493871</v>
       </c>
       <c r="F33">
-        <v>3909.173809604411</v>
+        <v>4035.276190559392</v>
       </c>
       <c r="G33">
         <v>905</v>
@@ -4207,28 +4207,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M33">
-        <v>209.140798813836</v>
+        <v>215.8872761949275</v>
       </c>
       <c r="N33">
-        <v>1526.192534519497</v>
+        <v>1519.446057138406</v>
       </c>
       <c r="O33">
-        <v>381.5481336298744</v>
+        <v>379.8615142846015</v>
       </c>
       <c r="P33">
-        <v>1144.644400889623</v>
+        <v>1139.584542853804</v>
       </c>
       <c r="Q33">
-        <v>2158.644400889623</v>
+        <v>2153.584542853804</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09528283289643651</v>
+        <v>0.095874449741205</v>
       </c>
       <c r="T33">
-        <v>1.142790598070127</v>
+        <v>1.156453804646767</v>
       </c>
       <c r="U33">
         <v>0.05350000000000001</v>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.29744049547223</v>
+        <v>8.038145479988721</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4253,22 +4253,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0780346258240194</v>
+        <v>0.07788534694949761</v>
       </c>
       <c r="C34">
-        <v>9983.308188150746</v>
+        <v>9918.2174933116</v>
       </c>
       <c r="D34">
-        <v>13113.58437871014</v>
+        <v>13174.59606482597</v>
       </c>
       <c r="E34">
-        <v>-6010.66190493871</v>
+        <v>-5884.559523983728</v>
       </c>
       <c r="F34">
-        <v>4035.276190559392</v>
+        <v>4161.378571514374</v>
       </c>
       <c r="G34">
         <v>905</v>
@@ -4289,28 +4289,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M34">
-        <v>215.8872761949275</v>
+        <v>222.633753576019</v>
       </c>
       <c r="N34">
-        <v>1519.446057138406</v>
+        <v>1512.699579757314</v>
       </c>
       <c r="O34">
-        <v>379.8615142846015</v>
+        <v>378.1748949393286</v>
       </c>
       <c r="P34">
-        <v>1139.584542853804</v>
+        <v>1134.524684817986</v>
       </c>
       <c r="Q34">
-        <v>2153.584542853804</v>
+        <v>2148.524684817986</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.095874449741205</v>
+        <v>0.09648372679029493</v>
       </c>
       <c r="T34">
-        <v>1.156453804646767</v>
+        <v>1.170524868136142</v>
       </c>
       <c r="U34">
         <v>0.05350000000000001</v>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.038145479988721</v>
+        <v>7.794565313928457</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4335,22 +4335,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07788534694949761</v>
+        <v>0.0779400680749758</v>
       </c>
       <c r="C35">
-        <v>9918.2174933116</v>
+        <v>9769.684272362563</v>
       </c>
       <c r="D35">
-        <v>13174.59606482597</v>
+        <v>13152.16522483192</v>
       </c>
       <c r="E35">
-        <v>-5884.559523983728</v>
+        <v>-5758.457143028748</v>
       </c>
       <c r="F35">
-        <v>4161.378571514374</v>
+        <v>4287.480952469355</v>
       </c>
       <c r="G35">
         <v>905</v>
@@ -4371,45 +4371,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M35">
-        <v>222.633753576019</v>
+        <v>232.810215719086</v>
       </c>
       <c r="N35">
-        <v>1512.699579757314</v>
+        <v>1502.523117614247</v>
       </c>
       <c r="O35">
-        <v>378.1748949393286</v>
+        <v>375.6307794035619</v>
       </c>
       <c r="P35">
-        <v>1134.524684817986</v>
+        <v>1126.892338210685</v>
       </c>
       <c r="Q35">
-        <v>2148.524684817986</v>
+        <v>2140.892338210685</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09648372679029493</v>
+        <v>0.09711146678026639</v>
       </c>
       <c r="T35">
-        <v>1.170524868136142</v>
+        <v>1.185022327488831</v>
       </c>
       <c r="U35">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04012500000000001</v>
+        <v>0.040725</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.794565313928457</v>
+        <v>7.453853895428822</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4417,22 +4417,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0779400680749758</v>
+        <v>0.07779678920045402</v>
       </c>
       <c r="C36">
-        <v>9769.684272362563</v>
+        <v>9702.47615792704</v>
       </c>
       <c r="D36">
-        <v>13152.16522483192</v>
+        <v>13211.05949135138</v>
       </c>
       <c r="E36">
-        <v>-5758.457143028748</v>
+        <v>-5632.354762073766</v>
       </c>
       <c r="F36">
-        <v>4287.480952469355</v>
+        <v>4413.583333424336</v>
       </c>
       <c r="G36">
         <v>905</v>
@@ -4453,28 +4453,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M36">
-        <v>232.810215719086</v>
+        <v>239.6575750049415</v>
       </c>
       <c r="N36">
-        <v>1502.523117614247</v>
+        <v>1495.675758328392</v>
       </c>
       <c r="O36">
-        <v>375.6307794035619</v>
+        <v>373.918939582098</v>
       </c>
       <c r="P36">
-        <v>1126.892338210685</v>
+        <v>1121.756818746294</v>
       </c>
       <c r="Q36">
-        <v>2140.892338210685</v>
+        <v>2135.756818746294</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09711146678026639</v>
+        <v>0.09775852184685234</v>
       </c>
       <c r="T36">
-        <v>1.185022327488831</v>
+        <v>1.199965862513911</v>
       </c>
       <c r="U36">
         <v>0.05430000000000001</v>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.453853895428822</v>
+        <v>7.240886641273712</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07779678920045402</v>
+        <v>0.07765351032593222</v>
       </c>
       <c r="C37">
-        <v>9702.47615792704</v>
+        <v>9635.797862914022</v>
       </c>
       <c r="D37">
-        <v>13211.05949135138</v>
+        <v>13270.48357729334</v>
       </c>
       <c r="E37">
-        <v>-5632.354762073766</v>
+        <v>-5506.252381118786</v>
       </c>
       <c r="F37">
-        <v>4413.583333424336</v>
+        <v>4539.685714379317</v>
       </c>
       <c r="G37">
         <v>905</v>
@@ -4535,28 +4535,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M37">
-        <v>239.6575750049415</v>
+        <v>246.5049342907969</v>
       </c>
       <c r="N37">
-        <v>1495.675758328392</v>
+        <v>1488.828399042537</v>
       </c>
       <c r="O37">
-        <v>373.918939582098</v>
+        <v>372.2070997606342</v>
       </c>
       <c r="P37">
-        <v>1121.756818746294</v>
+        <v>1116.621299281902</v>
       </c>
       <c r="Q37">
-        <v>2135.756818746294</v>
+        <v>2130.621299281902</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09775852184685234</v>
+        <v>0.0984257973842691</v>
       </c>
       <c r="T37">
-        <v>1.199965862513911</v>
+        <v>1.215376383008524</v>
       </c>
       <c r="U37">
         <v>0.05430000000000001</v>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.240886641273712</v>
+        <v>7.039750901238332</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4581,22 +4581,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07765351032593223</v>
+        <v>0.07751023145141045</v>
       </c>
       <c r="C38">
-        <v>9635.797862914016</v>
+        <v>9569.656569099881</v>
       </c>
       <c r="D38">
-        <v>13270.48357729333</v>
+        <v>13330.44466443418</v>
       </c>
       <c r="E38">
-        <v>-5506.252381118786</v>
+        <v>-5380.150000163805</v>
       </c>
       <c r="F38">
-        <v>4539.685714379317</v>
+        <v>4665.788095334297</v>
       </c>
       <c r="G38">
         <v>905</v>
@@ -4617,28 +4617,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M38">
-        <v>246.5049342907969</v>
+        <v>253.3522935766524</v>
       </c>
       <c r="N38">
-        <v>1488.828399042537</v>
+        <v>1481.981039756681</v>
       </c>
       <c r="O38">
-        <v>372.2070997606342</v>
+        <v>370.4952599391703</v>
       </c>
       <c r="P38">
-        <v>1116.621299281902</v>
+        <v>1111.485779817511</v>
       </c>
       <c r="Q38">
-        <v>2130.621299281902</v>
+        <v>2125.485779817511</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0984257973842691</v>
+        <v>0.09911425627208006</v>
       </c>
       <c r="T38">
-        <v>1.215376383008524</v>
+        <v>1.231276126375983</v>
       </c>
       <c r="U38">
         <v>0.05430000000000001</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.039750901238332</v>
+        <v>6.849487363367026</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4663,22 +4663,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07751023145141045</v>
+        <v>0.07736695257688865</v>
       </c>
       <c r="C39">
-        <v>9569.656569099881</v>
+        <v>9504.059588650161</v>
       </c>
       <c r="D39">
-        <v>13330.44466443418</v>
+        <v>13390.95006493944</v>
       </c>
       <c r="E39">
-        <v>-5380.150000163805</v>
+        <v>-5254.047619208824</v>
       </c>
       <c r="F39">
-        <v>4665.788095334297</v>
+        <v>4791.890476289279</v>
       </c>
       <c r="G39">
         <v>905</v>
@@ -4699,28 +4699,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M39">
-        <v>253.3522935766524</v>
+        <v>260.1996528625079</v>
       </c>
       <c r="N39">
-        <v>1481.981039756681</v>
+        <v>1475.133680470826</v>
       </c>
       <c r="O39">
-        <v>370.4952599391703</v>
+        <v>368.7834201177064</v>
       </c>
       <c r="P39">
-        <v>1111.485779817511</v>
+        <v>1106.350260353119</v>
       </c>
       <c r="Q39">
-        <v>2125.485779817511</v>
+        <v>2120.350260353119</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09911425627208006</v>
+        <v>0.09982492351111072</v>
       </c>
       <c r="T39">
-        <v>1.231276126375983</v>
+        <v>1.247688764690779</v>
       </c>
       <c r="U39">
         <v>0.05430000000000001</v>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.849487363367026</v>
+        <v>6.669237695909998</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4745,22 +4745,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07736695257688865</v>
+        <v>0.07722367370236685</v>
       </c>
       <c r="C40">
-        <v>9504.059588650161</v>
+        <v>9439.014367092099</v>
       </c>
       <c r="D40">
-        <v>13390.95006493944</v>
+        <v>13452.00722433636</v>
       </c>
       <c r="E40">
-        <v>-5254.047619208824</v>
+        <v>-5127.945238253843</v>
       </c>
       <c r="F40">
-        <v>4791.890476289279</v>
+        <v>4917.99285724426</v>
       </c>
       <c r="G40">
         <v>905</v>
@@ -4781,28 +4781,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M40">
-        <v>260.1996528625079</v>
+        <v>267.0470121483633</v>
       </c>
       <c r="N40">
-        <v>1475.133680470826</v>
+        <v>1468.28632118497</v>
       </c>
       <c r="O40">
-        <v>368.7834201177064</v>
+        <v>367.0715802962425</v>
       </c>
       <c r="P40">
-        <v>1106.350260353119</v>
+        <v>1101.214740888728</v>
       </c>
       <c r="Q40">
-        <v>2120.350260353119</v>
+        <v>2115.214740888728</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09982492351111072</v>
+        <v>0.1005588913153555</v>
       </c>
       <c r="T40">
-        <v>1.247688764690779</v>
+        <v>1.264639522294584</v>
       </c>
       <c r="U40">
         <v>0.05430000000000001</v>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.669237695909998</v>
+        <v>6.498231601143076</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4827,22 +4827,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07722367370236685</v>
+        <v>0.07708039482784505</v>
       </c>
       <c r="C41">
-        <v>9439.014367092099</v>
+        <v>9374.528486368958</v>
       </c>
       <c r="D41">
-        <v>13452.00722433636</v>
+        <v>13513.6237245682</v>
       </c>
       <c r="E41">
-        <v>-5127.945238253843</v>
+        <v>-5001.842857298861</v>
       </c>
       <c r="F41">
-        <v>4917.99285724426</v>
+        <v>5044.095238199241</v>
       </c>
       <c r="G41">
         <v>905</v>
@@ -4863,28 +4863,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M41">
-        <v>267.0470121483633</v>
+        <v>273.8943714342188</v>
       </c>
       <c r="N41">
-        <v>1468.28632118497</v>
+        <v>1461.438961899115</v>
       </c>
       <c r="O41">
-        <v>367.0715802962425</v>
+        <v>365.3597404747787</v>
       </c>
       <c r="P41">
-        <v>1101.214740888728</v>
+        <v>1096.079221424336</v>
       </c>
       <c r="Q41">
-        <v>2115.214740888728</v>
+        <v>2110.079221424336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1005588913153555</v>
+        <v>0.1013173247130751</v>
       </c>
       <c r="T41">
-        <v>1.264639522294584</v>
+        <v>1.28215530515185</v>
       </c>
       <c r="U41">
         <v>0.05430000000000001</v>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.498231601143076</v>
+        <v>6.335775811114498</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4909,22 +4909,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07708039482784505</v>
+        <v>0.07693711595332327</v>
       </c>
       <c r="C42">
-        <v>9374.528486368958</v>
+        <v>9310.609667978653</v>
       </c>
       <c r="D42">
-        <v>13513.6237245682</v>
+        <v>13575.80728713287</v>
       </c>
       <c r="E42">
-        <v>-5001.842857298861</v>
+        <v>-4875.740476343881</v>
       </c>
       <c r="F42">
-        <v>5044.095238199241</v>
+        <v>5170.197619154222</v>
       </c>
       <c r="G42">
         <v>905</v>
@@ -4945,28 +4945,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M42">
-        <v>273.8943714342188</v>
+        <v>280.7417307200743</v>
       </c>
       <c r="N42">
-        <v>1461.438961899115</v>
+        <v>1454.591602613259</v>
       </c>
       <c r="O42">
-        <v>365.3597404747787</v>
+        <v>363.6479006533148</v>
       </c>
       <c r="P42">
-        <v>1096.079221424336</v>
+        <v>1090.943701959945</v>
       </c>
       <c r="Q42">
-        <v>2110.079221424336</v>
+        <v>2104.943701959945</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1013173247130751</v>
+        <v>0.1021014677174971</v>
       </c>
       <c r="T42">
-        <v>1.28215530515185</v>
+        <v>1.30026484336021</v>
       </c>
       <c r="U42">
         <v>0.05430000000000001</v>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.335775811114498</v>
+        <v>6.181244693770243</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4991,22 +4991,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07693711595332327</v>
+        <v>0.07710883707880148</v>
       </c>
       <c r="C43">
-        <v>9310.609667978653</v>
+        <v>9110.047386109622</v>
       </c>
       <c r="D43">
-        <v>13575.80728713287</v>
+        <v>13501.34738621882</v>
       </c>
       <c r="E43">
-        <v>-4875.740476343881</v>
+        <v>-4749.638095388899</v>
       </c>
       <c r="F43">
-        <v>5170.197619154222</v>
+        <v>5296.300000109203</v>
       </c>
       <c r="G43">
         <v>905</v>
@@ -5027,45 +5027,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M43">
-        <v>280.7417307200743</v>
+        <v>292.885390006039</v>
       </c>
       <c r="N43">
-        <v>1454.591602613259</v>
+        <v>1442.447943327295</v>
       </c>
       <c r="O43">
-        <v>363.6479006533148</v>
+        <v>360.6119858318236</v>
       </c>
       <c r="P43">
-        <v>1090.943701959945</v>
+        <v>1081.835957495471</v>
       </c>
       <c r="Q43">
-        <v>2104.943701959945</v>
+        <v>2095.835957495471</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1021014677174971</v>
+        <v>0.1029126501358646</v>
       </c>
       <c r="T43">
-        <v>1.30026484336021</v>
+        <v>1.31899884840334</v>
       </c>
       <c r="U43">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.181244693770243</v>
+        <v>5.924956971385813</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5073,22 +5073,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07710883707880149</v>
+        <v>0.07697305820427969</v>
       </c>
       <c r="C44">
-        <v>9110.047386109612</v>
+        <v>9042.752124450264</v>
       </c>
       <c r="D44">
-        <v>13501.34738621881</v>
+        <v>13560.15450551445</v>
       </c>
       <c r="E44">
-        <v>-4749.6380953889</v>
+        <v>-4623.535714433919</v>
       </c>
       <c r="F44">
-        <v>5296.300000109202</v>
+        <v>5422.402381064184</v>
       </c>
       <c r="G44">
         <v>905</v>
@@ -5109,28 +5109,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M44">
-        <v>292.885390006039</v>
+        <v>299.8588516728494</v>
       </c>
       <c r="N44">
-        <v>1442.447943327295</v>
+        <v>1435.474481660484</v>
       </c>
       <c r="O44">
-        <v>360.6119858318236</v>
+        <v>358.868620415121</v>
       </c>
       <c r="P44">
-        <v>1081.835957495471</v>
+        <v>1076.605861245363</v>
       </c>
       <c r="Q44">
-        <v>2095.835957495471</v>
+        <v>2090.605861245363</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1029126501358646</v>
+        <v>0.1037522950952275</v>
       </c>
       <c r="T44">
-        <v>1.31899884840334</v>
+        <v>1.338390186956756</v>
       </c>
       <c r="U44">
         <v>0.05530000000000001</v>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.924956971385813</v>
+        <v>5.787167274376841</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5155,22 +5155,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07697305820427969</v>
+        <v>0.0768372793297579</v>
       </c>
       <c r="C45">
-        <v>9042.752124450264</v>
+        <v>8975.971390136361</v>
       </c>
       <c r="D45">
-        <v>13560.15450551445</v>
+        <v>13619.47615215552</v>
       </c>
       <c r="E45">
-        <v>-4623.535714433919</v>
+        <v>-4497.433333478938</v>
       </c>
       <c r="F45">
-        <v>5422.402381064184</v>
+        <v>5548.504762019164</v>
       </c>
       <c r="G45">
         <v>905</v>
@@ -5191,28 +5191,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M45">
-        <v>299.8588516728494</v>
+        <v>306.8323133396598</v>
       </c>
       <c r="N45">
-        <v>1435.474481660484</v>
+        <v>1428.501019993674</v>
       </c>
       <c r="O45">
-        <v>358.868620415121</v>
+        <v>357.1252549984184</v>
       </c>
       <c r="P45">
-        <v>1076.605861245363</v>
+        <v>1071.375764995255</v>
       </c>
       <c r="Q45">
-        <v>2090.605861245363</v>
+        <v>2085.375764995255</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1037522950952275</v>
+        <v>0.1046219273745677</v>
       </c>
       <c r="T45">
-        <v>1.338390186956756</v>
+        <v>1.358474073315651</v>
       </c>
       <c r="U45">
         <v>0.05530000000000001</v>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.787167274376841</v>
+        <v>5.655640745413732</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5237,22 +5237,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0768372793297579</v>
+        <v>0.07670150045523612</v>
       </c>
       <c r="C46">
-        <v>8975.971390136361</v>
+        <v>8909.711965551562</v>
       </c>
       <c r="D46">
-        <v>13619.47615215552</v>
+        <v>13679.31910852571</v>
       </c>
       <c r="E46">
-        <v>-4497.433333478938</v>
+        <v>-4371.330952523957</v>
       </c>
       <c r="F46">
-        <v>5548.504762019164</v>
+        <v>5674.607142974146</v>
       </c>
       <c r="G46">
         <v>905</v>
@@ -5273,28 +5273,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M46">
-        <v>306.8323133396598</v>
+        <v>313.8057750064703</v>
       </c>
       <c r="N46">
-        <v>1428.501019993674</v>
+        <v>1421.527558326863</v>
       </c>
       <c r="O46">
-        <v>357.1252549984184</v>
+        <v>355.3818895817158</v>
       </c>
       <c r="P46">
-        <v>1071.375764995255</v>
+        <v>1066.145668745147</v>
       </c>
       <c r="Q46">
-        <v>2085.375764995255</v>
+        <v>2080.145668745147</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1046219273745677</v>
+        <v>0.1055231826458838</v>
       </c>
       <c r="T46">
-        <v>1.358474073315651</v>
+        <v>1.379288282814869</v>
       </c>
       <c r="U46">
         <v>0.05530000000000001</v>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.655640745413732</v>
+        <v>5.529959839960092</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5319,22 +5319,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07670150045523612</v>
+        <v>0.07656572158071431</v>
       </c>
       <c r="C47">
-        <v>8909.711965551562</v>
+        <v>8843.98075281077</v>
       </c>
       <c r="D47">
-        <v>13679.31910852571</v>
+        <v>13739.6902767399</v>
       </c>
       <c r="E47">
-        <v>-4371.330952523957</v>
+        <v>-4245.228571568975</v>
       </c>
       <c r="F47">
-        <v>5674.607142974146</v>
+        <v>5800.709523929127</v>
       </c>
       <c r="G47">
         <v>905</v>
@@ -5355,28 +5355,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M47">
-        <v>313.8057750064703</v>
+        <v>320.7792366732808</v>
       </c>
       <c r="N47">
-        <v>1421.527558326863</v>
+        <v>1414.554096660053</v>
       </c>
       <c r="O47">
-        <v>355.3818895817158</v>
+        <v>353.6385241650132</v>
       </c>
       <c r="P47">
-        <v>1066.145668745147</v>
+        <v>1060.915572495039</v>
       </c>
       <c r="Q47">
-        <v>2080.145668745147</v>
+        <v>2074.91557249504</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1055231826458838</v>
+        <v>0.1064578177420635</v>
       </c>
       <c r="T47">
-        <v>1.379288282814869</v>
+        <v>1.400873388962206</v>
       </c>
       <c r="U47">
         <v>0.05530000000000001</v>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.529959839960092</v>
+        <v>5.40974332170009</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5401,22 +5401,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07656572158071431</v>
+        <v>0.07642994270619252</v>
       </c>
       <c r="C48">
-        <v>8843.98075281077</v>
+        <v>8778.784776413857</v>
       </c>
       <c r="D48">
-        <v>13739.6902767399</v>
+        <v>13800.59668129796</v>
       </c>
       <c r="E48">
-        <v>-4245.228571568975</v>
+        <v>-4119.126190613994</v>
       </c>
       <c r="F48">
-        <v>5800.709523929127</v>
+        <v>5926.811904884108</v>
       </c>
       <c r="G48">
         <v>905</v>
@@ -5437,28 +5437,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M48">
-        <v>320.7792366732808</v>
+        <v>327.7526983400912</v>
       </c>
       <c r="N48">
-        <v>1414.554096660053</v>
+        <v>1407.580634993242</v>
       </c>
       <c r="O48">
-        <v>353.6385241650132</v>
+        <v>351.8951587483106</v>
       </c>
       <c r="P48">
-        <v>1060.915572495039</v>
+        <v>1055.685476244932</v>
       </c>
       <c r="Q48">
-        <v>2074.91557249504</v>
+        <v>2069.685476244932</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1064578177420635</v>
+        <v>0.1074277220871557</v>
       </c>
       <c r="T48">
-        <v>1.400873388962206</v>
+        <v>1.423273027416991</v>
       </c>
       <c r="U48">
         <v>0.05530000000000001</v>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.40974332170009</v>
+        <v>5.29464239996179</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5483,22 +5483,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07642994270619252</v>
+        <v>0.07629416383167073</v>
       </c>
       <c r="C49">
-        <v>8778.784776413857</v>
+        <v>8714.131185970378</v>
       </c>
       <c r="D49">
-        <v>13800.59668129796</v>
+        <v>13862.04547180947</v>
       </c>
       <c r="E49">
-        <v>-4119.126190613994</v>
+        <v>-3993.023809659013</v>
       </c>
       <c r="F49">
-        <v>5926.811904884108</v>
+        <v>6052.91428583909</v>
       </c>
       <c r="G49">
         <v>905</v>
@@ -5519,28 +5519,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M49">
-        <v>327.7526983400912</v>
+        <v>334.7261600069017</v>
       </c>
       <c r="N49">
-        <v>1407.580634993242</v>
+        <v>1400.607173326432</v>
       </c>
       <c r="O49">
-        <v>351.8951587483106</v>
+        <v>350.151793331608</v>
       </c>
       <c r="P49">
-        <v>1055.685476244932</v>
+        <v>1050.455379994824</v>
       </c>
       <c r="Q49">
-        <v>2069.685476244932</v>
+        <v>2064.455379994824</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1074277220871557</v>
+        <v>0.1084349304455206</v>
       </c>
       <c r="T49">
-        <v>1.423273027416991</v>
+        <v>1.446534190427728</v>
       </c>
       <c r="U49">
         <v>0.05530000000000001</v>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.29464239996179</v>
+        <v>5.184337349962587</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07629416383167073</v>
+        <v>0.07615838495714893</v>
       </c>
       <c r="C50">
-        <v>8714.131185970378</v>
+        <v>8650.027258997357</v>
       </c>
       <c r="D50">
-        <v>13862.04547180947</v>
+        <v>13924.04392579143</v>
       </c>
       <c r="E50">
-        <v>-3993.023809659014</v>
+        <v>-3866.921428704033</v>
       </c>
       <c r="F50">
-        <v>6052.914285839089</v>
+        <v>6179.016666794069</v>
       </c>
       <c r="G50">
         <v>905</v>
@@ -5601,28 +5601,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M50">
-        <v>334.7261600069016</v>
+        <v>341.6996216737121</v>
       </c>
       <c r="N50">
-        <v>1400.607173326432</v>
+        <v>1393.633711659621</v>
       </c>
       <c r="O50">
-        <v>350.151793331608</v>
+        <v>348.4084279149054</v>
       </c>
       <c r="P50">
-        <v>1050.455379994824</v>
+        <v>1045.225283744716</v>
       </c>
       <c r="Q50">
-        <v>2064.455379994824</v>
+        <v>2059.225283744716</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1084349304455206</v>
+        <v>0.1094816371708802</v>
       </c>
       <c r="T50">
-        <v>1.446534190427728</v>
+        <v>1.470707555909475</v>
       </c>
       <c r="U50">
         <v>0.05530000000000001</v>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.184337349962587</v>
+        <v>5.078534546902127</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5647,22 +5647,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07615838495714893</v>
+        <v>0.07602260608262715</v>
       </c>
       <c r="C51">
-        <v>8650.027258997357</v>
+        <v>8586.480403792437</v>
       </c>
       <c r="D51">
-        <v>13924.04392579143</v>
+        <v>13986.59945154149</v>
       </c>
       <c r="E51">
-        <v>-3866.921428704033</v>
+        <v>-3740.819047749052</v>
       </c>
       <c r="F51">
-        <v>6179.016666794069</v>
+        <v>6305.119047749051</v>
       </c>
       <c r="G51">
         <v>905</v>
@@ -5683,28 +5683,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M51">
-        <v>341.6996216737121</v>
+        <v>348.6730833405226</v>
       </c>
       <c r="N51">
-        <v>1393.633711659621</v>
+        <v>1386.660249992811</v>
       </c>
       <c r="O51">
-        <v>348.4084279149054</v>
+        <v>346.6650624982027</v>
       </c>
       <c r="P51">
-        <v>1045.225283744716</v>
+        <v>1039.995187494608</v>
       </c>
       <c r="Q51">
-        <v>2059.225283744716</v>
+        <v>2053.995187494608</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1094816371708802</v>
+        <v>0.1105702121652543</v>
       </c>
       <c r="T51">
-        <v>1.470707555909475</v>
+        <v>1.495847856010492</v>
       </c>
       <c r="U51">
         <v>0.05530000000000001</v>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.078534546902127</v>
+        <v>4.976963855964083</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5729,22 +5729,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07602260608262715</v>
+        <v>0.07588682720810536</v>
       </c>
       <c r="C52">
-        <v>8586.480403792437</v>
+        <v>8523.498162384964</v>
       </c>
       <c r="D52">
-        <v>13986.59945154149</v>
+        <v>14049.719591089</v>
       </c>
       <c r="E52">
-        <v>-3740.819047749052</v>
+        <v>-3614.71666679407</v>
       </c>
       <c r="F52">
-        <v>6305.119047749051</v>
+        <v>6431.221428704032</v>
       </c>
       <c r="G52">
         <v>905</v>
@@ -5765,28 +5765,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M52">
-        <v>348.6730833405226</v>
+        <v>355.646545007333</v>
       </c>
       <c r="N52">
-        <v>1386.660249992811</v>
+        <v>1379.686788326</v>
       </c>
       <c r="O52">
-        <v>346.6650624982027</v>
+        <v>344.9216970815001</v>
       </c>
       <c r="P52">
-        <v>1039.995187494608</v>
+        <v>1034.7650912445</v>
       </c>
       <c r="Q52">
-        <v>2053.995187494608</v>
+        <v>2048.765091244501</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1105702121652543</v>
+        <v>0.1117032187920518</v>
       </c>
       <c r="T52">
-        <v>1.495847856010492</v>
+        <v>1.522014290809509</v>
       </c>
       <c r="U52">
         <v>0.05530000000000001</v>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.976963855964083</v>
+        <v>4.879376329376552</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5811,22 +5811,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07588682720810536</v>
+        <v>0.07575104833358356</v>
       </c>
       <c r="C53">
-        <v>8523.498162384964</v>
+        <v>8461.088213567185</v>
       </c>
       <c r="D53">
-        <v>14049.719591089</v>
+        <v>14113.4120232262</v>
       </c>
       <c r="E53">
-        <v>-3614.71666679407</v>
+        <v>-3488.614285839089</v>
       </c>
       <c r="F53">
-        <v>6431.221428704032</v>
+        <v>6557.323809659013</v>
       </c>
       <c r="G53">
         <v>905</v>
@@ -5847,28 +5847,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M53">
-        <v>355.646545007333</v>
+        <v>362.6200066741435</v>
       </c>
       <c r="N53">
-        <v>1379.686788326</v>
+        <v>1372.71332665919</v>
       </c>
       <c r="O53">
-        <v>344.9216970815001</v>
+        <v>343.1783316647975</v>
       </c>
       <c r="P53">
-        <v>1034.7650912445</v>
+        <v>1029.534994994392</v>
       </c>
       <c r="Q53">
-        <v>2048.765091244501</v>
+        <v>2043.534994994392</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1117032187920518</v>
+        <v>0.1128834340282991</v>
       </c>
       <c r="T53">
-        <v>1.522014290809509</v>
+        <v>1.549270993725152</v>
       </c>
       <c r="U53">
         <v>0.05530000000000001</v>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.879376329376552</v>
+        <v>4.785542169196233</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5893,22 +5893,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07575104833358356</v>
+        <v>0.07561526945906177</v>
       </c>
       <c r="C54">
-        <v>8461.088213567185</v>
+        <v>8399.258376008371</v>
       </c>
       <c r="D54">
-        <v>14113.4120232262</v>
+        <v>14177.68456662237</v>
       </c>
       <c r="E54">
-        <v>-3488.614285839089</v>
+        <v>-3362.511904884108</v>
       </c>
       <c r="F54">
-        <v>6557.323809659013</v>
+        <v>6683.426190613995</v>
       </c>
       <c r="G54">
         <v>905</v>
@@ -5929,28 +5929,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M54">
-        <v>362.6200066741435</v>
+        <v>369.593468340954</v>
       </c>
       <c r="N54">
-        <v>1372.71332665919</v>
+        <v>1365.73986499238</v>
       </c>
       <c r="O54">
-        <v>343.1783316647975</v>
+        <v>341.4349662480949</v>
       </c>
       <c r="P54">
-        <v>1029.534994994392</v>
+        <v>1024.304898744285</v>
       </c>
       <c r="Q54">
-        <v>2043.534994994392</v>
+        <v>2038.304898744285</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1128834340282991</v>
+        <v>0.1141138711894931</v>
       </c>
       <c r="T54">
-        <v>1.549270993725152</v>
+        <v>1.577687556339333</v>
       </c>
       <c r="U54">
         <v>0.05530000000000001</v>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.785542169196233</v>
+        <v>4.695248920720833</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5975,22 +5975,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07561526945906177</v>
+        <v>0.07547949058453997</v>
       </c>
       <c r="C55">
-        <v>8399.258376008371</v>
+        <v>8338.016611454397</v>
       </c>
       <c r="D55">
-        <v>14177.68456662237</v>
+        <v>14242.54518302337</v>
       </c>
       <c r="E55">
-        <v>-3362.511904884108</v>
+        <v>-3236.409523929127</v>
       </c>
       <c r="F55">
-        <v>6683.426190613995</v>
+        <v>6809.528571568975</v>
       </c>
       <c r="G55">
         <v>905</v>
@@ -6011,28 +6011,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M55">
-        <v>369.593468340954</v>
+        <v>376.5669300077644</v>
       </c>
       <c r="N55">
-        <v>1365.73986499238</v>
+        <v>1358.766403325569</v>
       </c>
       <c r="O55">
-        <v>341.4349662480949</v>
+        <v>339.6916008313923</v>
       </c>
       <c r="P55">
-        <v>1024.304898744285</v>
+        <v>1019.074802494177</v>
       </c>
       <c r="Q55">
-        <v>2038.304898744285</v>
+        <v>2033.074802494177</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1141138711894931</v>
+        <v>0.1153978056185652</v>
       </c>
       <c r="T55">
-        <v>1.577687556339333</v>
+        <v>1.60733962167587</v>
       </c>
       <c r="U55">
         <v>0.05530000000000001</v>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.695248920720833</v>
+        <v>4.608299866633411</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6057,22 +6057,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07547949058453997</v>
+        <v>0.07534371171001819</v>
       </c>
       <c r="C56">
-        <v>8338.016611454397</v>
+        <v>8277.37102801551</v>
       </c>
       <c r="D56">
-        <v>14242.54518302337</v>
+        <v>14308.00198053947</v>
       </c>
       <c r="E56">
-        <v>-3236.409523929127</v>
+        <v>-3110.307142974146</v>
       </c>
       <c r="F56">
-        <v>6809.528571568975</v>
+        <v>6935.630952523957</v>
       </c>
       <c r="G56">
         <v>905</v>
@@ -6093,28 +6093,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M56">
-        <v>376.5669300077644</v>
+        <v>383.5403916745749</v>
       </c>
       <c r="N56">
-        <v>1358.766403325569</v>
+        <v>1351.792941658759</v>
       </c>
       <c r="O56">
-        <v>339.6916008313923</v>
+        <v>337.9482354146896</v>
       </c>
       <c r="P56">
-        <v>1019.074802494177</v>
+        <v>1013.844706244069</v>
       </c>
       <c r="Q56">
-        <v>2033.074802494177</v>
+        <v>2027.844706244069</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1153978056185652</v>
+        <v>0.1167388038000404</v>
       </c>
       <c r="T56">
-        <v>1.60733962167587</v>
+        <v>1.63830955658292</v>
       </c>
       <c r="U56">
         <v>0.05530000000000001</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.608299866633411</v>
+        <v>4.524512596330984</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6139,22 +6139,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07534371171001819</v>
+        <v>0.07625793283549639</v>
       </c>
       <c r="C57">
-        <v>8277.37102801551</v>
+        <v>7721.801626280031</v>
       </c>
       <c r="D57">
-        <v>14308.00198053947</v>
+        <v>13878.53495975897</v>
       </c>
       <c r="E57">
-        <v>-3110.307142974146</v>
+        <v>-2984.204762019165</v>
       </c>
       <c r="F57">
-        <v>6935.630952523957</v>
+        <v>7061.733333478937</v>
       </c>
       <c r="G57">
         <v>905</v>
@@ -6175,45 +6175,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M57">
-        <v>383.5403916745749</v>
+        <v>408.1681866750826</v>
       </c>
       <c r="N57">
-        <v>1351.792941658759</v>
+        <v>1327.165146658251</v>
       </c>
       <c r="O57">
-        <v>337.9482354146896</v>
+        <v>331.7912866645627</v>
       </c>
       <c r="P57">
-        <v>1013.844706244069</v>
+        <v>995.3738599936883</v>
       </c>
       <c r="Q57">
-        <v>2027.844706244069</v>
+        <v>2009.373859993688</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1167388038000404</v>
+        <v>0.11814075644431</v>
       </c>
       <c r="T57">
-        <v>1.63830955658292</v>
+        <v>1.670687215803926</v>
       </c>
       <c r="U57">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.524512596330984</v>
+        <v>4.2515154046406</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6221,22 +6221,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07625793283549639</v>
+        <v>0.0761409039609746</v>
       </c>
       <c r="C58">
-        <v>7721.801626280031</v>
+        <v>7649.230587978551</v>
       </c>
       <c r="D58">
-        <v>13878.53495975897</v>
+        <v>13932.06630241247</v>
       </c>
       <c r="E58">
-        <v>-2984.204762019165</v>
+        <v>-2858.102381064184</v>
       </c>
       <c r="F58">
-        <v>7061.733333478937</v>
+        <v>7187.835714433919</v>
       </c>
       <c r="G58">
         <v>905</v>
@@ -6257,28 +6257,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M58">
-        <v>408.1681866750826</v>
+        <v>415.4569042942805</v>
       </c>
       <c r="N58">
-        <v>1327.165146658251</v>
+        <v>1319.876429039053</v>
       </c>
       <c r="O58">
-        <v>331.7912866645627</v>
+        <v>329.9691072597632</v>
       </c>
       <c r="P58">
-        <v>995.3738599936883</v>
+        <v>989.9073217792898</v>
       </c>
       <c r="Q58">
-        <v>2009.373859993688</v>
+        <v>2003.90732177929</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.11814075644431</v>
+        <v>0.119607916188313</v>
       </c>
       <c r="T58">
-        <v>1.670687215803926</v>
+        <v>1.704570812663118</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.2515154046406</v>
+        <v>4.176927415085501</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6303,22 +6303,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0761409039609746</v>
+        <v>0.07602387508645281</v>
       </c>
       <c r="C59">
-        <v>7649.230587978551</v>
+        <v>7577.074103586157</v>
       </c>
       <c r="D59">
-        <v>13932.06630241247</v>
+        <v>13986.01219897506</v>
       </c>
       <c r="E59">
-        <v>-2858.102381064184</v>
+        <v>-2732.000000109202</v>
       </c>
       <c r="F59">
-        <v>7187.835714433919</v>
+        <v>7313.9380953889</v>
       </c>
       <c r="G59">
         <v>905</v>
@@ -6339,28 +6339,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M59">
-        <v>415.4569042942805</v>
+        <v>422.7456219134785</v>
       </c>
       <c r="N59">
-        <v>1319.876429039053</v>
+        <v>1312.587711419855</v>
       </c>
       <c r="O59">
-        <v>329.9691072597632</v>
+        <v>328.1469278549637</v>
       </c>
       <c r="P59">
-        <v>989.9073217792898</v>
+        <v>984.4407835648913</v>
       </c>
       <c r="Q59">
-        <v>2003.90732177929</v>
+        <v>1998.440783564891</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.119607916188313</v>
+        <v>0.1211449406820305</v>
       </c>
       <c r="T59">
-        <v>1.704570812663118</v>
+        <v>1.740067914134654</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.176927415085501</v>
+        <v>4.104911425170233</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6385,22 +6385,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07602387508645281</v>
+        <v>0.07590684621193101</v>
       </c>
       <c r="C60">
-        <v>7577.074103586158</v>
+        <v>7505.337007363176</v>
       </c>
       <c r="D60">
-        <v>13986.01219897506</v>
+        <v>14040.37748370706</v>
       </c>
       <c r="E60">
-        <v>-2732.000000109204</v>
+        <v>-2605.897619154222</v>
       </c>
       <c r="F60">
-        <v>7313.938095388899</v>
+        <v>7440.04047634388</v>
       </c>
       <c r="G60">
         <v>905</v>
@@ -6421,28 +6421,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M60">
-        <v>422.7456219134784</v>
+        <v>430.0343395326763</v>
       </c>
       <c r="N60">
-        <v>1312.587711419855</v>
+        <v>1305.298993800657</v>
       </c>
       <c r="O60">
-        <v>328.1469278549638</v>
+        <v>326.3247484501643</v>
       </c>
       <c r="P60">
-        <v>984.4407835648914</v>
+        <v>978.9742453504929</v>
       </c>
       <c r="Q60">
-        <v>1998.440783564891</v>
+        <v>1992.974245350493</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1211449406820305</v>
+        <v>0.1227569419803196</v>
       </c>
       <c r="T60">
-        <v>1.740067914134654</v>
+        <v>1.777296581531629</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.104911425170235</v>
+        <v>4.035336655252094</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6467,22 +6467,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07590684621193101</v>
+        <v>0.07736481733740923</v>
       </c>
       <c r="C61">
-        <v>7505.337007363176</v>
+        <v>6730.71305432868</v>
       </c>
       <c r="D61">
-        <v>14040.37748370706</v>
+        <v>13391.85591162754</v>
       </c>
       <c r="E61">
-        <v>-2605.897619154222</v>
+        <v>-2479.795238199242</v>
       </c>
       <c r="F61">
-        <v>7440.04047634388</v>
+        <v>7566.142857298861</v>
       </c>
       <c r="G61">
         <v>905</v>
@@ -6503,45 +6503,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M61">
-        <v>430.0343395326763</v>
+        <v>463.8045571524202</v>
       </c>
       <c r="N61">
-        <v>1305.298993800657</v>
+        <v>1271.528776180913</v>
       </c>
       <c r="O61">
-        <v>326.3247484501643</v>
+        <v>317.8821940452283</v>
       </c>
       <c r="P61">
-        <v>978.9742453504929</v>
+        <v>953.6465821356849</v>
       </c>
       <c r="Q61">
-        <v>1992.974245350493</v>
+        <v>1967.646582135685</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1227569419803196</v>
+        <v>0.1244495433435231</v>
       </c>
       <c r="T61">
-        <v>1.777296581531629</v>
+        <v>1.816386682298454</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.035336655252094</v>
+        <v>3.741518505095348</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6549,22 +6549,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07736481733740923</v>
+        <v>0.07727403846288744</v>
       </c>
       <c r="C62">
-        <v>6730.71305432868</v>
+        <v>6643.2360823389</v>
       </c>
       <c r="D62">
-        <v>13391.85591162754</v>
+        <v>13430.48132059274</v>
       </c>
       <c r="E62">
-        <v>-2479.795238199242</v>
+        <v>-2353.69285724426</v>
       </c>
       <c r="F62">
-        <v>7566.142857298861</v>
+        <v>7692.245238253842</v>
       </c>
       <c r="G62">
         <v>905</v>
@@ -6585,28 +6585,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M62">
-        <v>463.8045571524202</v>
+        <v>471.5346331049606</v>
       </c>
       <c r="N62">
-        <v>1271.528776180913</v>
+        <v>1263.798700228373</v>
       </c>
       <c r="O62">
-        <v>317.8821940452283</v>
+        <v>315.9496750570933</v>
       </c>
       <c r="P62">
-        <v>953.6465821356849</v>
+        <v>947.8490251712798</v>
       </c>
       <c r="Q62">
-        <v>1967.646582135685</v>
+        <v>1961.84902517128</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1244495433435231</v>
+        <v>0.1262289447766345</v>
       </c>
       <c r="T62">
-        <v>1.816386682298454</v>
+        <v>1.857481403617424</v>
       </c>
       <c r="U62">
         <v>0.06130000000000001</v>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.741518505095348</v>
+        <v>3.68018213615936</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07727403846288744</v>
+        <v>0.07718325958836564</v>
       </c>
       <c r="C63">
-        <v>6643.2360823389</v>
+        <v>6555.982565222827</v>
       </c>
       <c r="D63">
-        <v>13430.48132059274</v>
+        <v>13469.33018443165</v>
       </c>
       <c r="E63">
-        <v>-2353.69285724426</v>
+        <v>-2227.59047628928</v>
       </c>
       <c r="F63">
-        <v>7692.245238253842</v>
+        <v>7818.347619208823</v>
       </c>
       <c r="G63">
         <v>905</v>
@@ -6667,28 +6667,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M63">
-        <v>471.5346331049606</v>
+        <v>479.2647090575009</v>
       </c>
       <c r="N63">
-        <v>1263.798700228373</v>
+        <v>1256.068624275832</v>
       </c>
       <c r="O63">
-        <v>315.9496750570933</v>
+        <v>314.0171560689581</v>
       </c>
       <c r="P63">
-        <v>947.8490251712798</v>
+        <v>942.0514682068743</v>
       </c>
       <c r="Q63">
-        <v>1961.84902517128</v>
+        <v>1956.051468206874</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1262289447766345</v>
+        <v>0.1281019989167517</v>
       </c>
       <c r="T63">
-        <v>1.857481403617424</v>
+        <v>1.900739005005813</v>
       </c>
       <c r="U63">
         <v>0.06130000000000001</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.68018213615936</v>
+        <v>3.620824359769692</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6713,22 +6713,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07718325958836564</v>
+        <v>0.07709248071384385</v>
       </c>
       <c r="C64">
-        <v>6555.982565222827</v>
+        <v>6468.954447695101</v>
       </c>
       <c r="D64">
-        <v>13469.33018443165</v>
+        <v>13508.40444785891</v>
       </c>
       <c r="E64">
-        <v>-2227.59047628928</v>
+        <v>-2101.488095334298</v>
       </c>
       <c r="F64">
-        <v>7818.347619208823</v>
+        <v>7944.450000163804</v>
       </c>
       <c r="G64">
         <v>905</v>
@@ -6749,28 +6749,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M64">
-        <v>479.2647090575009</v>
+        <v>486.9947850100413</v>
       </c>
       <c r="N64">
-        <v>1256.068624275832</v>
+        <v>1248.338548323292</v>
       </c>
       <c r="O64">
-        <v>314.0171560689581</v>
+        <v>312.0846370808231</v>
       </c>
       <c r="P64">
-        <v>942.0514682068743</v>
+        <v>936.2539112424693</v>
       </c>
       <c r="Q64">
-        <v>1956.051468206874</v>
+        <v>1950.253911242469</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1281019989167517</v>
+        <v>0.130076299226605</v>
       </c>
       <c r="T64">
-        <v>1.900739005005813</v>
+        <v>1.946334855117898</v>
       </c>
       <c r="U64">
         <v>0.06130000000000001</v>
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.620824359769692</v>
+        <v>3.563350957233665</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6795,22 +6795,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07709248071384385</v>
+        <v>0.07700170183932206</v>
       </c>
       <c r="C65">
-        <v>6468.954447695101</v>
+        <v>6382.153697102356</v>
       </c>
       <c r="D65">
-        <v>13508.40444785891</v>
+        <v>13547.70607822114</v>
       </c>
       <c r="E65">
-        <v>-2101.488095334298</v>
+        <v>-1975.385714379318</v>
       </c>
       <c r="F65">
-        <v>7944.450000163804</v>
+        <v>8070.552381118785</v>
       </c>
       <c r="G65">
         <v>905</v>
@@ -6831,28 +6831,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M65">
-        <v>486.9947850100413</v>
+        <v>494.7248609625816</v>
       </c>
       <c r="N65">
-        <v>1248.338548323292</v>
+        <v>1240.608472370752</v>
       </c>
       <c r="O65">
-        <v>312.0846370808231</v>
+        <v>310.1521180926879</v>
       </c>
       <c r="P65">
-        <v>936.2539112424693</v>
+        <v>930.4563542780638</v>
       </c>
       <c r="Q65">
-        <v>1950.253911242469</v>
+        <v>1944.456354278064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.130076299226605</v>
+        <v>0.1321602828870057</v>
       </c>
       <c r="T65">
-        <v>1.946334855117898</v>
+        <v>1.994463808013989</v>
       </c>
       <c r="U65">
         <v>0.06130000000000001</v>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.563350957233665</v>
+        <v>3.507673598526889</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6877,22 +6877,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07700170183932206</v>
+        <v>0.07827592296480028</v>
       </c>
       <c r="C66">
-        <v>6382.153697102356</v>
+        <v>5724.495267521763</v>
       </c>
       <c r="D66">
-        <v>13547.70607822114</v>
+        <v>13016.15002959553</v>
       </c>
       <c r="E66">
-        <v>-1975.385714379318</v>
+        <v>-1849.283333424337</v>
       </c>
       <c r="F66">
-        <v>8070.552381118785</v>
+        <v>8196.654762073766</v>
       </c>
       <c r="G66">
         <v>905</v>
@@ -6913,45 +6913,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M66">
-        <v>494.7248609625816</v>
+        <v>525.4055702489284</v>
       </c>
       <c r="N66">
-        <v>1240.608472370752</v>
+        <v>1209.927763084405</v>
       </c>
       <c r="O66">
-        <v>310.1521180926879</v>
+        <v>302.4819407711013</v>
       </c>
       <c r="P66">
-        <v>930.4563542780638</v>
+        <v>907.4458223133038</v>
       </c>
       <c r="Q66">
-        <v>1944.456354278064</v>
+        <v>1921.445822313304</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1321602828870057</v>
+        <v>0.1343633513280008</v>
       </c>
       <c r="T66">
-        <v>1.994463808013989</v>
+        <v>2.045342986789856</v>
       </c>
       <c r="U66">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.507673598526889</v>
+        <v>3.302845328630912</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6959,22 +6959,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07827592296480028</v>
+        <v>0.07820614409027848</v>
       </c>
       <c r="C67">
-        <v>5724.495267521763</v>
+        <v>5626.420050092986</v>
       </c>
       <c r="D67">
-        <v>13016.15002959553</v>
+        <v>13044.17719312173</v>
       </c>
       <c r="E67">
-        <v>-1849.283333424337</v>
+        <v>-1723.180952469354</v>
       </c>
       <c r="F67">
-        <v>8196.654762073766</v>
+        <v>8322.757143028748</v>
       </c>
       <c r="G67">
         <v>905</v>
@@ -6995,28 +6995,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M67">
-        <v>525.4055702489284</v>
+        <v>533.4887328681427</v>
       </c>
       <c r="N67">
-        <v>1209.927763084405</v>
+        <v>1201.844600465191</v>
       </c>
       <c r="O67">
-        <v>302.4819407711013</v>
+        <v>300.4611501162977</v>
       </c>
       <c r="P67">
-        <v>907.4458223133038</v>
+        <v>901.3834503488931</v>
       </c>
       <c r="Q67">
-        <v>1921.445822313304</v>
+        <v>1915.383450348893</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1343633513280008</v>
+        <v>0.1366960120302308</v>
       </c>
       <c r="T67">
-        <v>2.045342986789856</v>
+        <v>2.099215058434892</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.302845328630912</v>
+        <v>3.252802217591049</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7041,22 +7041,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07820614409027848</v>
+        <v>0.07813636521575669</v>
       </c>
       <c r="C68">
-        <v>5626.420050092986</v>
+        <v>5528.465792698764</v>
       </c>
       <c r="D68">
-        <v>13044.17719312173</v>
+        <v>13072.32531668249</v>
       </c>
       <c r="E68">
-        <v>-1723.180952469354</v>
+        <v>-1597.078571514374</v>
       </c>
       <c r="F68">
-        <v>8322.757143028748</v>
+        <v>8448.859523983729</v>
       </c>
       <c r="G68">
         <v>905</v>
@@ -7077,28 +7077,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M68">
-        <v>533.4887328681427</v>
+        <v>541.5718954873571</v>
       </c>
       <c r="N68">
-        <v>1201.844600465191</v>
+        <v>1193.761437845976</v>
       </c>
       <c r="O68">
-        <v>300.4611501162977</v>
+        <v>298.4403594614941</v>
       </c>
       <c r="P68">
-        <v>901.3834503488931</v>
+        <v>895.3210783844822</v>
       </c>
       <c r="Q68">
-        <v>1915.383450348893</v>
+        <v>1909.321078384482</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1366960120302308</v>
+        <v>0.1391700461083536</v>
       </c>
       <c r="T68">
-        <v>2.099215058434892</v>
+        <v>2.156352104119021</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.252802217591049</v>
+        <v>3.204252930761331</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7123,22 +7123,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07813636521575669</v>
+        <v>0.07806658634123489</v>
       </c>
       <c r="C69">
-        <v>5528.465792698764</v>
+        <v>5430.633280094102</v>
       </c>
       <c r="D69">
-        <v>13072.32531668249</v>
+        <v>13100.59518503281</v>
       </c>
       <c r="E69">
-        <v>-1597.078571514374</v>
+        <v>-1470.976190559393</v>
       </c>
       <c r="F69">
-        <v>8448.859523983729</v>
+        <v>8574.961904938709</v>
       </c>
       <c r="G69">
         <v>905</v>
@@ -7159,28 +7159,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M69">
-        <v>541.5718954873571</v>
+        <v>549.6550581065713</v>
       </c>
       <c r="N69">
-        <v>1193.761437845976</v>
+        <v>1185.678275226762</v>
       </c>
       <c r="O69">
-        <v>298.4403594614941</v>
+        <v>296.4195688066906</v>
       </c>
       <c r="P69">
-        <v>895.3210783844822</v>
+        <v>889.2587064200717</v>
       </c>
       <c r="Q69">
-        <v>1909.321078384482</v>
+        <v>1903.258706420072</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1391700461083536</v>
+        <v>0.141798707316359</v>
       </c>
       <c r="T69">
-        <v>2.156352104119021</v>
+        <v>2.217060215158408</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.204252930761331</v>
+        <v>3.157131564132489</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7205,22 +7205,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07806658634123489</v>
+        <v>0.0779968074667131</v>
       </c>
       <c r="C70">
-        <v>5430.633280094102</v>
+        <v>5332.923303837077</v>
       </c>
       <c r="D70">
-        <v>13100.59518503281</v>
+        <v>13128.98758973077</v>
       </c>
       <c r="E70">
-        <v>-1470.976190559393</v>
+        <v>-1344.873809604411</v>
       </c>
       <c r="F70">
-        <v>8574.961904938709</v>
+        <v>8701.064285893692</v>
       </c>
       <c r="G70">
         <v>905</v>
@@ -7241,28 +7241,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M70">
-        <v>549.6550581065713</v>
+        <v>557.7382207257857</v>
       </c>
       <c r="N70">
-        <v>1185.678275226762</v>
+        <v>1177.595112607548</v>
       </c>
       <c r="O70">
-        <v>296.4195688066906</v>
+        <v>294.398778151887</v>
       </c>
       <c r="P70">
-        <v>889.2587064200717</v>
+        <v>883.1963344556609</v>
       </c>
       <c r="Q70">
-        <v>1903.258706420072</v>
+        <v>1897.196334455661</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.141798707316359</v>
+        <v>0.1445969595700423</v>
       </c>
       <c r="T70">
-        <v>2.217060215158408</v>
+        <v>2.281684978522916</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.157131564132489</v>
+        <v>3.111376034217525</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7287,22 +7287,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0779968074667131</v>
+        <v>0.07792702859219131</v>
       </c>
       <c r="C71">
-        <v>5332.923303837077</v>
+        <v>5235.336662362739</v>
       </c>
       <c r="D71">
-        <v>13128.98758973077</v>
+        <v>13157.50332921141</v>
       </c>
       <c r="E71">
-        <v>-1344.873809604411</v>
+        <v>-1218.77142864943</v>
       </c>
       <c r="F71">
-        <v>8701.064285893692</v>
+        <v>8827.166666848672</v>
       </c>
       <c r="G71">
         <v>905</v>
@@ -7323,28 +7323,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M71">
-        <v>557.7382207257857</v>
+        <v>565.821383345</v>
       </c>
       <c r="N71">
-        <v>1177.595112607548</v>
+        <v>1169.511949988334</v>
       </c>
       <c r="O71">
-        <v>294.398778151887</v>
+        <v>292.3779874970834</v>
       </c>
       <c r="P71">
-        <v>883.1963344556609</v>
+        <v>877.1339624912501</v>
       </c>
       <c r="Q71">
-        <v>1897.196334455661</v>
+        <v>1891.13396249125</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1445969595700423</v>
+        <v>0.147581761973971</v>
       </c>
       <c r="T71">
-        <v>2.281684978522916</v>
+        <v>2.350618059445059</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.111376034217525</v>
+        <v>3.066927805157274</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7369,22 +7369,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07792702859219131</v>
+        <v>0.07785724971766952</v>
       </c>
       <c r="C72">
-        <v>5235.336662362739</v>
+        <v>5137.874161057911</v>
       </c>
       <c r="D72">
-        <v>13157.50332921141</v>
+        <v>13186.14320886156</v>
       </c>
       <c r="E72">
-        <v>-1218.77142864943</v>
+        <v>-1092.66904769445</v>
       </c>
       <c r="F72">
-        <v>8827.166666848672</v>
+        <v>8953.269047803653</v>
       </c>
       <c r="G72">
         <v>905</v>
@@ -7405,28 +7405,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M72">
-        <v>565.821383345</v>
+        <v>573.9045459642142</v>
       </c>
       <c r="N72">
-        <v>1169.511949988334</v>
+        <v>1161.428787369119</v>
       </c>
       <c r="O72">
-        <v>292.3779874970834</v>
+        <v>290.3571968422798</v>
       </c>
       <c r="P72">
-        <v>877.1339624912501</v>
+        <v>871.0715905268394</v>
       </c>
       <c r="Q72">
-        <v>1891.13396249125</v>
+        <v>1885.071590526839</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.147581761973971</v>
+        <v>0.1507724128195501</v>
       </c>
       <c r="T72">
-        <v>2.350618059445059</v>
+        <v>2.424305145948039</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.066927805157274</v>
+        <v>3.023731638887454</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7451,22 +7451,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07785724971766952</v>
+        <v>0.08199947084314772</v>
       </c>
       <c r="C73">
-        <v>5137.874161057913</v>
+        <v>3502.912128535223</v>
       </c>
       <c r="D73">
-        <v>13186.14320886156</v>
+        <v>11677.28355729386</v>
       </c>
       <c r="E73">
-        <v>-1092.669047694451</v>
+        <v>-966.5666667394689</v>
       </c>
       <c r="F73">
-        <v>8953.269047803651</v>
+        <v>9079.371428758634</v>
       </c>
       <c r="G73">
         <v>905</v>
@@ -7487,45 +7487,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M73">
-        <v>573.9045459642141</v>
+        <v>652.8068057277458</v>
       </c>
       <c r="N73">
-        <v>1161.428787369119</v>
+        <v>1082.526527605588</v>
       </c>
       <c r="O73">
-        <v>290.3571968422798</v>
+        <v>270.6316319013969</v>
       </c>
       <c r="P73">
-        <v>871.0715905268396</v>
+        <v>811.8948957041907</v>
       </c>
       <c r="Q73">
-        <v>1885.07159052684</v>
+        <v>1825.894895704191</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1507724128195501</v>
+        <v>0.1541909672969561</v>
       </c>
       <c r="T73">
-        <v>2.424305145948038</v>
+        <v>2.503255595772659</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.023731638887454</v>
+        <v>2.658264770078175</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7533,22 +7533,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08199947084314772</v>
+        <v>0.08198819196862593</v>
       </c>
       <c r="C74">
-        <v>3502.912128535223</v>
+        <v>3380.449239050618</v>
       </c>
       <c r="D74">
-        <v>11677.28355729386</v>
+        <v>11680.92304876423</v>
       </c>
       <c r="E74">
-        <v>-966.5666667394689</v>
+        <v>-840.4642857844883</v>
       </c>
       <c r="F74">
-        <v>9079.371428758634</v>
+        <v>9205.473809713614</v>
       </c>
       <c r="G74">
         <v>905</v>
@@ -7569,28 +7569,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M74">
-        <v>652.8068057277458</v>
+        <v>661.8735669184089</v>
       </c>
       <c r="N74">
-        <v>1082.526527605588</v>
+        <v>1073.459766414925</v>
       </c>
       <c r="O74">
-        <v>270.6316319013969</v>
+        <v>268.3649416037312</v>
       </c>
       <c r="P74">
-        <v>811.8948957041907</v>
+        <v>805.0948248111935</v>
       </c>
       <c r="Q74">
-        <v>1825.894895704191</v>
+        <v>1819.094824811194</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1541909672969561</v>
+        <v>0.1578627480319479</v>
       </c>
       <c r="T74">
-        <v>2.503255595772659</v>
+        <v>2.588054227065771</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.658264770078175</v>
+        <v>2.621850184186693</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7615,22 +7615,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08198819196862593</v>
+        <v>0.08197691309410414</v>
       </c>
       <c r="C75">
-        <v>3380.449239050618</v>
+        <v>3257.988618934187</v>
       </c>
       <c r="D75">
-        <v>11680.92304876423</v>
+        <v>11684.56480960278</v>
       </c>
       <c r="E75">
-        <v>-840.4642857844883</v>
+        <v>-714.3619048295077</v>
       </c>
       <c r="F75">
-        <v>9205.473809713614</v>
+        <v>9331.576190668595</v>
       </c>
       <c r="G75">
         <v>905</v>
@@ -7651,28 +7651,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M75">
-        <v>661.8735669184089</v>
+        <v>670.940328109072</v>
       </c>
       <c r="N75">
-        <v>1073.459766414925</v>
+        <v>1064.393005224262</v>
       </c>
       <c r="O75">
-        <v>268.3649416037312</v>
+        <v>266.0982513060654</v>
       </c>
       <c r="P75">
-        <v>805.0948248111935</v>
+        <v>798.2947539181962</v>
       </c>
       <c r="Q75">
-        <v>1819.094824811194</v>
+        <v>1812.294753918196</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1578627480319479</v>
+        <v>0.1618169734388621</v>
       </c>
       <c r="T75">
-        <v>2.588054227065771</v>
+        <v>2.679375829996814</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.621850184186693</v>
+        <v>2.586419776292278</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7697,22 +7697,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08197691309410414</v>
+        <v>0.08196563421958235</v>
       </c>
       <c r="C76">
-        <v>3257.988618934187</v>
+        <v>3135.530270309153</v>
       </c>
       <c r="D76">
-        <v>11684.56480960278</v>
+        <v>11688.20884193273</v>
       </c>
       <c r="E76">
-        <v>-714.3619048295077</v>
+        <v>-588.2595238745271</v>
       </c>
       <c r="F76">
-        <v>9331.576190668595</v>
+        <v>9457.678571623575</v>
       </c>
       <c r="G76">
         <v>905</v>
@@ -7733,28 +7733,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M76">
-        <v>670.940328109072</v>
+        <v>680.0070892997351</v>
       </c>
       <c r="N76">
-        <v>1064.393005224262</v>
+        <v>1055.326244033598</v>
       </c>
       <c r="O76">
-        <v>266.0982513060654</v>
+        <v>263.8315610083996</v>
       </c>
       <c r="P76">
-        <v>798.2947539181962</v>
+        <v>791.4946830251988</v>
       </c>
       <c r="Q76">
-        <v>1812.294753918196</v>
+        <v>1805.494683025199</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1618169734388621</v>
+        <v>0.1660875368783294</v>
       </c>
       <c r="T76">
-        <v>2.679375829996814</v>
+        <v>2.778003161162342</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.586419776292278</v>
+        <v>2.551934179275047</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7779,22 +7779,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08196563421958235</v>
+        <v>0.08195435534506054</v>
       </c>
       <c r="C77">
-        <v>3135.530270309153</v>
+        <v>3013.074195301399</v>
       </c>
       <c r="D77">
-        <v>11688.20884193273</v>
+        <v>11691.85514787996</v>
       </c>
       <c r="E77">
-        <v>-588.2595238745271</v>
+        <v>-462.1571429195446</v>
       </c>
       <c r="F77">
-        <v>9457.678571623575</v>
+        <v>9583.780952578558</v>
       </c>
       <c r="G77">
         <v>905</v>
@@ -7815,28 +7815,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M77">
-        <v>680.0070892997351</v>
+        <v>689.0738504903984</v>
       </c>
       <c r="N77">
-        <v>1055.326244033598</v>
+        <v>1046.259482842935</v>
       </c>
       <c r="O77">
-        <v>263.8315610083996</v>
+        <v>261.5648707107338</v>
       </c>
       <c r="P77">
-        <v>791.4946830251988</v>
+        <v>784.6946121322013</v>
       </c>
       <c r="Q77">
-        <v>1805.494683025199</v>
+        <v>1798.694612132201</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1660875368783294</v>
+        <v>0.170713980604419</v>
       </c>
       <c r="T77">
-        <v>2.778003161162342</v>
+        <v>2.884849436591662</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.551934179275047</v>
+        <v>2.518356097968796</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7861,22 +7861,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08195435534506054</v>
+        <v>0.08419532647053878</v>
       </c>
       <c r="C78">
-        <v>3013.074195301399</v>
+        <v>2204.568193953255</v>
       </c>
       <c r="D78">
-        <v>11691.85514787996</v>
+        <v>11009.45152748679</v>
       </c>
       <c r="E78">
-        <v>-462.1571429195446</v>
+        <v>-336.054761964564</v>
       </c>
       <c r="F78">
-        <v>9583.780952578558</v>
+        <v>9709.883333533538</v>
       </c>
       <c r="G78">
         <v>905</v>
@@ -7897,45 +7897,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M78">
-        <v>689.0738504903984</v>
+        <v>736.0091566818422</v>
       </c>
       <c r="N78">
-        <v>1046.259482842935</v>
+        <v>999.3241766514913</v>
       </c>
       <c r="O78">
-        <v>261.5648707107338</v>
+        <v>249.8310441628728</v>
       </c>
       <c r="P78">
-        <v>784.6946121322013</v>
+        <v>749.4931324886185</v>
       </c>
       <c r="Q78">
-        <v>1798.694612132201</v>
+        <v>1763.493132488618</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.170713980604419</v>
+        <v>0.1757427237849512</v>
       </c>
       <c r="T78">
-        <v>2.884849436591662</v>
+        <v>3.000986692493099</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.518356097968796</v>
+        <v>2.357760521834749</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7943,22 +7943,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08419532647053878</v>
+        <v>0.08421329759601698</v>
       </c>
       <c r="C79">
-        <v>2204.568193953255</v>
+        <v>2073.315194664818</v>
       </c>
       <c r="D79">
-        <v>11009.45152748679</v>
+        <v>11004.30090915334</v>
       </c>
       <c r="E79">
-        <v>-336.054761964564</v>
+        <v>-209.9523810095834</v>
       </c>
       <c r="F79">
-        <v>9709.883333533538</v>
+        <v>9835.985714488519</v>
       </c>
       <c r="G79">
         <v>905</v>
@@ -7979,28 +7979,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M79">
-        <v>736.0091566818422</v>
+        <v>745.5677171582298</v>
       </c>
       <c r="N79">
-        <v>999.3241766514913</v>
+        <v>989.7656161751037</v>
       </c>
       <c r="O79">
-        <v>249.8310441628728</v>
+        <v>247.4414040437759</v>
       </c>
       <c r="P79">
-        <v>749.4931324886185</v>
+        <v>742.3242121313277</v>
       </c>
       <c r="Q79">
-        <v>1763.493132488618</v>
+        <v>1756.324212131328</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1757427237849512</v>
+        <v>0.1812286254364408</v>
       </c>
       <c r="T79">
-        <v>3.000986692493099</v>
+        <v>3.12768188074921</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.357760521834749</v>
+        <v>2.327532822836867</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8025,22 +8025,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08421329759601698</v>
+        <v>0.08423126872149519</v>
       </c>
       <c r="C80">
-        <v>2073.315194664818</v>
+        <v>1942.067012412677</v>
       </c>
       <c r="D80">
-        <v>11004.30090915334</v>
+        <v>10999.15510785618</v>
       </c>
       <c r="E80">
-        <v>-209.9523810095834</v>
+        <v>-83.85000005460097</v>
       </c>
       <c r="F80">
-        <v>9835.985714488519</v>
+        <v>9962.088095443502</v>
       </c>
       <c r="G80">
         <v>905</v>
@@ -8061,28 +8061,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M80">
-        <v>745.5677171582298</v>
+        <v>755.1262776346175</v>
       </c>
       <c r="N80">
-        <v>989.7656161751037</v>
+        <v>980.207055698716</v>
       </c>
       <c r="O80">
-        <v>247.4414040437759</v>
+        <v>245.051763924679</v>
       </c>
       <c r="P80">
-        <v>742.3242121313277</v>
+        <v>735.155291774037</v>
       </c>
       <c r="Q80">
-        <v>1756.324212131328</v>
+        <v>1749.155291774037</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1812286254364408</v>
+        <v>0.1872369939118818</v>
       </c>
       <c r="T80">
-        <v>3.12768188074921</v>
+        <v>3.266443277410666</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.327532822836867</v>
+        <v>2.298070382041463</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8107,22 +8107,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08423126872149519</v>
+        <v>0.0842492398469734</v>
       </c>
       <c r="C81">
-        <v>1942.067012412677</v>
+        <v>1810.823640442421</v>
       </c>
       <c r="D81">
-        <v>10999.15510785618</v>
+        <v>10994.0141168409</v>
       </c>
       <c r="E81">
-        <v>-83.85000005460097</v>
+        <v>42.25238090037965</v>
       </c>
       <c r="F81">
-        <v>9962.088095443502</v>
+        <v>10088.19047639848</v>
       </c>
       <c r="G81">
         <v>905</v>
@@ -8143,28 +8143,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M81">
-        <v>755.1262776346175</v>
+        <v>764.684838111005</v>
       </c>
       <c r="N81">
-        <v>980.207055698716</v>
+        <v>970.6484952223285</v>
       </c>
       <c r="O81">
-        <v>245.051763924679</v>
+        <v>242.6621238055821</v>
       </c>
       <c r="P81">
-        <v>735.155291774037</v>
+        <v>727.9863714167464</v>
       </c>
       <c r="Q81">
-        <v>1749.155291774037</v>
+        <v>1741.986371416746</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1872369939118818</v>
+        <v>0.193846199234867</v>
       </c>
       <c r="T81">
-        <v>3.266443277410666</v>
+        <v>3.419080813738268</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.298070382041463</v>
+        <v>2.269344502265946</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8189,22 +8189,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0842492398469734</v>
+        <v>0.0842672109724516</v>
       </c>
       <c r="C82">
-        <v>1810.823640442421</v>
+        <v>1679.585072012233</v>
       </c>
       <c r="D82">
-        <v>10994.0141168409</v>
+        <v>10988.8779293657</v>
       </c>
       <c r="E82">
-        <v>42.25238090037965</v>
+        <v>168.3547618553603</v>
       </c>
       <c r="F82">
-        <v>10088.19047639848</v>
+        <v>10214.29285735346</v>
       </c>
       <c r="G82">
         <v>905</v>
@@ -8225,28 +8225,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M82">
-        <v>764.684838111005</v>
+        <v>774.2433985873926</v>
       </c>
       <c r="N82">
-        <v>970.6484952223285</v>
+        <v>961.0899347459409</v>
       </c>
       <c r="O82">
-        <v>242.6621238055821</v>
+        <v>240.2724836864852</v>
       </c>
       <c r="P82">
-        <v>727.9863714167464</v>
+        <v>720.8174510594557</v>
       </c>
       <c r="Q82">
-        <v>1741.986371416746</v>
+        <v>1734.817451059456</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.193846199234867</v>
+        <v>0.2011511103813242</v>
       </c>
       <c r="T82">
-        <v>3.419080813738268</v>
+        <v>3.587785459152985</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.269344502265946</v>
+        <v>2.241327903472539</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8271,22 +8271,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0842672109724516</v>
+        <v>0.0842851820979298</v>
       </c>
       <c r="C83">
-        <v>1679.585072012233</v>
+        <v>1548.351300392897</v>
       </c>
       <c r="D83">
-        <v>10988.8779293657</v>
+        <v>10983.74653870134</v>
       </c>
       <c r="E83">
-        <v>168.3547618553603</v>
+        <v>294.4571428103409</v>
       </c>
       <c r="F83">
-        <v>10214.29285735346</v>
+        <v>10340.39523830844</v>
       </c>
       <c r="G83">
         <v>905</v>
@@ -8307,28 +8307,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M83">
-        <v>774.2433985873926</v>
+        <v>783.80195906378</v>
       </c>
       <c r="N83">
-        <v>961.0899347459409</v>
+        <v>951.5313742695535</v>
       </c>
       <c r="O83">
-        <v>240.2724836864852</v>
+        <v>237.8828435673884</v>
       </c>
       <c r="P83">
-        <v>720.8174510594557</v>
+        <v>713.6485307021651</v>
       </c>
       <c r="Q83">
-        <v>1734.817451059456</v>
+        <v>1727.648530702165</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2011511103813242</v>
+        <v>0.2092676783218323</v>
       </c>
       <c r="T83">
-        <v>3.587785459152985</v>
+        <v>3.775235065169337</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.241327903472539</v>
+        <v>2.21399463635702</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8353,22 +8353,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0842851820979298</v>
+        <v>0.08430315322340801</v>
       </c>
       <c r="C84">
-        <v>1548.351300392897</v>
+        <v>1417.122318867763</v>
       </c>
       <c r="D84">
-        <v>10983.74653870134</v>
+        <v>10978.61993813119</v>
       </c>
       <c r="E84">
-        <v>294.4571428103409</v>
+        <v>420.5595237653233</v>
       </c>
       <c r="F84">
-        <v>10340.39523830844</v>
+        <v>10466.49761926343</v>
       </c>
       <c r="G84">
         <v>905</v>
@@ -8389,28 +8389,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M84">
-        <v>783.80195906378</v>
+        <v>793.3605195401677</v>
       </c>
       <c r="N84">
-        <v>951.5313742695535</v>
+        <v>941.9728137931658</v>
       </c>
       <c r="O84">
-        <v>237.8828435673884</v>
+        <v>235.4932034482914</v>
       </c>
       <c r="P84">
-        <v>713.6485307021651</v>
+        <v>706.4796103448743</v>
       </c>
       <c r="Q84">
-        <v>1727.648530702165</v>
+        <v>1720.479610344874</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2092676783218323</v>
+        <v>0.2183391366082825</v>
       </c>
       <c r="T84">
-        <v>3.775235065169337</v>
+        <v>3.984737566011143</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.21399463635702</v>
+        <v>2.187320002184043</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8435,22 +8435,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08430315322340801</v>
+        <v>0.08432112434888622</v>
       </c>
       <c r="C85">
-        <v>1417.122318867763</v>
+        <v>1285.898120732711</v>
       </c>
       <c r="D85">
-        <v>10978.61993813119</v>
+        <v>10973.49812095112</v>
       </c>
       <c r="E85">
-        <v>420.5595237653233</v>
+        <v>546.6619047203039</v>
       </c>
       <c r="F85">
-        <v>10466.49761926343</v>
+        <v>10592.60000021841</v>
       </c>
       <c r="G85">
         <v>905</v>
@@ -8471,28 +8471,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M85">
-        <v>793.3605195401677</v>
+        <v>802.9190800165553</v>
       </c>
       <c r="N85">
-        <v>941.9728137931658</v>
+        <v>932.4142533167782</v>
       </c>
       <c r="O85">
-        <v>235.4932034482914</v>
+        <v>233.1035633291945</v>
       </c>
       <c r="P85">
-        <v>706.4796103448743</v>
+        <v>699.3106899875836</v>
       </c>
       <c r="Q85">
-        <v>1720.479610344874</v>
+        <v>1713.310689987584</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2183391366082825</v>
+        <v>0.228544527180539</v>
       </c>
       <c r="T85">
-        <v>3.984737566011143</v>
+        <v>4.220427879458176</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.187320002184043</v>
+        <v>2.161280478348519</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8517,22 +8517,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08432112434888622</v>
+        <v>0.08433909547436444</v>
       </c>
       <c r="C86">
-        <v>1285.898120732712</v>
+        <v>1154.67869929613</v>
       </c>
       <c r="D86">
-        <v>10973.49812095112</v>
+        <v>10968.38108046952</v>
       </c>
       <c r="E86">
-        <v>546.6619047203021</v>
+        <v>672.7642856752846</v>
       </c>
       <c r="F86">
-        <v>10592.6000002184</v>
+        <v>10718.70238117339</v>
       </c>
       <c r="G86">
         <v>905</v>
@@ -8553,28 +8553,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M86">
-        <v>802.9190800165551</v>
+        <v>812.4776404929428</v>
       </c>
       <c r="N86">
-        <v>932.4142533167784</v>
+        <v>922.8556928403907</v>
       </c>
       <c r="O86">
-        <v>233.1035633291946</v>
+        <v>230.7139232100977</v>
       </c>
       <c r="P86">
-        <v>699.3106899875838</v>
+        <v>692.1417696302931</v>
       </c>
       <c r="Q86">
-        <v>1713.310689987584</v>
+        <v>1706.141769630293</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2285445271805389</v>
+        <v>0.2401106364957629</v>
       </c>
       <c r="T86">
-        <v>4.220427879458172</v>
+        <v>4.487543568031475</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.16128047834852</v>
+        <v>2.135853649191478</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8599,22 +8599,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08433909547436444</v>
+        <v>0.08435706659984264</v>
       </c>
       <c r="C87">
-        <v>1154.67869929613</v>
+        <v>1023.464047878886</v>
       </c>
       <c r="D87">
-        <v>10968.38108046952</v>
+        <v>10963.26881000725</v>
       </c>
       <c r="E87">
-        <v>672.7642856752846</v>
+        <v>798.8666666302652</v>
       </c>
       <c r="F87">
-        <v>10718.70238117339</v>
+        <v>10844.80476212837</v>
       </c>
       <c r="G87">
         <v>905</v>
@@ -8635,28 +8635,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M87">
-        <v>812.4776404929428</v>
+        <v>822.0362009693304</v>
       </c>
       <c r="N87">
-        <v>922.8556928403907</v>
+        <v>913.2971323640031</v>
       </c>
       <c r="O87">
-        <v>230.7139232100977</v>
+        <v>228.3242830910008</v>
       </c>
       <c r="P87">
-        <v>692.1417696302931</v>
+        <v>684.9728492730023</v>
       </c>
       <c r="Q87">
-        <v>1706.141769630293</v>
+        <v>1698.972849273002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2401106364957629</v>
+        <v>0.2533290471417331</v>
       </c>
       <c r="T87">
-        <v>4.487543568031475</v>
+        <v>4.792818640686677</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.135853649191478</v>
+        <v>2.11101814164274</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8681,22 +8681,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08435706659984264</v>
+        <v>0.08437503772532085</v>
       </c>
       <c r="C88">
-        <v>1023.464047878886</v>
+        <v>892.2541598142852</v>
       </c>
       <c r="D88">
-        <v>10963.26881000725</v>
+        <v>10958.16130289763</v>
       </c>
       <c r="E88">
-        <v>798.8666666302652</v>
+        <v>924.9690475852458</v>
       </c>
       <c r="F88">
-        <v>10844.80476212837</v>
+        <v>10970.90714308335</v>
       </c>
       <c r="G88">
         <v>905</v>
@@ -8717,28 +8717,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M88">
-        <v>822.0362009693304</v>
+        <v>831.5947614457178</v>
       </c>
       <c r="N88">
-        <v>913.2971323640031</v>
+        <v>903.7385718876156</v>
       </c>
       <c r="O88">
-        <v>228.3242830910008</v>
+        <v>225.9346429719039</v>
       </c>
       <c r="P88">
-        <v>684.9728492730023</v>
+        <v>677.8039289157117</v>
       </c>
       <c r="Q88">
-        <v>1698.972849273002</v>
+        <v>1691.803928915712</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2533290471417331</v>
+        <v>0.2685810594255449</v>
       </c>
       <c r="T88">
-        <v>4.792818640686677</v>
+        <v>5.145059109134987</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.11101814164274</v>
+        <v>2.086753565302019</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8763,22 +8763,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08437503772532085</v>
+        <v>0.08439300885079906</v>
       </c>
       <c r="C89">
-        <v>892.2541598142852</v>
+        <v>761.0490284480529</v>
       </c>
       <c r="D89">
-        <v>10958.16130289763</v>
+        <v>10953.05855248638</v>
       </c>
       <c r="E89">
-        <v>924.9690475852458</v>
+        <v>1051.071428540226</v>
       </c>
       <c r="F89">
-        <v>10970.90714308335</v>
+        <v>11097.00952403833</v>
       </c>
       <c r="G89">
         <v>905</v>
@@ -8799,28 +8799,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M89">
-        <v>831.5947614457178</v>
+        <v>841.1533219221054</v>
       </c>
       <c r="N89">
-        <v>903.7385718876156</v>
+        <v>894.1800114112281</v>
       </c>
       <c r="O89">
-        <v>225.9346429719039</v>
+        <v>223.545002852807</v>
       </c>
       <c r="P89">
-        <v>677.8039289157117</v>
+        <v>670.6350085584211</v>
       </c>
       <c r="Q89">
-        <v>1691.803928915712</v>
+        <v>1684.635008558421</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2685810594255449</v>
+        <v>0.2863750737566588</v>
       </c>
       <c r="T89">
-        <v>5.145059109134987</v>
+        <v>5.556006322324683</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.086753565302019</v>
+        <v>2.063040456605405</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8845,22 +8845,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08439300885079906</v>
+        <v>0.08441097997627726</v>
       </c>
       <c r="C90">
-        <v>761.0490284480529</v>
+        <v>629.8486471383076</v>
       </c>
       <c r="D90">
-        <v>10953.05855248638</v>
+        <v>10947.96055213162</v>
       </c>
       <c r="E90">
-        <v>1051.071428540226</v>
+        <v>1177.173809495209</v>
       </c>
       <c r="F90">
-        <v>11097.00952403833</v>
+        <v>11223.11190499331</v>
       </c>
       <c r="G90">
         <v>905</v>
@@ -8881,28 +8881,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M90">
-        <v>841.1533219221054</v>
+        <v>850.7118823984931</v>
       </c>
       <c r="N90">
-        <v>894.1800114112281</v>
+        <v>884.6214509348404</v>
       </c>
       <c r="O90">
-        <v>223.545002852807</v>
+        <v>221.1553627337101</v>
       </c>
       <c r="P90">
-        <v>670.6350085584211</v>
+        <v>663.4660882011303</v>
       </c>
       <c r="Q90">
-        <v>1684.635008558421</v>
+        <v>1677.46608820113</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2863750737566588</v>
+        <v>0.3074043634207024</v>
       </c>
       <c r="T90">
-        <v>5.556006322324683</v>
+        <v>6.041671210639779</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.063040456605405</v>
+        <v>2.039860226755906</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8927,22 +8927,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08441097997627726</v>
+        <v>0.08442895110175547</v>
       </c>
       <c r="C91">
-        <v>629.8486471383076</v>
+        <v>498.653009255524</v>
       </c>
       <c r="D91">
-        <v>10947.96055213162</v>
+        <v>10942.86729520382</v>
       </c>
       <c r="E91">
-        <v>1177.173809495209</v>
+        <v>1303.276190450189</v>
       </c>
       <c r="F91">
-        <v>11223.11190499331</v>
+        <v>11349.21428594829</v>
       </c>
       <c r="G91">
         <v>905</v>
@@ -8963,28 +8963,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M91">
-        <v>850.7118823984931</v>
+        <v>860.2704428748806</v>
       </c>
       <c r="N91">
-        <v>884.6214509348404</v>
+        <v>875.0628904584529</v>
       </c>
       <c r="O91">
-        <v>221.1553627337101</v>
+        <v>218.7657226146132</v>
       </c>
       <c r="P91">
-        <v>663.4660882011303</v>
+        <v>656.2971678438397</v>
       </c>
       <c r="Q91">
-        <v>1677.46608820113</v>
+        <v>1670.29716784384</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3074043634207024</v>
+        <v>0.3326395110175547</v>
       </c>
       <c r="T91">
-        <v>6.041671210639779</v>
+        <v>6.624469076617893</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.039860226755906</v>
+        <v>2.017195113125285</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9009,22 +9009,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08442895110175547</v>
+        <v>0.09413842222723368</v>
       </c>
       <c r="C92">
-        <v>498.653009255524</v>
+        <v>-1825.482512567278</v>
       </c>
       <c r="D92">
-        <v>10942.86729520382</v>
+        <v>8744.834154335995</v>
       </c>
       <c r="E92">
-        <v>1303.276190450189</v>
+        <v>1429.37857140517</v>
       </c>
       <c r="F92">
-        <v>11349.21428594829</v>
+        <v>11475.31666690327</v>
       </c>
       <c r="G92">
         <v>905</v>
@@ -9045,45 +9045,45 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M92">
-        <v>860.2704428748806</v>
+        <v>1032.778500021295</v>
       </c>
       <c r="N92">
-        <v>875.0628904584529</v>
+        <v>702.5548333120389</v>
       </c>
       <c r="O92">
-        <v>218.7657226146132</v>
+        <v>175.6387083280097</v>
       </c>
       <c r="P92">
-        <v>656.2971678438397</v>
+        <v>526.9161249840292</v>
       </c>
       <c r="Q92">
-        <v>1670.29716784384</v>
+        <v>1540.916124984029</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3326395110175547</v>
+        <v>0.3634824691914854</v>
       </c>
       <c r="T92">
-        <v>6.624469076617893</v>
+        <v>7.336777579480033</v>
       </c>
       <c r="U92">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V92">
         <v>0.25</v>
       </c>
       <c r="W92">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.017195113125285</v>
+        <v>1.680257028295567</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9091,22 +9091,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09413842222723368</v>
+        <v>0.0942628933527119</v>
       </c>
       <c r="C93">
-        <v>-1825.482512567278</v>
+        <v>-1974.044950568146</v>
       </c>
       <c r="D93">
-        <v>8744.834154335995</v>
+        <v>8722.374097290109</v>
       </c>
       <c r="E93">
-        <v>1429.37857140517</v>
+        <v>1555.480952360153</v>
       </c>
       <c r="F93">
-        <v>11475.31666690327</v>
+        <v>11601.41904785825</v>
       </c>
       <c r="G93">
         <v>905</v>
@@ -9127,28 +9127,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M93">
-        <v>1032.778500021295</v>
+        <v>1044.127714307243</v>
       </c>
       <c r="N93">
-        <v>702.5548333120389</v>
+        <v>691.2056190260905</v>
       </c>
       <c r="O93">
-        <v>175.6387083280097</v>
+        <v>172.8014047565226</v>
       </c>
       <c r="P93">
-        <v>526.9161249840292</v>
+        <v>518.4042142695679</v>
       </c>
       <c r="Q93">
-        <v>1540.916124984029</v>
+        <v>1532.404214269568</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3634824691914854</v>
+        <v>0.4020361669088988</v>
       </c>
       <c r="T93">
-        <v>7.336777579480033</v>
+        <v>8.227163208057709</v>
       </c>
       <c r="U93">
         <v>0.09000000000000001</v>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.680257028295567</v>
+        <v>1.661993364944528</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9173,22 +9173,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.0942628933527119</v>
+        <v>0.0943873644781901</v>
       </c>
       <c r="C94">
-        <v>-1974.044950568146</v>
+        <v>-2122.492312206716</v>
       </c>
       <c r="D94">
-        <v>8722.374097290109</v>
+        <v>8700.02911660652</v>
       </c>
       <c r="E94">
-        <v>1555.480952360153</v>
+        <v>1681.583333315133</v>
       </c>
       <c r="F94">
-        <v>11601.41904785825</v>
+        <v>11727.52142881324</v>
       </c>
       <c r="G94">
         <v>905</v>
@@ -9209,28 +9209,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M94">
-        <v>1044.127714307243</v>
+        <v>1055.476928593191</v>
       </c>
       <c r="N94">
-        <v>691.2056190260905</v>
+        <v>679.8564047401421</v>
       </c>
       <c r="O94">
-        <v>172.8014047565226</v>
+        <v>169.9641011850355</v>
       </c>
       <c r="P94">
-        <v>518.4042142695679</v>
+        <v>509.8923035551066</v>
       </c>
       <c r="Q94">
-        <v>1532.404214269568</v>
+        <v>1523.892303555107</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4020361669088988</v>
+        <v>0.4516052068312874</v>
       </c>
       <c r="T94">
-        <v>8.227163208057709</v>
+        <v>9.37194473051472</v>
       </c>
       <c r="U94">
         <v>0.09000000000000001</v>
@@ -9247,7 +9247,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.661993364944528</v>
+        <v>1.644122468547275</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9255,22 +9255,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0943873644781901</v>
+        <v>0.0945118356036683</v>
       </c>
       <c r="C95">
-        <v>-2122.492312206716</v>
+        <v>-2270.825479631083</v>
       </c>
       <c r="D95">
-        <v>8700.02911660652</v>
+        <v>8677.798330137133</v>
       </c>
       <c r="E95">
-        <v>1681.583333315133</v>
+        <v>1807.685714270114</v>
       </c>
       <c r="F95">
-        <v>11727.52142881324</v>
+        <v>11853.62380976822</v>
       </c>
       <c r="G95">
         <v>905</v>
@@ -9291,28 +9291,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M95">
-        <v>1055.476928593191</v>
+        <v>1066.82614287914</v>
       </c>
       <c r="N95">
-        <v>679.8564047401421</v>
+        <v>668.507190454194</v>
       </c>
       <c r="O95">
-        <v>169.9641011850355</v>
+        <v>167.1267976135485</v>
       </c>
       <c r="P95">
-        <v>509.8923035551066</v>
+        <v>501.3803928406455</v>
       </c>
       <c r="Q95">
-        <v>1523.892303555107</v>
+        <v>1515.380392840646</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4516052068312874</v>
+        <v>0.5176972600611387</v>
       </c>
       <c r="T95">
-        <v>9.37194473051472</v>
+        <v>10.89832009379073</v>
       </c>
       <c r="U95">
         <v>0.09000000000000001</v>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.644122468547275</v>
+        <v>1.626631803988261</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9337,22 +9337,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0945118356036683</v>
+        <v>0.09463630672914652</v>
       </c>
       <c r="C96">
-        <v>-2270.825479631083</v>
+        <v>-2419.045325995885</v>
       </c>
       <c r="D96">
-        <v>8677.798330137133</v>
+        <v>8655.680864727312</v>
       </c>
       <c r="E96">
-        <v>1807.685714270114</v>
+        <v>1933.788095225094</v>
       </c>
       <c r="F96">
-        <v>11853.62380976822</v>
+        <v>11979.7261907232</v>
       </c>
       <c r="G96">
         <v>905</v>
@@ -9373,28 +9373,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M96">
-        <v>1066.82614287914</v>
+        <v>1078.175357165088</v>
       </c>
       <c r="N96">
-        <v>668.507190454194</v>
+        <v>657.1579761682456</v>
       </c>
       <c r="O96">
-        <v>167.1267976135485</v>
+        <v>164.2894940420614</v>
       </c>
       <c r="P96">
-        <v>501.3803928406455</v>
+        <v>492.8684821261842</v>
       </c>
       <c r="Q96">
-        <v>1515.380392840646</v>
+        <v>1506.868482126184</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5176972600611387</v>
+        <v>0.610226134582931</v>
       </c>
       <c r="T96">
-        <v>10.89832009379073</v>
+        <v>13.03524560237716</v>
       </c>
       <c r="U96">
         <v>0.09000000000000001</v>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.626631803988261</v>
+        <v>1.60950936394628</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9419,22 +9419,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09463630672914652</v>
+        <v>0.09476077785462472</v>
       </c>
       <c r="C97">
-        <v>-2419.045325995885</v>
+        <v>-2567.152715576582</v>
       </c>
       <c r="D97">
-        <v>8655.680864727312</v>
+        <v>8633.675856101598</v>
       </c>
       <c r="E97">
-        <v>1933.788095225094</v>
+        <v>2059.890476180077</v>
       </c>
       <c r="F97">
-        <v>11979.7261907232</v>
+        <v>12105.82857167818</v>
       </c>
       <c r="G97">
         <v>905</v>
@@ -9455,28 +9455,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M97">
-        <v>1078.175357165088</v>
+        <v>1089.524571451036</v>
       </c>
       <c r="N97">
-        <v>657.1579761682456</v>
+        <v>645.8087618822972</v>
       </c>
       <c r="O97">
-        <v>164.2894940420614</v>
+        <v>161.4521904705743</v>
       </c>
       <c r="P97">
-        <v>492.8684821261842</v>
+        <v>484.3565714117229</v>
       </c>
       <c r="Q97">
-        <v>1506.868482126184</v>
+        <v>1498.356571411723</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.610226134582931</v>
+        <v>0.7490194463656192</v>
       </c>
       <c r="T97">
-        <v>13.03524560237716</v>
+        <v>16.2406338652568</v>
       </c>
       <c r="U97">
         <v>0.09000000000000001</v>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.60950936394628</v>
+        <v>1.592743641405172</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9501,22 +9501,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09476077785462472</v>
+        <v>0.09488524898010293</v>
       </c>
       <c r="C98">
-        <v>-2567.15271557658</v>
+        <v>-2715.148503882077</v>
       </c>
       <c r="D98">
-        <v>8633.675856101598</v>
+        <v>8611.782448751081</v>
       </c>
       <c r="E98">
-        <v>2059.890476180075</v>
+        <v>2185.992857135056</v>
       </c>
       <c r="F98">
-        <v>12105.82857167818</v>
+        <v>12231.93095263316</v>
       </c>
       <c r="G98">
         <v>905</v>
@@ -9537,28 +9537,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M98">
-        <v>1089.524571451036</v>
+        <v>1100.873785736984</v>
       </c>
       <c r="N98">
-        <v>645.8087618822974</v>
+        <v>634.4595475963492</v>
       </c>
       <c r="O98">
-        <v>161.4521904705744</v>
+        <v>158.6148868990873</v>
       </c>
       <c r="P98">
-        <v>484.3565714117231</v>
+        <v>475.8446606972619</v>
       </c>
       <c r="Q98">
-        <v>1498.356571411723</v>
+        <v>1489.844660697262</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7490194463656173</v>
+        <v>0.9803416326700967</v>
       </c>
       <c r="T98">
-        <v>16.24063386525675</v>
+        <v>21.58294763672279</v>
       </c>
       <c r="U98">
         <v>0.09000000000000001</v>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.592743641405173</v>
+        <v>1.576323603864914</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9583,22 +9583,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09488524898010293</v>
+        <v>0.09500972010558115</v>
       </c>
       <c r="C99">
-        <v>-2715.148503882077</v>
+        <v>-2863.033537765581</v>
       </c>
       <c r="D99">
-        <v>8611.782448751081</v>
+        <v>8589.999795822558</v>
       </c>
       <c r="E99">
-        <v>2185.992857135056</v>
+        <v>2312.095238090036</v>
       </c>
       <c r="F99">
-        <v>12231.93095263316</v>
+        <v>12358.03333358814</v>
       </c>
       <c r="G99">
         <v>905</v>
@@ -9619,28 +9619,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M99">
-        <v>1100.873785736984</v>
+        <v>1112.223000022933</v>
       </c>
       <c r="N99">
-        <v>634.4595475963492</v>
+        <v>623.1103333104008</v>
       </c>
       <c r="O99">
-        <v>158.6148868990873</v>
+        <v>155.7775833276002</v>
       </c>
       <c r="P99">
-        <v>475.8446606972619</v>
+        <v>467.3327499828006</v>
       </c>
       <c r="Q99">
-        <v>1489.844660697262</v>
+        <v>1481.332749982801</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9803416326700967</v>
+        <v>1.442986005279056</v>
       </c>
       <c r="T99">
-        <v>21.58294763672279</v>
+        <v>32.26757517965487</v>
       </c>
       <c r="U99">
         <v>0.09000000000000001</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.576323603864914</v>
+        <v>1.560238669131598</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9665,22 +9665,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09500972010558115</v>
+        <v>0.09513419123105935</v>
       </c>
       <c r="C100">
-        <v>-2863.033537765581</v>
+        <v>-3010.808655533778</v>
       </c>
       <c r="D100">
-        <v>8589.999795822558</v>
+        <v>8568.327059009343</v>
       </c>
       <c r="E100">
-        <v>2312.095238090036</v>
+        <v>2438.197619045019</v>
       </c>
       <c r="F100">
-        <v>12358.03333358814</v>
+        <v>12484.13571454312</v>
       </c>
       <c r="G100">
         <v>905</v>
@@ -9701,28 +9701,28 @@
         <v>1735.333333333333</v>
       </c>
       <c r="M100">
-        <v>1112.223000022933</v>
+        <v>1123.572214308881</v>
       </c>
       <c r="N100">
-        <v>623.1103333104008</v>
+        <v>611.7611190244525</v>
       </c>
       <c r="O100">
-        <v>155.7775833276002</v>
+        <v>152.9402797561131</v>
       </c>
       <c r="P100">
-        <v>467.3327499828006</v>
+        <v>458.8208392683393</v>
       </c>
       <c r="Q100">
-        <v>1481.332749982801</v>
+        <v>1472.820839268339</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.442986005279056</v>
+        <v>2.830919123105932</v>
       </c>
       <c r="T100">
-        <v>32.26757517965487</v>
+        <v>64.32145780845109</v>
       </c>
       <c r="U100">
         <v>0.09000000000000001</v>
@@ -9739,91 +9739,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.560238669131598</v>
+        <v>1.544478682574713</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09513419123105935</v>
-      </c>
-      <c r="C101">
-        <v>-3010.808655533778</v>
-      </c>
-      <c r="D101">
-        <v>8568.327059009343</v>
-      </c>
-      <c r="E101">
-        <v>2438.197619045019</v>
-      </c>
-      <c r="F101">
-        <v>12484.13571454312</v>
-      </c>
-      <c r="G101">
-        <v>905</v>
-      </c>
-      <c r="H101">
-        <v>2564.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2749.333333333333</v>
-      </c>
-      <c r="K101">
-        <v>1014</v>
-      </c>
-      <c r="L101">
-        <v>1735.333333333333</v>
-      </c>
-      <c r="M101">
-        <v>1123.572214308881</v>
-      </c>
-      <c r="N101">
-        <v>611.7611190244525</v>
-      </c>
-      <c r="O101">
-        <v>152.9402797561131</v>
-      </c>
-      <c r="P101">
-        <v>458.8208392683393</v>
-      </c>
-      <c r="Q101">
-        <v>1472.820839268339</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.830919123105932</v>
-      </c>
-      <c r="T101">
-        <v>64.32145780845109</v>
-      </c>
-      <c r="U101">
-        <v>0.09000000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.0675</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.544478682574713</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
